--- a/재고조사표.xlsx
+++ b/재고조사표.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QC\Downloads\창고\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김훈희\Downloads\창고\창고\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA26485-304C-425B-AEDD-AAB034D9BE34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="47925" windowHeight="17160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="47925" windowHeight="17160"/>
   </bookViews>
   <sheets>
-    <sheet name="B1" sheetId="1" r:id="rId1"/>
-    <sheet name="B2" sheetId="8" r:id="rId2"/>
-    <sheet name="B3" sheetId="9" r:id="rId3"/>
+    <sheet name="셀" sheetId="1" r:id="rId1"/>
+    <sheet name="루" sheetId="8" r:id="rId2"/>
+    <sheet name="리" sheetId="9" r:id="rId3"/>
     <sheet name="W1,캡창고" sheetId="10" r:id="rId4"/>
     <sheet name="W2" sheetId="11" r:id="rId5"/>
     <sheet name="W3" sheetId="12" r:id="rId6"/>
@@ -23,15 +22,15 @@
     <sheet name="TOTAL" sheetId="2" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'B1'!$A$3:$AI$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'B2'!$A$3:$AM$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'B3'!$A$3:$AM$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'W1,캡창고'!$A$3:$AM$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'W2'!$A$3:$AM$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'W3'!$A$3:$AM$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">루!$A$3:$AM$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">리!$A$3:$AI$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">셀!$A$3:$AE$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'액젓,비트,완제품'!$A$3:$AM$45</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="358">
   <si>
     <t>M300</t>
   </si>
@@ -1341,7 +1340,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
@@ -1953,6 +1952,12 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1965,16 +1970,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2025,13 +2024,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>271462</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>409575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>2576512</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>1400175</xdr:rowOff>
@@ -2303,13 +2302,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>271462</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>409575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>2576512</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>1400175</xdr:rowOff>
@@ -2700,19 +2699,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:AI46"/>
+  <dimension ref="A3:AH46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.125" customWidth="1"/>
-    <col min="2" max="35" width="36.125" customWidth="1"/>
+    <col min="2" max="31" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:35" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
@@ -2724,7 +2723,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="22"/>
     </row>
-    <row r="4" spans="1:35" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1"/>
       <c r="C4" s="35" t="s">
         <v>155</v>
@@ -2733,13 +2732,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -2759,13 +2758,9 @@
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="4"/>
-    </row>
-    <row r="5" spans="1:35" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE4" s="4"/>
+    </row>
+    <row r="5" spans="1:34" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="25">
         <v>1</v>
       </c>
@@ -2794,114 +2789,98 @@
         <v>7</v>
       </c>
       <c r="O5" s="30"/>
-      <c r="P5" s="31">
-        <v>8</v>
-      </c>
+      <c r="P5" s="34"/>
       <c r="Q5" s="32"/>
       <c r="R5" s="31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S5" s="32"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="32"/>
+      <c r="T5" s="31">
+        <v>6</v>
+      </c>
+      <c r="U5" s="30"/>
       <c r="V5" s="31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W5" s="32"/>
       <c r="X5" s="31">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="30"/>
+        <v>4</v>
+      </c>
+      <c r="Y5" s="32"/>
       <c r="Z5" s="31">
-        <v>5</v>
-      </c>
-      <c r="AA5" s="32"/>
+        <v>3</v>
+      </c>
+      <c r="AA5" s="30"/>
       <c r="AB5" s="31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="32"/>
       <c r="AD5" s="31">
-        <v>3</v>
-      </c>
-      <c r="AE5" s="30"/>
-      <c r="AF5" s="31">
-        <v>2</v>
-      </c>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="31">
         <v>1</v>
       </c>
-      <c r="AI5" s="32"/>
-    </row>
-    <row r="6" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="AE5" s="32"/>
+    </row>
+    <row r="6" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="58" t="s">
+        <v>152</v>
+      </c>
       <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AI6" s="57"/>
-    </row>
-    <row r="7" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE6" s="59"/>
+    </row>
+    <row r="7" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="41" t="s">
         <v>153</v>
       </c>
@@ -2944,20 +2923,20 @@
       <c r="O7" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="P7" s="41" t="s">
+      <c r="P7" s="28"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="Q7" s="42" t="s">
+      <c r="S7" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="R7" s="41" t="s">
+      <c r="T7" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="S7" s="42" t="s">
+      <c r="U7" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="T7" s="28"/>
-      <c r="U7" s="29"/>
       <c r="V7" s="26" t="s">
         <v>153</v>
       </c>
@@ -2988,21 +2967,9 @@
       <c r="AE7" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="AF7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="63">
+    </row>
+    <row r="8" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A8" s="56">
         <v>1</v>
       </c>
       <c r="B8" s="53" t="s" ph="1">
@@ -3021,12 +2988,12 @@
       <c r="M8" s="50"/>
       <c r="N8" s="49" ph="1"/>
       <c r="O8" s="50"/>
-      <c r="P8" s="49" ph="1"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="49" ph="1"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="8"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="51" ph="1"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="51" ph="1"/>
+      <c r="U8" s="52"/>
       <c r="V8" s="51" ph="1"/>
       <c r="W8" s="52"/>
       <c r="X8" s="51" ph="1"/>
@@ -3035,17 +3002,15 @@
       <c r="AA8" s="52"/>
       <c r="AB8" s="51" ph="1"/>
       <c r="AC8" s="52"/>
-      <c r="AD8" s="51" ph="1"/>
+      <c r="AD8" s="51" t="s" ph="1">
+        <v>278</v>
+      </c>
       <c r="AE8" s="52"/>
-      <c r="AF8" s="51" ph="1"/>
-      <c r="AG8" s="52"/>
-      <c r="AH8" s="51" t="s" ph="1">
-        <v>278</v>
-      </c>
-      <c r="AI8" s="52"/>
-    </row>
-    <row r="9" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="63"/>
+      <c r="AF8" ph="1"/>
+      <c r="AH8" ph="1"/>
+    </row>
+    <row r="9" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="56"/>
       <c r="B9" s="47">
         <v>10</v>
       </c>
@@ -3064,12 +3029,12 @@
       <c r="M9" s="48"/>
       <c r="N9" s="47"/>
       <c r="O9" s="48"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="21"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="40"/>
       <c r="V9" s="39"/>
       <c r="W9" s="40"/>
       <c r="X9" s="39"/>
@@ -3079,16 +3044,12 @@
       <c r="AB9" s="39"/>
       <c r="AC9" s="40"/>
       <c r="AD9" s="39"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="40">
+      <c r="AE9" s="40">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="63">
+    <row r="10" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A10" s="56">
         <v>2</v>
       </c>
       <c r="B10" s="49" ph="1"/>
@@ -3105,33 +3066,31 @@
       <c r="M10" s="50"/>
       <c r="N10" s="49" ph="1"/>
       <c r="O10" s="50"/>
-      <c r="P10" s="49" ph="1"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="49" ph="1"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="8"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="51" ph="1"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="51" ph="1"/>
+      <c r="U10" s="52"/>
       <c r="V10" s="51" ph="1"/>
       <c r="W10" s="52"/>
       <c r="X10" s="51" ph="1"/>
       <c r="Y10" s="52"/>
       <c r="Z10" s="51" ph="1"/>
       <c r="AA10" s="52"/>
-      <c r="AB10" s="51" ph="1"/>
+      <c r="AB10" s="51" t="s" ph="1">
+        <v>280</v>
+      </c>
       <c r="AC10" s="52"/>
-      <c r="AD10" s="51" ph="1"/>
+      <c r="AD10" s="51" t="s" ph="1">
+        <v>279</v>
+      </c>
       <c r="AE10" s="52"/>
-      <c r="AF10" s="51" t="s" ph="1">
-        <v>280</v>
-      </c>
-      <c r="AG10" s="52"/>
-      <c r="AH10" s="51" t="s" ph="1">
-        <v>279</v>
-      </c>
-      <c r="AI10" s="52"/>
-    </row>
-    <row r="11" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
+      <c r="AF10" ph="1"/>
+      <c r="AH10" ph="1"/>
+    </row>
+    <row r="11" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="56"/>
       <c r="B11" s="47"/>
       <c r="C11" s="48"/>
       <c r="D11" s="47"/>
@@ -3146,12 +3105,12 @@
       <c r="M11" s="48"/>
       <c r="N11" s="47"/>
       <c r="O11" s="48"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="18"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="40"/>
       <c r="V11" s="39"/>
       <c r="W11" s="40"/>
       <c r="X11" s="39"/>
@@ -3159,22 +3118,18 @@
       <c r="Z11" s="39"/>
       <c r="AA11" s="40"/>
       <c r="AB11" s="39"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="40">
+      <c r="AC11" s="40">
         <v>6</v>
       </c>
-      <c r="AH11" s="39">
+      <c r="AD11" s="39">
         <v>5</v>
       </c>
-      <c r="AI11" s="40">
+      <c r="AE11" s="40">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="63">
+    <row r="12" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A12" s="56">
         <v>3</v>
       </c>
       <c r="B12" s="49" ph="1"/>
@@ -3191,12 +3146,12 @@
       <c r="M12" s="50"/>
       <c r="N12" s="49" ph="1"/>
       <c r="O12" s="50"/>
-      <c r="P12" s="49" ph="1"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="49" ph="1"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="8"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="51" ph="1"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="51" ph="1"/>
+      <c r="U12" s="52"/>
       <c r="V12" s="51" ph="1"/>
       <c r="W12" s="52"/>
       <c r="X12" s="51" ph="1"/>
@@ -3205,17 +3160,15 @@
       <c r="AA12" s="52"/>
       <c r="AB12" s="51" ph="1"/>
       <c r="AC12" s="52"/>
-      <c r="AD12" s="51" ph="1"/>
+      <c r="AD12" s="51" t="s" ph="1">
+        <v>281</v>
+      </c>
       <c r="AE12" s="52"/>
-      <c r="AF12" s="51" ph="1"/>
-      <c r="AG12" s="52"/>
-      <c r="AH12" s="51" t="s" ph="1">
-        <v>281</v>
-      </c>
-      <c r="AI12" s="52"/>
-    </row>
-    <row r="13" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
+      <c r="AF12" ph="1"/>
+      <c r="AH12" ph="1"/>
+    </row>
+    <row r="13" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="56"/>
       <c r="B13" s="47"/>
       <c r="C13" s="48"/>
       <c r="D13" s="47"/>
@@ -3230,12 +3183,12 @@
       <c r="M13" s="48"/>
       <c r="N13" s="47"/>
       <c r="O13" s="48"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="18"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="40"/>
       <c r="V13" s="39"/>
       <c r="W13" s="40"/>
       <c r="X13" s="39"/>
@@ -3244,19 +3197,15 @@
       <c r="AA13" s="40"/>
       <c r="AB13" s="39"/>
       <c r="AC13" s="40"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="39">
+      <c r="AD13" s="39">
         <v>10</v>
       </c>
-      <c r="AI13" s="40">
+      <c r="AE13" s="40">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="63">
+    <row r="14" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A14" s="56">
         <v>4</v>
       </c>
       <c r="B14" s="49" ph="1"/>
@@ -3273,12 +3222,12 @@
       <c r="M14" s="50"/>
       <c r="N14" s="49" ph="1"/>
       <c r="O14" s="50"/>
-      <c r="P14" s="49" ph="1"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="49" ph="1"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="8"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="51" ph="1"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="51" ph="1"/>
+      <c r="U14" s="52"/>
       <c r="V14" s="51" ph="1"/>
       <c r="W14" s="52"/>
       <c r="X14" s="51" ph="1"/>
@@ -3287,17 +3236,15 @@
       <c r="AA14" s="52"/>
       <c r="AB14" s="51" ph="1"/>
       <c r="AC14" s="52"/>
-      <c r="AD14" s="51" ph="1"/>
+      <c r="AD14" s="51" t="s" ph="1">
+        <v>282</v>
+      </c>
       <c r="AE14" s="52"/>
-      <c r="AF14" s="51" ph="1"/>
-      <c r="AG14" s="52"/>
-      <c r="AH14" s="51" t="s" ph="1">
-        <v>282</v>
-      </c>
-      <c r="AI14" s="52"/>
-    </row>
-    <row r="15" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63"/>
+      <c r="AF14" ph="1"/>
+      <c r="AH14" ph="1"/>
+    </row>
+    <row r="15" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="56"/>
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="47"/>
@@ -3312,12 +3259,12 @@
       <c r="M15" s="48"/>
       <c r="N15" s="47"/>
       <c r="O15" s="48"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="18"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="40"/>
       <c r="V15" s="39"/>
       <c r="W15" s="40"/>
       <c r="X15" s="39"/>
@@ -3326,19 +3273,15 @@
       <c r="AA15" s="40"/>
       <c r="AB15" s="39"/>
       <c r="AC15" s="40"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="39">
+      <c r="AD15" s="39">
         <v>2</v>
       </c>
-      <c r="AI15" s="40">
+      <c r="AE15" s="40">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="63">
+    <row r="16" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A16" s="56">
         <v>5</v>
       </c>
       <c r="B16" s="51" ph="1"/>
@@ -3355,12 +3298,12 @@
       <c r="M16" s="52"/>
       <c r="N16" s="51" ph="1"/>
       <c r="O16" s="52"/>
-      <c r="P16" s="51" ph="1"/>
-      <c r="Q16" s="52"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="8"/>
       <c r="R16" s="51" ph="1"/>
       <c r="S16" s="52"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="8"/>
+      <c r="T16" s="51" ph="1"/>
+      <c r="U16" s="52"/>
       <c r="V16" s="51" ph="1"/>
       <c r="W16" s="52"/>
       <c r="X16" s="51" ph="1"/>
@@ -3369,17 +3312,15 @@
       <c r="AA16" s="52"/>
       <c r="AB16" s="51" ph="1"/>
       <c r="AC16" s="52"/>
-      <c r="AD16" s="51" ph="1"/>
+      <c r="AD16" s="51" t="s" ph="1">
+        <v>283</v>
+      </c>
       <c r="AE16" s="52"/>
-      <c r="AF16" s="51" ph="1"/>
-      <c r="AG16" s="52"/>
-      <c r="AH16" s="51" t="s" ph="1">
-        <v>283</v>
-      </c>
-      <c r="AI16" s="52"/>
-    </row>
-    <row r="17" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="63"/>
+      <c r="AF16" ph="1"/>
+      <c r="AH16" ph="1"/>
+    </row>
+    <row r="17" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="56"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="39"/>
@@ -3394,12 +3335,12 @@
       <c r="M17" s="40"/>
       <c r="N17" s="39"/>
       <c r="O17" s="40"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="8"/>
       <c r="R17" s="39"/>
       <c r="S17" s="40"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="8"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="40"/>
       <c r="V17" s="39"/>
       <c r="W17" s="40"/>
       <c r="X17" s="39"/>
@@ -3408,19 +3349,15 @@
       <c r="AA17" s="40"/>
       <c r="AB17" s="39"/>
       <c r="AC17" s="40"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="40"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="40"/>
-      <c r="AH17" s="39">
+      <c r="AD17" s="39">
         <v>1</v>
       </c>
-      <c r="AI17" s="40">
+      <c r="AE17" s="40">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="63">
+    <row r="18" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A18" s="56">
         <v>6</v>
       </c>
       <c r="B18" s="51" t="s" ph="1">
@@ -3439,33 +3376,31 @@
       <c r="M18" s="52"/>
       <c r="N18" s="51" ph="1"/>
       <c r="O18" s="52"/>
-      <c r="P18" s="51" ph="1"/>
-      <c r="Q18" s="52"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="8"/>
       <c r="R18" s="51" ph="1"/>
       <c r="S18" s="52"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="8"/>
+      <c r="T18" s="51" ph="1"/>
+      <c r="U18" s="52"/>
       <c r="V18" s="51" ph="1"/>
       <c r="W18" s="52"/>
       <c r="X18" s="51" ph="1"/>
       <c r="Y18" s="52"/>
       <c r="Z18" s="51" ph="1"/>
       <c r="AA18" s="52"/>
-      <c r="AB18" s="51" ph="1"/>
+      <c r="AB18" s="51" t="s" ph="1">
+        <v>286</v>
+      </c>
       <c r="AC18" s="52"/>
-      <c r="AD18" s="51" ph="1"/>
+      <c r="AD18" s="51" t="s" ph="1">
+        <v>285</v>
+      </c>
       <c r="AE18" s="52"/>
-      <c r="AF18" s="51" t="s" ph="1">
-        <v>286</v>
-      </c>
-      <c r="AG18" s="52"/>
-      <c r="AH18" s="51" t="s" ph="1">
-        <v>285</v>
-      </c>
-      <c r="AI18" s="52"/>
-    </row>
-    <row r="19" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
+      <c r="AF18" ph="1"/>
+      <c r="AH18" ph="1"/>
+    </row>
+    <row r="19" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="56"/>
       <c r="B19" s="39">
         <v>10</v>
       </c>
@@ -3484,35 +3419,31 @@
       <c r="M19" s="40"/>
       <c r="N19" s="39"/>
       <c r="O19" s="40"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="8"/>
       <c r="R19" s="39"/>
       <c r="S19" s="40"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="8"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="40"/>
       <c r="V19" s="39"/>
       <c r="W19" s="40"/>
       <c r="X19" s="39"/>
       <c r="Y19" s="40"/>
       <c r="Z19" s="39"/>
       <c r="AA19" s="40"/>
-      <c r="AB19" s="39"/>
+      <c r="AB19" s="39">
+        <v>4</v>
+      </c>
       <c r="AC19" s="40"/>
-      <c r="AD19" s="39"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="39">
-        <v>4</v>
-      </c>
-      <c r="AG19" s="40"/>
-      <c r="AH19" s="39">
+      <c r="AD19" s="39">
         <v>6</v>
       </c>
-      <c r="AI19" s="40">
+      <c r="AE19" s="40">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="63">
+    <row r="20" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A20" s="56">
         <v>7</v>
       </c>
       <c r="B20" s="51" t="s" ph="1">
@@ -3531,33 +3462,31 @@
       <c r="M20" s="52"/>
       <c r="N20" s="51" ph="1"/>
       <c r="O20" s="52"/>
-      <c r="P20" s="51" ph="1"/>
-      <c r="Q20" s="52"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="8"/>
       <c r="R20" s="51" ph="1"/>
       <c r="S20" s="52"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="8"/>
+      <c r="T20" s="51" ph="1"/>
+      <c r="U20" s="52"/>
       <c r="V20" s="51" ph="1"/>
       <c r="W20" s="52"/>
       <c r="X20" s="51" ph="1"/>
       <c r="Y20" s="52"/>
       <c r="Z20" s="51" ph="1"/>
       <c r="AA20" s="52"/>
-      <c r="AB20" s="51" ph="1"/>
+      <c r="AB20" s="51" t="s" ph="1">
+        <v>286</v>
+      </c>
       <c r="AC20" s="52"/>
-      <c r="AD20" s="51" ph="1"/>
+      <c r="AD20" s="51" t="s" ph="1">
+        <v>287</v>
+      </c>
       <c r="AE20" s="52"/>
-      <c r="AF20" s="51" t="s" ph="1">
-        <v>286</v>
-      </c>
-      <c r="AG20" s="52"/>
-      <c r="AH20" s="51" t="s" ph="1">
-        <v>287</v>
-      </c>
-      <c r="AI20" s="52"/>
-    </row>
-    <row r="21" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
+      <c r="AF20" ph="1"/>
+      <c r="AH20" ph="1"/>
+    </row>
+    <row r="21" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="56"/>
       <c r="B21" s="39">
         <v>6</v>
       </c>
@@ -3576,37 +3505,33 @@
       <c r="M21" s="40"/>
       <c r="N21" s="39"/>
       <c r="O21" s="40"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="8"/>
       <c r="R21" s="39"/>
       <c r="S21" s="40"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="8"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="40"/>
       <c r="V21" s="39"/>
       <c r="W21" s="40"/>
       <c r="X21" s="39"/>
       <c r="Y21" s="40"/>
       <c r="Z21" s="39"/>
       <c r="AA21" s="40"/>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="39"/>
-      <c r="AE21" s="40"/>
-      <c r="AF21" s="39">
+      <c r="AB21" s="39">
         <v>3</v>
       </c>
-      <c r="AG21" s="40">
+      <c r="AC21" s="40">
         <v>15</v>
       </c>
-      <c r="AH21" s="39">
+      <c r="AD21" s="39">
         <v>10</v>
       </c>
-      <c r="AI21" s="40">
+      <c r="AE21" s="40">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="63">
+    <row r="22" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A22" s="56">
         <v>8</v>
       </c>
       <c r="B22" s="51" t="s" ph="1">
@@ -3625,12 +3550,12 @@
       <c r="M22" s="52"/>
       <c r="N22" s="51" ph="1"/>
       <c r="O22" s="52"/>
-      <c r="P22" s="51" ph="1"/>
-      <c r="Q22" s="52"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="8"/>
       <c r="R22" s="51" ph="1"/>
       <c r="S22" s="52"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="8"/>
+      <c r="T22" s="51" ph="1"/>
+      <c r="U22" s="52"/>
       <c r="V22" s="51" ph="1"/>
       <c r="W22" s="52"/>
       <c r="X22" s="51" ph="1"/>
@@ -3639,17 +3564,15 @@
       <c r="AA22" s="52"/>
       <c r="AB22" s="51" ph="1"/>
       <c r="AC22" s="52"/>
-      <c r="AD22" s="51" ph="1"/>
+      <c r="AD22" s="51" t="s" ph="1">
+        <v>277</v>
+      </c>
       <c r="AE22" s="52"/>
-      <c r="AF22" s="51" ph="1"/>
-      <c r="AG22" s="52"/>
-      <c r="AH22" s="51" t="s" ph="1">
-        <v>277</v>
-      </c>
-      <c r="AI22" s="52"/>
-    </row>
-    <row r="23" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="63"/>
+      <c r="AF22" ph="1"/>
+      <c r="AH22" ph="1"/>
+    </row>
+    <row r="23" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="56"/>
       <c r="B23" s="39">
         <v>16</v>
       </c>
@@ -3668,12 +3591,12 @@
       <c r="M23" s="40"/>
       <c r="N23" s="39"/>
       <c r="O23" s="40"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="8"/>
       <c r="R23" s="39"/>
       <c r="S23" s="40"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="8"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="40"/>
       <c r="V23" s="39"/>
       <c r="W23" s="40"/>
       <c r="X23" s="39"/>
@@ -3682,17 +3605,13 @@
       <c r="AA23" s="40"/>
       <c r="AB23" s="39"/>
       <c r="AC23" s="40"/>
-      <c r="AD23" s="39"/>
+      <c r="AD23" s="39">
+        <v>13</v>
+      </c>
       <c r="AE23" s="40"/>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="40"/>
-      <c r="AH23" s="39">
-        <v>13</v>
-      </c>
-      <c r="AI23" s="40"/>
-    </row>
-    <row r="24" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="63">
+    </row>
+    <row r="24" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A24" s="56">
         <v>9</v>
       </c>
       <c r="B24" s="51" t="s" ph="1">
@@ -3713,12 +3632,12 @@
       <c r="M24" s="52"/>
       <c r="N24" s="51" ph="1"/>
       <c r="O24" s="52"/>
-      <c r="P24" s="51" ph="1"/>
-      <c r="Q24" s="52"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="8"/>
       <c r="R24" s="51" ph="1"/>
       <c r="S24" s="52"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="8"/>
+      <c r="T24" s="51" ph="1"/>
+      <c r="U24" s="52"/>
       <c r="V24" s="51" ph="1"/>
       <c r="W24" s="52"/>
       <c r="X24" s="51" ph="1"/>
@@ -3727,17 +3646,15 @@
       <c r="AA24" s="52"/>
       <c r="AB24" s="51" ph="1"/>
       <c r="AC24" s="52"/>
-      <c r="AD24" s="51" ph="1"/>
+      <c r="AD24" s="51" t="s" ph="1">
+        <v>272</v>
+      </c>
       <c r="AE24" s="52"/>
-      <c r="AF24" s="51" ph="1"/>
-      <c r="AG24" s="52"/>
-      <c r="AH24" s="51" t="s" ph="1">
-        <v>272</v>
-      </c>
-      <c r="AI24" s="52"/>
-    </row>
-    <row r="25" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="63"/>
+      <c r="AF24" ph="1"/>
+      <c r="AH24" ph="1"/>
+    </row>
+    <row r="25" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="56"/>
       <c r="B25" s="39">
         <v>2</v>
       </c>
@@ -3758,12 +3675,12 @@
       <c r="M25" s="40"/>
       <c r="N25" s="39"/>
       <c r="O25" s="40"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="8"/>
       <c r="R25" s="39"/>
       <c r="S25" s="40"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="8"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="40"/>
       <c r="V25" s="39"/>
       <c r="W25" s="40"/>
       <c r="X25" s="39"/>
@@ -3772,19 +3689,15 @@
       <c r="AA25" s="40"/>
       <c r="AB25" s="39"/>
       <c r="AC25" s="40"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="40"/>
-      <c r="AH25" s="39">
+      <c r="AD25" s="39">
         <v>5</v>
       </c>
-      <c r="AI25" s="40">
+      <c r="AE25" s="40">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="63">
+    <row r="26" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A26" s="56">
         <v>10</v>
       </c>
       <c r="B26" s="51" ph="1"/>
@@ -3801,12 +3714,12 @@
       <c r="M26" s="52"/>
       <c r="N26" s="51" ph="1"/>
       <c r="O26" s="52"/>
-      <c r="P26" s="51" ph="1"/>
-      <c r="Q26" s="52"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="8"/>
       <c r="R26" s="51" ph="1"/>
       <c r="S26" s="52"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="8"/>
+      <c r="T26" s="51" ph="1"/>
+      <c r="U26" s="52"/>
       <c r="V26" s="51" ph="1"/>
       <c r="W26" s="52"/>
       <c r="X26" s="51" ph="1"/>
@@ -3817,13 +3730,11 @@
       <c r="AC26" s="52"/>
       <c r="AD26" s="51" ph="1"/>
       <c r="AE26" s="52"/>
-      <c r="AF26" s="51" ph="1"/>
-      <c r="AG26" s="52"/>
-      <c r="AH26" s="51" ph="1"/>
-      <c r="AI26" s="52"/>
-    </row>
-    <row r="27" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="63"/>
+      <c r="AF26" ph="1"/>
+      <c r="AH26" ph="1"/>
+    </row>
+    <row r="27" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="56"/>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="39"/>
@@ -3838,12 +3749,12 @@
       <c r="M27" s="40"/>
       <c r="N27" s="39"/>
       <c r="O27" s="40"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="8"/>
       <c r="R27" s="39"/>
       <c r="S27" s="40"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="8"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="40"/>
       <c r="V27" s="39"/>
       <c r="W27" s="40"/>
       <c r="X27" s="39"/>
@@ -3854,13 +3765,9 @@
       <c r="AC27" s="40"/>
       <c r="AD27" s="39"/>
       <c r="AE27" s="40"/>
-      <c r="AF27" s="39"/>
-      <c r="AG27" s="40"/>
-      <c r="AH27" s="39"/>
-      <c r="AI27" s="40"/>
-    </row>
-    <row r="28" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="63">
+    </row>
+    <row r="28" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A28" s="56">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -3877,12 +3784,12 @@
       <c r="M28" s="52"/>
       <c r="N28" s="51" ph="1"/>
       <c r="O28" s="52"/>
-      <c r="P28" s="51" ph="1"/>
-      <c r="Q28" s="52"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="8"/>
       <c r="R28" s="51" ph="1"/>
       <c r="S28" s="52"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="8"/>
+      <c r="T28" s="51" ph="1"/>
+      <c r="U28" s="52"/>
       <c r="V28" s="51" ph="1"/>
       <c r="W28" s="52"/>
       <c r="X28" s="51" ph="1"/>
@@ -3893,13 +3800,11 @@
       <c r="AC28" s="52"/>
       <c r="AD28" s="51" ph="1"/>
       <c r="AE28" s="52"/>
-      <c r="AF28" s="51" ph="1"/>
-      <c r="AG28" s="52"/>
-      <c r="AH28" s="51" ph="1"/>
-      <c r="AI28" s="52"/>
-    </row>
-    <row r="29" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="63"/>
+      <c r="AF28" ph="1"/>
+      <c r="AH28" ph="1"/>
+    </row>
+    <row r="29" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="56"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -3914,12 +3819,12 @@
       <c r="M29" s="40"/>
       <c r="N29" s="39"/>
       <c r="O29" s="40"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="8"/>
       <c r="R29" s="39"/>
       <c r="S29" s="40"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="8"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="40"/>
       <c r="V29" s="39"/>
       <c r="W29" s="40"/>
       <c r="X29" s="39"/>
@@ -3930,13 +3835,9 @@
       <c r="AC29" s="40"/>
       <c r="AD29" s="39"/>
       <c r="AE29" s="40"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="40"/>
-      <c r="AH29" s="39"/>
-      <c r="AI29" s="40"/>
-    </row>
-    <row r="30" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="63">
+    </row>
+    <row r="30" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A30" s="56">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -3953,33 +3854,31 @@
       <c r="M30" s="52"/>
       <c r="N30" s="51" ph="1"/>
       <c r="O30" s="52"/>
-      <c r="P30" s="51" ph="1"/>
-      <c r="Q30" s="52"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="8"/>
       <c r="R30" s="51" ph="1"/>
       <c r="S30" s="52"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="8"/>
+      <c r="T30" s="51" ph="1"/>
+      <c r="U30" s="52"/>
       <c r="V30" s="51" ph="1"/>
       <c r="W30" s="52"/>
       <c r="X30" s="51" ph="1"/>
       <c r="Y30" s="52"/>
       <c r="Z30" s="51" ph="1"/>
       <c r="AA30" s="52"/>
-      <c r="AB30" s="51" ph="1"/>
+      <c r="AB30" s="51" t="s" ph="1">
+        <v>276</v>
+      </c>
       <c r="AC30" s="52"/>
-      <c r="AD30" s="51" ph="1"/>
+      <c r="AD30" s="51" t="s" ph="1">
+        <v>275</v>
+      </c>
       <c r="AE30" s="52"/>
-      <c r="AF30" s="51" t="s" ph="1">
-        <v>276</v>
-      </c>
-      <c r="AG30" s="52"/>
-      <c r="AH30" s="51" t="s" ph="1">
-        <v>275</v>
-      </c>
-      <c r="AI30" s="52"/>
-    </row>
-    <row r="31" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="63"/>
+      <c r="AF30" ph="1"/>
+      <c r="AH30" ph="1"/>
+    </row>
+    <row r="31" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="56"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -3994,35 +3893,31 @@
       <c r="M31" s="40"/>
       <c r="N31" s="39"/>
       <c r="O31" s="40"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="40"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="8"/>
       <c r="R31" s="39"/>
       <c r="S31" s="40"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="8"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="40"/>
       <c r="V31" s="39"/>
       <c r="W31" s="40"/>
       <c r="X31" s="39"/>
       <c r="Y31" s="40"/>
       <c r="Z31" s="39"/>
       <c r="AA31" s="40"/>
-      <c r="AB31" s="39"/>
-      <c r="AC31" s="40"/>
+      <c r="AB31" s="39">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="40">
+        <v>14</v>
+      </c>
       <c r="AD31" s="39"/>
-      <c r="AE31" s="40"/>
-      <c r="AF31" s="39">
-        <v>2</v>
-      </c>
-      <c r="AG31" s="40">
-        <v>14</v>
-      </c>
-      <c r="AH31" s="39"/>
-      <c r="AI31" s="40">
+      <c r="AE31" s="40">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="63">
+    <row r="32" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A32" s="56">
         <v>13</v>
       </c>
       <c r="B32" s="51" ph="1"/>
@@ -4039,33 +3934,31 @@
       <c r="M32" s="52"/>
       <c r="N32" s="51" ph="1"/>
       <c r="O32" s="52"/>
-      <c r="P32" s="51" ph="1"/>
-      <c r="Q32" s="52"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="8"/>
       <c r="R32" s="51" ph="1"/>
       <c r="S32" s="52"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="8"/>
+      <c r="T32" s="51" ph="1"/>
+      <c r="U32" s="52"/>
       <c r="V32" s="51" ph="1"/>
       <c r="W32" s="52"/>
       <c r="X32" s="51" ph="1"/>
       <c r="Y32" s="52"/>
       <c r="Z32" s="51" ph="1"/>
       <c r="AA32" s="52"/>
-      <c r="AB32" s="51" ph="1"/>
+      <c r="AB32" s="51" t="s" ph="1">
+        <v>274</v>
+      </c>
       <c r="AC32" s="52"/>
-      <c r="AD32" s="51" ph="1"/>
+      <c r="AD32" s="51" t="s" ph="1">
+        <v>273</v>
+      </c>
       <c r="AE32" s="52"/>
-      <c r="AF32" s="51" t="s" ph="1">
-        <v>274</v>
-      </c>
-      <c r="AG32" s="52"/>
-      <c r="AH32" s="51" t="s" ph="1">
-        <v>273</v>
-      </c>
-      <c r="AI32" s="52"/>
-    </row>
-    <row r="33" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="63"/>
+      <c r="AF32" ph="1"/>
+      <c r="AH32" ph="1"/>
+    </row>
+    <row r="33" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="56"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40"/>
       <c r="D33" s="39"/>
@@ -4080,37 +3973,33 @@
       <c r="M33" s="40"/>
       <c r="N33" s="39"/>
       <c r="O33" s="40"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="40"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="8"/>
       <c r="R33" s="39"/>
       <c r="S33" s="40"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="8"/>
+      <c r="T33" s="39"/>
+      <c r="U33" s="40"/>
       <c r="V33" s="39"/>
       <c r="W33" s="40"/>
       <c r="X33" s="39"/>
       <c r="Y33" s="40"/>
       <c r="Z33" s="39"/>
       <c r="AA33" s="40"/>
-      <c r="AB33" s="39"/>
-      <c r="AC33" s="40"/>
-      <c r="AD33" s="39"/>
-      <c r="AE33" s="40"/>
-      <c r="AF33" s="39">
+      <c r="AB33" s="39">
         <v>1</v>
       </c>
-      <c r="AG33" s="40">
+      <c r="AC33" s="40">
         <v>3</v>
       </c>
-      <c r="AH33" s="39">
+      <c r="AD33" s="39">
         <v>1</v>
       </c>
-      <c r="AI33" s="40">
+      <c r="AE33" s="40">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="63">
+    <row r="34" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A34" s="56">
         <v>14</v>
       </c>
       <c r="B34" s="51" ph="1"/>
@@ -4127,12 +4016,12 @@
       <c r="M34" s="52"/>
       <c r="N34" s="51" ph="1"/>
       <c r="O34" s="52"/>
-      <c r="P34" s="51" ph="1"/>
-      <c r="Q34" s="52"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="8"/>
       <c r="R34" s="51" ph="1"/>
       <c r="S34" s="52"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="8"/>
+      <c r="T34" s="51" ph="1"/>
+      <c r="U34" s="52"/>
       <c r="V34" s="51" ph="1"/>
       <c r="W34" s="52"/>
       <c r="X34" s="51" ph="1"/>
@@ -4141,17 +4030,15 @@
       <c r="AA34" s="52"/>
       <c r="AB34" s="51" ph="1"/>
       <c r="AC34" s="52"/>
-      <c r="AD34" s="51" ph="1"/>
+      <c r="AD34" s="51" t="s" ph="1">
+        <v>272</v>
+      </c>
       <c r="AE34" s="52"/>
-      <c r="AF34" s="51" ph="1"/>
-      <c r="AG34" s="52"/>
-      <c r="AH34" s="51" t="s" ph="1">
-        <v>272</v>
-      </c>
-      <c r="AI34" s="52"/>
-    </row>
-    <row r="35" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="63"/>
+      <c r="AF34" ph="1"/>
+      <c r="AH34" ph="1"/>
+    </row>
+    <row r="35" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="56"/>
       <c r="B35" s="39"/>
       <c r="C35" s="40"/>
       <c r="D35" s="39"/>
@@ -4166,12 +4053,12 @@
       <c r="M35" s="40"/>
       <c r="N35" s="39"/>
       <c r="O35" s="40"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="40"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="8"/>
       <c r="R35" s="39"/>
       <c r="S35" s="40"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="8"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="40"/>
       <c r="V35" s="39"/>
       <c r="W35" s="40"/>
       <c r="X35" s="39"/>
@@ -4180,19 +4067,15 @@
       <c r="AA35" s="40"/>
       <c r="AB35" s="39"/>
       <c r="AC35" s="40"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="40"/>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="40"/>
-      <c r="AH35" s="39">
+      <c r="AD35" s="39">
         <v>2</v>
       </c>
-      <c r="AI35" s="40">
+      <c r="AE35" s="40">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="63">
+    <row r="36" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A36" s="56">
         <v>15</v>
       </c>
       <c r="B36" s="51" ph="1"/>
@@ -4209,12 +4092,12 @@
       <c r="M36" s="52"/>
       <c r="N36" s="51" ph="1"/>
       <c r="O36" s="52"/>
-      <c r="P36" s="51" ph="1"/>
-      <c r="Q36" s="52"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="8"/>
       <c r="R36" s="51" ph="1"/>
       <c r="S36" s="52"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="8"/>
+      <c r="T36" s="51" ph="1"/>
+      <c r="U36" s="52"/>
       <c r="V36" s="51" ph="1"/>
       <c r="W36" s="52"/>
       <c r="X36" s="51" ph="1"/>
@@ -4223,17 +4106,15 @@
       <c r="AA36" s="52"/>
       <c r="AB36" s="51" ph="1"/>
       <c r="AC36" s="52"/>
-      <c r="AD36" s="51" ph="1"/>
+      <c r="AD36" s="51" t="s" ph="1">
+        <v>271</v>
+      </c>
       <c r="AE36" s="52"/>
-      <c r="AF36" s="51" ph="1"/>
-      <c r="AG36" s="52"/>
-      <c r="AH36" s="51" t="s" ph="1">
-        <v>271</v>
-      </c>
-      <c r="AI36" s="52"/>
-    </row>
-    <row r="37" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="63"/>
+      <c r="AF36" ph="1"/>
+      <c r="AH36" ph="1"/>
+    </row>
+    <row r="37" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="56"/>
       <c r="B37" s="39"/>
       <c r="C37" s="40"/>
       <c r="D37" s="39"/>
@@ -4248,12 +4129,12 @@
       <c r="M37" s="40"/>
       <c r="N37" s="39"/>
       <c r="O37" s="40"/>
-      <c r="P37" s="39"/>
-      <c r="Q37" s="40"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="8"/>
       <c r="R37" s="39"/>
       <c r="S37" s="40"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="8"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="40"/>
       <c r="V37" s="39"/>
       <c r="W37" s="40"/>
       <c r="X37" s="39"/>
@@ -4262,19 +4143,15 @@
       <c r="AA37" s="40"/>
       <c r="AB37" s="39"/>
       <c r="AC37" s="40"/>
-      <c r="AD37" s="39"/>
-      <c r="AE37" s="40"/>
-      <c r="AF37" s="39"/>
-      <c r="AG37" s="40"/>
-      <c r="AH37" s="39">
+      <c r="AD37" s="39">
         <v>16</v>
       </c>
-      <c r="AI37" s="40">
+      <c r="AE37" s="40">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="63">
+    <row r="38" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A38" s="56">
         <v>16</v>
       </c>
       <c r="B38" s="51" ph="1"/>
@@ -4291,12 +4168,12 @@
       <c r="M38" s="52"/>
       <c r="N38" s="51" ph="1"/>
       <c r="O38" s="52"/>
-      <c r="P38" s="51" ph="1"/>
-      <c r="Q38" s="52"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="8"/>
       <c r="R38" s="51" ph="1"/>
       <c r="S38" s="52"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="8"/>
+      <c r="T38" s="51" ph="1"/>
+      <c r="U38" s="52"/>
       <c r="V38" s="51" ph="1"/>
       <c r="W38" s="52"/>
       <c r="X38" s="51" ph="1"/>
@@ -4305,17 +4182,15 @@
       <c r="AA38" s="52"/>
       <c r="AB38" s="51" ph="1"/>
       <c r="AC38" s="52"/>
-      <c r="AD38" s="51" ph="1"/>
+      <c r="AD38" s="51" t="s" ph="1">
+        <v>270</v>
+      </c>
       <c r="AE38" s="52"/>
-      <c r="AF38" s="51" ph="1"/>
-      <c r="AG38" s="52"/>
-      <c r="AH38" s="51" t="s" ph="1">
-        <v>270</v>
-      </c>
-      <c r="AI38" s="52"/>
-    </row>
-    <row r="39" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="63"/>
+      <c r="AF38" ph="1"/>
+      <c r="AH38" ph="1"/>
+    </row>
+    <row r="39" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="56"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40"/>
       <c r="D39" s="39"/>
@@ -4330,12 +4205,12 @@
       <c r="M39" s="40"/>
       <c r="N39" s="39"/>
       <c r="O39" s="40"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="40"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="8"/>
       <c r="R39" s="39"/>
       <c r="S39" s="40"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="8"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="40"/>
       <c r="V39" s="39"/>
       <c r="W39" s="40"/>
       <c r="X39" s="39"/>
@@ -4344,19 +4219,15 @@
       <c r="AA39" s="40"/>
       <c r="AB39" s="39"/>
       <c r="AC39" s="40"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="40"/>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="40"/>
-      <c r="AH39" s="39">
+      <c r="AD39" s="39">
         <v>3</v>
       </c>
-      <c r="AI39" s="40">
+      <c r="AE39" s="40">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="63">
+    <row r="40" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A40" s="56">
         <v>17</v>
       </c>
       <c r="B40" s="51" ph="1"/>
@@ -4373,33 +4244,31 @@
       <c r="M40" s="52"/>
       <c r="N40" s="51" ph="1"/>
       <c r="O40" s="52"/>
-      <c r="P40" s="51" ph="1"/>
-      <c r="Q40" s="52"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="8"/>
       <c r="R40" s="51" ph="1"/>
       <c r="S40" s="52"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="8"/>
+      <c r="T40" s="51" ph="1"/>
+      <c r="U40" s="52"/>
       <c r="V40" s="51" ph="1"/>
       <c r="W40" s="52"/>
       <c r="X40" s="51" ph="1"/>
       <c r="Y40" s="52"/>
       <c r="Z40" s="51" ph="1"/>
       <c r="AA40" s="52"/>
-      <c r="AB40" s="51" ph="1"/>
+      <c r="AB40" s="51" t="s" ph="1">
+        <v>269</v>
+      </c>
       <c r="AC40" s="52"/>
-      <c r="AD40" s="51" ph="1"/>
+      <c r="AD40" s="51" t="s" ph="1">
+        <v>268</v>
+      </c>
       <c r="AE40" s="52"/>
-      <c r="AF40" s="51" t="s" ph="1">
-        <v>269</v>
-      </c>
-      <c r="AG40" s="52"/>
-      <c r="AH40" s="51" t="s" ph="1">
-        <v>268</v>
-      </c>
-      <c r="AI40" s="52"/>
-    </row>
-    <row r="41" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="63"/>
+      <c r="AF40" ph="1"/>
+      <c r="AH40" ph="1"/>
+    </row>
+    <row r="41" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="56"/>
       <c r="B41" s="39"/>
       <c r="C41" s="40"/>
       <c r="D41" s="39"/>
@@ -4414,12 +4283,12 @@
       <c r="M41" s="40"/>
       <c r="N41" s="39"/>
       <c r="O41" s="40"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="40"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="8"/>
       <c r="R41" s="39"/>
       <c r="S41" s="40"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="8"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="40"/>
       <c r="V41" s="39"/>
       <c r="W41" s="40"/>
       <c r="X41" s="39"/>
@@ -4427,22 +4296,18 @@
       <c r="Z41" s="39"/>
       <c r="AA41" s="40"/>
       <c r="AB41" s="39"/>
-      <c r="AC41" s="40"/>
-      <c r="AD41" s="39"/>
-      <c r="AE41" s="40"/>
-      <c r="AF41" s="39"/>
-      <c r="AG41" s="40">
+      <c r="AC41" s="40">
         <v>21</v>
       </c>
-      <c r="AH41" s="39">
+      <c r="AD41" s="39">
         <v>2</v>
       </c>
-      <c r="AI41" s="40">
+      <c r="AE41" s="40">
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="63">
+    <row r="42" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A42" s="56">
         <v>18</v>
       </c>
       <c r="B42" s="51" ph="1"/>
@@ -4459,33 +4324,31 @@
       <c r="M42" s="52"/>
       <c r="N42" s="51" ph="1"/>
       <c r="O42" s="52"/>
-      <c r="P42" s="51" ph="1"/>
-      <c r="Q42" s="52"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="8"/>
       <c r="R42" s="51" ph="1"/>
       <c r="S42" s="52"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
+      <c r="T42" s="51" ph="1"/>
+      <c r="U42" s="52"/>
       <c r="V42" s="51" ph="1"/>
       <c r="W42" s="52"/>
       <c r="X42" s="51" ph="1"/>
       <c r="Y42" s="52"/>
       <c r="Z42" s="51" ph="1"/>
       <c r="AA42" s="52"/>
-      <c r="AB42" s="51" ph="1"/>
+      <c r="AB42" s="51" t="s" ph="1">
+        <v>267</v>
+      </c>
       <c r="AC42" s="52"/>
-      <c r="AD42" s="51" ph="1"/>
+      <c r="AD42" s="51" t="s" ph="1">
+        <v>266</v>
+      </c>
       <c r="AE42" s="52"/>
-      <c r="AF42" s="51" t="s" ph="1">
-        <v>267</v>
-      </c>
-      <c r="AG42" s="52"/>
-      <c r="AH42" s="51" t="s" ph="1">
-        <v>266</v>
-      </c>
-      <c r="AI42" s="52"/>
-    </row>
-    <row r="43" spans="1:35" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="63"/>
+      <c r="AF42" ph="1"/>
+      <c r="AH42" ph="1"/>
+    </row>
+    <row r="43" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="56"/>
       <c r="B43" s="39"/>
       <c r="C43" s="40"/>
       <c r="D43" s="39"/>
@@ -4500,12 +4363,12 @@
       <c r="M43" s="40"/>
       <c r="N43" s="39"/>
       <c r="O43" s="40"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="40"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="8"/>
       <c r="R43" s="39"/>
       <c r="S43" s="40"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="8"/>
+      <c r="T43" s="39"/>
+      <c r="U43" s="40"/>
       <c r="V43" s="39"/>
       <c r="W43" s="40"/>
       <c r="X43" s="39"/>
@@ -4513,21 +4376,17 @@
       <c r="Z43" s="39"/>
       <c r="AA43" s="40"/>
       <c r="AB43" s="39"/>
-      <c r="AC43" s="40"/>
-      <c r="AD43" s="39"/>
-      <c r="AE43" s="40"/>
-      <c r="AF43" s="39"/>
-      <c r="AG43" s="40">
+      <c r="AC43" s="40">
         <v>22</v>
       </c>
-      <c r="AH43" s="39">
+      <c r="AD43" s="39">
         <v>12</v>
       </c>
-      <c r="AI43" s="40">
+      <c r="AE43" s="40">
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="43">
         <v>1</v>
       </c>
@@ -4556,46 +4415,38 @@
         <v>7</v>
       </c>
       <c r="O44" s="44"/>
-      <c r="P44" s="45">
-        <v>8</v>
-      </c>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="45">
-        <v>9</v>
-      </c>
-      <c r="S44" s="46"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="33"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="31">
+        <v>7</v>
+      </c>
+      <c r="S44" s="32"/>
+      <c r="T44" s="31">
+        <v>6</v>
+      </c>
+      <c r="U44" s="30"/>
       <c r="V44" s="31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W44" s="32"/>
       <c r="X44" s="31">
-        <v>6</v>
-      </c>
-      <c r="Y44" s="30"/>
+        <v>4</v>
+      </c>
+      <c r="Y44" s="32"/>
       <c r="Z44" s="31">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="32"/>
+        <v>3</v>
+      </c>
+      <c r="AA44" s="30"/>
       <c r="AB44" s="31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC44" s="32"/>
       <c r="AD44" s="31">
-        <v>3</v>
-      </c>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="31">
-        <v>2</v>
-      </c>
-      <c r="AG44" s="32"/>
-      <c r="AH44" s="31">
         <v>1</v>
       </c>
-      <c r="AI44" s="32"/>
-    </row>
-    <row r="45" spans="1:35" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AE44" s="32"/>
+    </row>
+    <row r="45" spans="1:34" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -4610,30 +4461,53 @@
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
       <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="58"/>
-      <c r="X45" s="58"/>
-      <c r="Y45" s="58"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="10"/>
-      <c r="AB45" s="11"/>
-      <c r="AC45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="60"/>
+      <c r="T45" s="60"/>
+      <c r="U45" s="60"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
-      <c r="AE45" s="9"/>
-      <c r="AF45" s="9"/>
-      <c r="AG45" s="9"/>
-      <c r="AH45" s="9"/>
-      <c r="AI45" s="12"/>
-    </row>
-    <row r="46" spans="1:35" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="AE45" s="12"/>
+    </row>
+    <row r="46" spans="1:34" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="35">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="S45:U45"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A42:A43"/>
@@ -4642,35 +4516,6 @@
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4680,7 +4525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -4712,13 +4557,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -4749,156 +4594,156 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="61">
+      <c r="B5" s="62">
         <v>1</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="61">
+      <c r="C5" s="63"/>
+      <c r="D5" s="62">
         <v>2</v>
       </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="61">
+      <c r="E5" s="63"/>
+      <c r="F5" s="62">
         <v>3</v>
       </c>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61">
+      <c r="G5" s="63"/>
+      <c r="H5" s="62">
         <v>4</v>
       </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="61">
+      <c r="I5" s="63"/>
+      <c r="J5" s="62">
         <v>5</v>
       </c>
-      <c r="K5" s="62"/>
-      <c r="L5" s="61">
+      <c r="K5" s="63"/>
+      <c r="L5" s="62">
         <v>6</v>
       </c>
-      <c r="M5" s="62"/>
-      <c r="N5" s="61">
+      <c r="M5" s="63"/>
+      <c r="N5" s="62">
         <v>7</v>
       </c>
-      <c r="O5" s="62"/>
-      <c r="P5" s="61">
+      <c r="O5" s="63"/>
+      <c r="P5" s="62">
         <v>8</v>
       </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="61">
+      <c r="Q5" s="63"/>
+      <c r="R5" s="62">
         <v>9</v>
       </c>
-      <c r="S5" s="62"/>
+      <c r="S5" s="63"/>
       <c r="T5" s="34"/>
       <c r="U5" s="32"/>
-      <c r="V5" s="61">
+      <c r="V5" s="62">
         <v>9</v>
       </c>
-      <c r="W5" s="62"/>
-      <c r="X5" s="61">
+      <c r="W5" s="63"/>
+      <c r="X5" s="62">
         <v>8</v>
       </c>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="61">
+      <c r="Y5" s="63"/>
+      <c r="Z5" s="62">
         <v>7</v>
       </c>
-      <c r="AA5" s="62"/>
-      <c r="AB5" s="61">
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="62">
         <v>6</v>
       </c>
-      <c r="AC5" s="62"/>
-      <c r="AD5" s="61">
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="62">
         <v>5</v>
       </c>
-      <c r="AE5" s="62"/>
-      <c r="AF5" s="61">
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="62">
         <v>4</v>
       </c>
-      <c r="AG5" s="62"/>
-      <c r="AH5" s="61">
+      <c r="AG5" s="63"/>
+      <c r="AH5" s="62">
         <v>3</v>
       </c>
-      <c r="AI5" s="62"/>
-      <c r="AJ5" s="61">
+      <c r="AI5" s="63"/>
+      <c r="AJ5" s="62">
         <v>2</v>
       </c>
-      <c r="AK5" s="62"/>
-      <c r="AL5" s="61">
+      <c r="AK5" s="63"/>
+      <c r="AL5" s="62">
         <v>1</v>
       </c>
-      <c r="AM5" s="62"/>
+      <c r="AM5" s="63"/>
     </row>
     <row r="6" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="57"/>
+      <c r="AM6" s="59"/>
     </row>
     <row r="7" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -5013,7 +4858,7 @@
       </c>
     </row>
     <row r="8" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="63">
+      <c r="A8" s="56">
         <v>1</v>
       </c>
       <c r="B8" s="51" t="s" ph="1">
@@ -5062,7 +4907,7 @@
       <c r="AM8" s="52"/>
     </row>
     <row r="9" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="63"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="39">
         <v>10</v>
       </c>
@@ -5113,7 +4958,7 @@
       <c r="AM9" s="40"/>
     </row>
     <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="63">
+      <c r="A10" s="56">
         <v>2</v>
       </c>
       <c r="B10" s="51" t="s" ph="1">
@@ -5160,7 +5005,7 @@
       <c r="AM10" s="52"/>
     </row>
     <row r="11" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="39">
         <v>4</v>
       </c>
@@ -5207,7 +5052,7 @@
       <c r="AM11" s="40"/>
     </row>
     <row r="12" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="63">
+      <c r="A12" s="56">
         <v>3</v>
       </c>
       <c r="B12" s="51" t="s" ph="1">
@@ -5256,7 +5101,7 @@
       <c r="AM12" s="52"/>
     </row>
     <row r="13" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="39">
         <v>10</v>
       </c>
@@ -5305,7 +5150,7 @@
       <c r="AM13" s="40"/>
     </row>
     <row r="14" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="63">
+      <c r="A14" s="56">
         <v>4</v>
       </c>
       <c r="B14" s="51" t="s" ph="1">
@@ -5354,7 +5199,7 @@
       <c r="AM14" s="52"/>
     </row>
     <row r="15" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="39">
         <v>2</v>
       </c>
@@ -5405,7 +5250,7 @@
       </c>
     </row>
     <row r="16" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="63">
+      <c r="A16" s="56">
         <v>5</v>
       </c>
       <c r="B16" s="51" t="s" ph="1">
@@ -5452,7 +5297,7 @@
       <c r="AM16" s="52"/>
     </row>
     <row r="17" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="63"/>
+      <c r="A17" s="56"/>
       <c r="B17" s="39">
         <v>8</v>
       </c>
@@ -5499,7 +5344,7 @@
       </c>
     </row>
     <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="63">
+      <c r="A18" s="56">
         <v>6</v>
       </c>
       <c r="B18" s="51" t="s" ph="1">
@@ -5546,7 +5391,7 @@
       <c r="AM18" s="52"/>
     </row>
     <row r="19" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
+      <c r="A19" s="56"/>
       <c r="B19" s="39">
         <v>6</v>
       </c>
@@ -5593,7 +5438,7 @@
       </c>
     </row>
     <row r="20" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="63">
+      <c r="A20" s="56">
         <v>7</v>
       </c>
       <c r="B20" s="51" ph="1"/>
@@ -5638,7 +5483,7 @@
       <c r="AM20" s="52"/>
     </row>
     <row r="21" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="39"/>
@@ -5681,7 +5526,7 @@
       <c r="AM21" s="40"/>
     </row>
     <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="63">
+      <c r="A22" s="56">
         <v>8</v>
       </c>
       <c r="B22" s="51" ph="1"/>
@@ -5724,7 +5569,7 @@
       <c r="AM22" s="52"/>
     </row>
     <row r="23" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="63"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
       <c r="D23" s="39"/>
@@ -5765,7 +5610,7 @@
       <c r="AM23" s="40"/>
     </row>
     <row r="24" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="63">
+      <c r="A24" s="56">
         <v>9</v>
       </c>
       <c r="B24" s="51" ph="1"/>
@@ -5808,7 +5653,7 @@
       <c r="AM24" s="52"/>
     </row>
     <row r="25" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="63"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
       <c r="D25" s="39"/>
@@ -5849,7 +5694,7 @@
       <c r="AM25" s="40"/>
     </row>
     <row r="26" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="63">
+      <c r="A26" s="56">
         <v>10</v>
       </c>
       <c r="B26" s="51" ph="1"/>
@@ -5892,7 +5737,7 @@
       <c r="AM26" s="52"/>
     </row>
     <row r="27" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="63"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="39"/>
@@ -5933,7 +5778,7 @@
       <c r="AM27" s="40"/>
     </row>
     <row r="28" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="63">
+      <c r="A28" s="56">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -5976,7 +5821,7 @@
       <c r="AM28" s="52"/>
     </row>
     <row r="29" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="63"/>
+      <c r="A29" s="56"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -6017,7 +5862,7 @@
       <c r="AM29" s="40"/>
     </row>
     <row r="30" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="63">
+      <c r="A30" s="56">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -6060,7 +5905,7 @@
       <c r="AM30" s="52"/>
     </row>
     <row r="31" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="63"/>
+      <c r="A31" s="56"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -6101,7 +5946,7 @@
       <c r="AM31" s="40"/>
     </row>
     <row r="32" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="63">
+      <c r="A32" s="56">
         <v>13</v>
       </c>
       <c r="B32" s="51" t="s" ph="1">
@@ -6148,7 +5993,7 @@
       <c r="AM32" s="52"/>
     </row>
     <row r="33" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="63"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="39">
         <v>5</v>
       </c>
@@ -6195,7 +6040,7 @@
       <c r="AM33" s="40"/>
     </row>
     <row r="34" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="63">
+      <c r="A34" s="56">
         <v>14</v>
       </c>
       <c r="B34" s="51" t="s" ph="1">
@@ -6242,7 +6087,7 @@
       <c r="AM34" s="52"/>
     </row>
     <row r="35" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="63"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="39">
         <v>15</v>
       </c>
@@ -6291,7 +6136,7 @@
       </c>
     </row>
     <row r="36" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="63">
+      <c r="A36" s="56">
         <v>15</v>
       </c>
       <c r="B36" s="51" t="s" ph="1">
@@ -6340,7 +6185,7 @@
       <c r="AM36" s="52"/>
     </row>
     <row r="37" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="63"/>
+      <c r="A37" s="56"/>
       <c r="B37" s="39">
         <v>6</v>
       </c>
@@ -6391,7 +6236,7 @@
       </c>
     </row>
     <row r="38" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="63">
+      <c r="A38" s="56">
         <v>16</v>
       </c>
       <c r="B38" s="51" t="s" ph="1">
@@ -6438,7 +6283,7 @@
       <c r="AM38" s="52"/>
     </row>
     <row r="39" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="63"/>
+      <c r="A39" s="56"/>
       <c r="B39" s="39">
         <v>20</v>
       </c>
@@ -6483,7 +6328,7 @@
       <c r="AM39" s="40"/>
     </row>
     <row r="40" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="63">
+      <c r="A40" s="56">
         <v>17</v>
       </c>
       <c r="B40" s="51" t="s" ph="1">
@@ -6528,7 +6373,7 @@
       <c r="AM40" s="52"/>
     </row>
     <row r="41" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="63"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="39">
         <v>17</v>
       </c>
@@ -6571,7 +6416,7 @@
       <c r="AM41" s="40"/>
     </row>
     <row r="42" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="63">
+      <c r="A42" s="56">
         <v>18</v>
       </c>
       <c r="B42" s="51" t="s" ph="1">
@@ -6618,7 +6463,7 @@
       <c r="AM42" s="52"/>
     </row>
     <row r="43" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="63"/>
+      <c r="A43" s="56"/>
       <c r="B43" s="39">
         <v>3</v>
       </c>
@@ -6766,9 +6611,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
+      <c r="AA45" s="60"/>
+      <c r="AB45" s="60"/>
+      <c r="AC45" s="60"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -6783,34 +6628,19 @@
     <row r="46" spans="1:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="AH5:AI5"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="AL5:AM5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="V5:W5"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A42:A43"/>
@@ -6827,19 +6657,34 @@
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="AH5:AI5"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="AL5:AM5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6849,7 +6694,2058 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A3:AL46"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.125" customWidth="1"/>
+    <col min="2" max="35" width="32.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:38" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" spans="1:38" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="1"/>
+      <c r="C4" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="57">
+        <f ca="1">(TODAY())</f>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="4"/>
+    </row>
+    <row r="5" spans="1:38" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="25">
+        <v>1</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31">
+        <v>2</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="31">
+        <v>3</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="31">
+        <v>4</v>
+      </c>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31">
+        <v>5</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="31">
+        <v>6</v>
+      </c>
+      <c r="M5" s="32"/>
+      <c r="N5" s="31">
+        <v>7</v>
+      </c>
+      <c r="O5" s="30"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="31">
+        <v>9</v>
+      </c>
+      <c r="S5" s="32"/>
+      <c r="T5" s="31">
+        <v>8</v>
+      </c>
+      <c r="U5" s="32"/>
+      <c r="V5" s="31">
+        <v>7</v>
+      </c>
+      <c r="W5" s="32"/>
+      <c r="X5" s="31">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="31">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="31">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="31">
+        <v>2</v>
+      </c>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="31">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="32"/>
+    </row>
+    <row r="6" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="O6" s="59"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="S6" s="59"/>
+      <c r="T6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="U6" s="59"/>
+      <c r="V6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI6" s="59"/>
+    </row>
+    <row r="7" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="S7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="V7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="W7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="X7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG7" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH7" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI7" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A8" s="56">
+        <v>1</v>
+      </c>
+      <c r="B8" s="51" t="s" ph="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="51" t="s" ph="1">
+        <v>320</v>
+      </c>
+      <c r="E8" s="52"/>
+      <c r="F8" s="51" t="s" ph="1">
+        <v>321</v>
+      </c>
+      <c r="G8" s="52"/>
+      <c r="H8" s="51" t="s" ph="1">
+        <v>322</v>
+      </c>
+      <c r="I8" s="52"/>
+      <c r="J8" s="51" ph="1"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="51" ph="1"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="51" ph="1"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="51" ph="1"/>
+      <c r="S8" s="52"/>
+      <c r="T8" s="51" ph="1"/>
+      <c r="U8" s="52"/>
+      <c r="V8" s="51" ph="1"/>
+      <c r="W8" s="52"/>
+      <c r="X8" s="51" ph="1"/>
+      <c r="Y8" s="52"/>
+      <c r="Z8" s="51" ph="1"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="51" ph="1"/>
+      <c r="AC8" s="52"/>
+      <c r="AD8" s="51" ph="1"/>
+      <c r="AE8" s="52"/>
+      <c r="AF8" s="51" ph="1"/>
+      <c r="AG8" s="52"/>
+      <c r="AH8" s="51" t="s" ph="1">
+        <v>313</v>
+      </c>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" ph="1"/>
+      <c r="AL8" ph="1"/>
+    </row>
+    <row r="9" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="56"/>
+      <c r="B9" s="39">
+        <v>10</v>
+      </c>
+      <c r="C9" s="40">
+        <v>18</v>
+      </c>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40">
+        <v>1</v>
+      </c>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40">
+        <v>3</v>
+      </c>
+      <c r="H9" s="39">
+        <v>2</v>
+      </c>
+      <c r="I9" s="40">
+        <v>8</v>
+      </c>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="39">
+        <v>2</v>
+      </c>
+      <c r="AI9" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A10" s="56">
+        <v>2</v>
+      </c>
+      <c r="B10" s="51" t="s" ph="1">
+        <v>323</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="51" t="s" ph="1">
+        <v>324</v>
+      </c>
+      <c r="E10" s="52"/>
+      <c r="F10" s="51" ph="1"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="51" ph="1"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="51" ph="1"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="51" ph="1"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="51" ph="1"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="51" ph="1"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="51" ph="1"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="51" ph="1"/>
+      <c r="W10" s="52"/>
+      <c r="X10" s="51" ph="1"/>
+      <c r="Y10" s="52"/>
+      <c r="Z10" s="51" ph="1"/>
+      <c r="AA10" s="52"/>
+      <c r="AB10" s="51" ph="1"/>
+      <c r="AC10" s="52"/>
+      <c r="AD10" s="51" ph="1"/>
+      <c r="AE10" s="52"/>
+      <c r="AF10" s="51" ph="1"/>
+      <c r="AG10" s="52"/>
+      <c r="AH10" s="51" t="s" ph="1">
+        <v>314</v>
+      </c>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" ph="1"/>
+      <c r="AL10" ph="1"/>
+    </row>
+    <row r="11" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="56"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40">
+        <v>18</v>
+      </c>
+      <c r="D11" s="39"/>
+      <c r="E11" s="40">
+        <v>11</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="39"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="39">
+        <v>18</v>
+      </c>
+      <c r="AI11" s="40"/>
+    </row>
+    <row r="12" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A12" s="56">
+        <v>3</v>
+      </c>
+      <c r="B12" s="51" t="s" ph="1">
+        <v>325</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="51" t="s" ph="1">
+        <v>326</v>
+      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="51" ph="1"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="51" ph="1"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="51" ph="1"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="51" ph="1"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="51" ph="1"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="51" ph="1"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="51" ph="1"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="51" ph="1"/>
+      <c r="W12" s="52"/>
+      <c r="X12" s="51" ph="1"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="51" ph="1"/>
+      <c r="AA12" s="52"/>
+      <c r="AB12" s="51" ph="1"/>
+      <c r="AC12" s="52"/>
+      <c r="AD12" s="51" ph="1"/>
+      <c r="AE12" s="52"/>
+      <c r="AF12" s="51" ph="1"/>
+      <c r="AG12" s="52"/>
+      <c r="AH12" s="51" t="s" ph="1">
+        <v>314</v>
+      </c>
+      <c r="AI12" s="52"/>
+      <c r="AJ12" ph="1"/>
+      <c r="AL12" ph="1"/>
+    </row>
+    <row r="13" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="56"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40">
+        <v>8</v>
+      </c>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40">
+        <v>5</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="39"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="39">
+        <v>20</v>
+      </c>
+      <c r="AI13" s="40"/>
+    </row>
+    <row r="14" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A14" s="56">
+        <v>4</v>
+      </c>
+      <c r="B14" s="51" ph="1"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="51" ph="1"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="51" ph="1"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="51" ph="1"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="51" ph="1"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="51" ph="1"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="51" ph="1"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="51" ph="1"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="51" ph="1"/>
+      <c r="U14" s="52"/>
+      <c r="V14" s="51" ph="1"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="51" ph="1"/>
+      <c r="Y14" s="52"/>
+      <c r="Z14" s="51" ph="1"/>
+      <c r="AA14" s="52"/>
+      <c r="AB14" s="51" ph="1"/>
+      <c r="AC14" s="52"/>
+      <c r="AD14" s="51" ph="1"/>
+      <c r="AE14" s="52"/>
+      <c r="AF14" s="51" ph="1"/>
+      <c r="AG14" s="52"/>
+      <c r="AH14" s="51" t="s" ph="1">
+        <v>315</v>
+      </c>
+      <c r="AI14" s="52"/>
+      <c r="AJ14" ph="1"/>
+      <c r="AL14" ph="1"/>
+    </row>
+    <row r="15" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="56"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="39">
+        <v>6</v>
+      </c>
+      <c r="AI15" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A16" s="56">
+        <v>5</v>
+      </c>
+      <c r="B16" s="51" t="s" ph="1">
+        <v>327</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="51" t="s" ph="1">
+        <v>328</v>
+      </c>
+      <c r="E16" s="52"/>
+      <c r="F16" s="51" t="s" ph="1">
+        <v>329</v>
+      </c>
+      <c r="G16" s="52"/>
+      <c r="H16" s="51" ph="1"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="51" ph="1"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="51" ph="1"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="51" ph="1"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="51" ph="1"/>
+      <c r="S16" s="52"/>
+      <c r="T16" s="51" ph="1"/>
+      <c r="U16" s="52"/>
+      <c r="V16" s="51" ph="1"/>
+      <c r="W16" s="52"/>
+      <c r="X16" s="51" ph="1"/>
+      <c r="Y16" s="52"/>
+      <c r="Z16" s="51" ph="1"/>
+      <c r="AA16" s="52"/>
+      <c r="AB16" s="51" ph="1"/>
+      <c r="AC16" s="52"/>
+      <c r="AD16" s="51" ph="1"/>
+      <c r="AE16" s="52"/>
+      <c r="AF16" s="51" ph="1"/>
+      <c r="AG16" s="52"/>
+      <c r="AH16" s="51" t="s" ph="1">
+        <v>316</v>
+      </c>
+      <c r="AI16" s="52"/>
+      <c r="AJ16" ph="1"/>
+      <c r="AL16" ph="1"/>
+    </row>
+    <row r="17" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="56"/>
+      <c r="B17" s="39">
+        <v>1</v>
+      </c>
+      <c r="C17" s="40">
+        <v>16</v>
+      </c>
+      <c r="D17" s="39">
+        <v>1</v>
+      </c>
+      <c r="E17" s="40">
+        <v>6</v>
+      </c>
+      <c r="F17" s="39">
+        <v>3</v>
+      </c>
+      <c r="G17" s="40">
+        <v>10</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="39"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="39"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="39">
+        <v>6</v>
+      </c>
+      <c r="AI17" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A18" s="56">
+        <v>6</v>
+      </c>
+      <c r="B18" s="51" t="s" ph="1">
+        <v>330</v>
+      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="51" ph="1"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="51" ph="1"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="51" ph="1"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="51" ph="1"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="51" ph="1"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="51" ph="1"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="51" ph="1"/>
+      <c r="S18" s="52"/>
+      <c r="T18" s="51" ph="1"/>
+      <c r="U18" s="52"/>
+      <c r="V18" s="51" ph="1"/>
+      <c r="W18" s="52"/>
+      <c r="X18" s="51" ph="1"/>
+      <c r="Y18" s="52"/>
+      <c r="Z18" s="51" ph="1"/>
+      <c r="AA18" s="52"/>
+      <c r="AB18" s="51" ph="1"/>
+      <c r="AC18" s="52"/>
+      <c r="AD18" s="51" ph="1"/>
+      <c r="AE18" s="52"/>
+      <c r="AF18" s="51" ph="1"/>
+      <c r="AG18" s="52"/>
+      <c r="AH18" s="51" t="s" ph="1">
+        <v>317</v>
+      </c>
+      <c r="AI18" s="52"/>
+      <c r="AJ18" ph="1"/>
+      <c r="AL18" ph="1"/>
+    </row>
+    <row r="19" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="56"/>
+      <c r="B19" s="39">
+        <v>3</v>
+      </c>
+      <c r="C19" s="40">
+        <v>13</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="39"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="40"/>
+      <c r="AH19" s="39">
+        <v>5</v>
+      </c>
+      <c r="AI19" s="40">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A20" s="56">
+        <v>7</v>
+      </c>
+      <c r="B20" s="51" t="s" ph="1">
+        <v>278</v>
+      </c>
+      <c r="C20" s="52"/>
+      <c r="D20" s="51" t="s" ph="1">
+        <v>331</v>
+      </c>
+      <c r="E20" s="52"/>
+      <c r="F20" s="51" ph="1"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="51" ph="1"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="51" ph="1"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="51" ph="1"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="51" ph="1"/>
+      <c r="O20" s="52"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="51" ph="1"/>
+      <c r="S20" s="52"/>
+      <c r="T20" s="51" ph="1"/>
+      <c r="U20" s="52"/>
+      <c r="V20" s="51" ph="1"/>
+      <c r="W20" s="52"/>
+      <c r="X20" s="51" ph="1"/>
+      <c r="Y20" s="52"/>
+      <c r="Z20" s="51" ph="1"/>
+      <c r="AA20" s="52"/>
+      <c r="AB20" s="51" ph="1"/>
+      <c r="AC20" s="52"/>
+      <c r="AD20" s="51" ph="1"/>
+      <c r="AE20" s="52"/>
+      <c r="AF20" s="51" ph="1"/>
+      <c r="AG20" s="52"/>
+      <c r="AH20" s="51" t="s" ph="1">
+        <v>314</v>
+      </c>
+      <c r="AI20" s="52"/>
+      <c r="AJ20" ph="1"/>
+      <c r="AL20" ph="1"/>
+    </row>
+    <row r="21" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="56"/>
+      <c r="B21" s="39">
+        <v>3</v>
+      </c>
+      <c r="C21" s="40">
+        <v>9</v>
+      </c>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40">
+        <v>1</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="39"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="39"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="39"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="39"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="39">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A22" s="56">
+        <v>8</v>
+      </c>
+      <c r="B22" s="51" t="s" ph="1">
+        <v>332</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="51" ph="1"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="51" ph="1"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="51" ph="1"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="51" ph="1"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="51" ph="1"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="51" ph="1"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="51" ph="1"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="51" ph="1"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="51" ph="1"/>
+      <c r="W22" s="52"/>
+      <c r="X22" s="51" ph="1"/>
+      <c r="Y22" s="52"/>
+      <c r="Z22" s="51" ph="1"/>
+      <c r="AA22" s="52"/>
+      <c r="AB22" s="51" ph="1"/>
+      <c r="AC22" s="52"/>
+      <c r="AD22" s="51" ph="1"/>
+      <c r="AE22" s="52"/>
+      <c r="AF22" s="51" ph="1"/>
+      <c r="AG22" s="52"/>
+      <c r="AH22" s="51" t="s" ph="1">
+        <v>318</v>
+      </c>
+      <c r="AI22" s="52"/>
+      <c r="AJ22" ph="1"/>
+      <c r="AL22" ph="1"/>
+    </row>
+    <row r="23" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="56"/>
+      <c r="B23" s="39">
+        <v>2</v>
+      </c>
+      <c r="C23" s="40">
+        <v>10</v>
+      </c>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="40"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="40"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="40"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="40"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="40"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="40"/>
+      <c r="AH23" s="39">
+        <v>4</v>
+      </c>
+      <c r="AI23" s="40"/>
+    </row>
+    <row r="24" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A24" s="56">
+        <v>9</v>
+      </c>
+      <c r="B24" s="51" t="s" ph="1">
+        <v>333</v>
+      </c>
+      <c r="C24" s="52"/>
+      <c r="D24" s="51" ph="1"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="51" ph="1"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="51" ph="1"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="51" ph="1"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="51" ph="1"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="51" ph="1"/>
+      <c r="O24" s="52"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="51" ph="1"/>
+      <c r="S24" s="52"/>
+      <c r="T24" s="51" ph="1"/>
+      <c r="U24" s="52"/>
+      <c r="V24" s="51" ph="1"/>
+      <c r="W24" s="52"/>
+      <c r="X24" s="51" ph="1"/>
+      <c r="Y24" s="52"/>
+      <c r="Z24" s="51" ph="1"/>
+      <c r="AA24" s="52"/>
+      <c r="AB24" s="51" ph="1"/>
+      <c r="AC24" s="52"/>
+      <c r="AD24" s="51" ph="1"/>
+      <c r="AE24" s="52"/>
+      <c r="AF24" s="51" ph="1"/>
+      <c r="AG24" s="52"/>
+      <c r="AH24" s="51" ph="1"/>
+      <c r="AI24" s="52"/>
+      <c r="AJ24" ph="1"/>
+      <c r="AL24" ph="1"/>
+    </row>
+    <row r="25" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="56"/>
+      <c r="B25" s="39">
+        <v>8</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="39"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="40"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="40"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="40"/>
+      <c r="AF25" s="39"/>
+      <c r="AG25" s="40"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="40"/>
+    </row>
+    <row r="26" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A26" s="56">
+        <v>10</v>
+      </c>
+      <c r="B26" s="51" t="s" ph="1">
+        <v>334</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="51" ph="1"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="51" ph="1"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="51" ph="1"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="51" ph="1"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="51" ph="1"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="51" ph="1"/>
+      <c r="O26" s="52"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="51" ph="1"/>
+      <c r="S26" s="52"/>
+      <c r="T26" s="51" ph="1"/>
+      <c r="U26" s="52"/>
+      <c r="V26" s="51" ph="1"/>
+      <c r="W26" s="52"/>
+      <c r="X26" s="51" ph="1"/>
+      <c r="Y26" s="52"/>
+      <c r="Z26" s="51" ph="1"/>
+      <c r="AA26" s="52"/>
+      <c r="AB26" s="51" ph="1"/>
+      <c r="AC26" s="52"/>
+      <c r="AD26" s="51" ph="1"/>
+      <c r="AE26" s="52"/>
+      <c r="AF26" s="51" ph="1"/>
+      <c r="AG26" s="52"/>
+      <c r="AH26" s="51" t="s" ph="1">
+        <v>319</v>
+      </c>
+      <c r="AI26" s="52"/>
+      <c r="AJ26" ph="1"/>
+      <c r="AL26" ph="1"/>
+    </row>
+    <row r="27" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="56"/>
+      <c r="B27" s="39">
+        <v>5</v>
+      </c>
+      <c r="C27" s="40">
+        <v>6</v>
+      </c>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="39"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="40"/>
+      <c r="Z27" s="39"/>
+      <c r="AA27" s="40"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="40"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="40"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="40"/>
+    </row>
+    <row r="28" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A28" s="56">
+        <v>11</v>
+      </c>
+      <c r="B28" s="51" ph="1"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="51" ph="1"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51" ph="1"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="51" ph="1"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="51" ph="1"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="51" ph="1"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="51" ph="1"/>
+      <c r="O28" s="52"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="51" ph="1"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="51" ph="1"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="51" ph="1"/>
+      <c r="W28" s="52"/>
+      <c r="X28" s="51" ph="1"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="51" ph="1"/>
+      <c r="AA28" s="52"/>
+      <c r="AB28" s="51" ph="1"/>
+      <c r="AC28" s="52"/>
+      <c r="AD28" s="51" ph="1"/>
+      <c r="AE28" s="52"/>
+      <c r="AF28" s="51" ph="1"/>
+      <c r="AG28" s="52"/>
+      <c r="AH28" s="51" ph="1"/>
+      <c r="AI28" s="52"/>
+      <c r="AJ28" ph="1"/>
+      <c r="AL28" ph="1"/>
+    </row>
+    <row r="29" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="56"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="40"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="40"/>
+    </row>
+    <row r="30" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A30" s="56">
+        <v>12</v>
+      </c>
+      <c r="B30" s="51" ph="1"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="51" ph="1"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="51" ph="1"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="51" ph="1"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="51" ph="1"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="51" ph="1"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="51" ph="1"/>
+      <c r="O30" s="52"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="51" ph="1"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="51" ph="1"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="51" ph="1"/>
+      <c r="W30" s="52"/>
+      <c r="X30" s="51" ph="1"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="51" ph="1"/>
+      <c r="AA30" s="52"/>
+      <c r="AB30" s="51" ph="1"/>
+      <c r="AC30" s="52"/>
+      <c r="AD30" s="51" ph="1"/>
+      <c r="AE30" s="52"/>
+      <c r="AF30" s="51" ph="1"/>
+      <c r="AG30" s="52"/>
+      <c r="AH30" s="51" ph="1"/>
+      <c r="AI30" s="52"/>
+      <c r="AJ30" ph="1"/>
+      <c r="AL30" ph="1"/>
+    </row>
+    <row r="31" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="56"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="40"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="40"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="40"/>
+      <c r="AB31" s="39"/>
+      <c r="AC31" s="40"/>
+      <c r="AD31" s="39"/>
+      <c r="AE31" s="40"/>
+      <c r="AF31" s="39"/>
+      <c r="AG31" s="40"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="40"/>
+    </row>
+    <row r="32" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A32" s="56">
+        <v>13</v>
+      </c>
+      <c r="B32" s="51" ph="1"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="51" ph="1"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="51" ph="1"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="51" ph="1"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="51" ph="1"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="51" ph="1"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="51" ph="1"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="51" ph="1"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="51" ph="1"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="51" ph="1"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="51" ph="1"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="51" ph="1"/>
+      <c r="AA32" s="52"/>
+      <c r="AB32" s="51" ph="1"/>
+      <c r="AC32" s="52"/>
+      <c r="AD32" s="51" ph="1"/>
+      <c r="AE32" s="52"/>
+      <c r="AF32" s="51" ph="1"/>
+      <c r="AG32" s="52"/>
+      <c r="AH32" s="51" ph="1"/>
+      <c r="AI32" s="52"/>
+      <c r="AJ32" ph="1"/>
+      <c r="AL32" ph="1"/>
+    </row>
+    <row r="33" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="56"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="39"/>
+      <c r="S33" s="40"/>
+      <c r="T33" s="39"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="40"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="40"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="40"/>
+      <c r="AD33" s="39"/>
+      <c r="AE33" s="40"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="40"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="40"/>
+    </row>
+    <row r="34" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A34" s="56">
+        <v>14</v>
+      </c>
+      <c r="B34" s="51" t="s" ph="1">
+        <v>346</v>
+      </c>
+      <c r="C34" s="52"/>
+      <c r="D34" s="51" t="s" ph="1">
+        <v>347</v>
+      </c>
+      <c r="E34" s="52"/>
+      <c r="F34" s="51" t="s" ph="1">
+        <v>348</v>
+      </c>
+      <c r="G34" s="52"/>
+      <c r="H34" s="51" t="s" ph="1">
+        <v>349</v>
+      </c>
+      <c r="I34" s="52"/>
+      <c r="J34" s="51" ph="1"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="51" ph="1"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="51" ph="1"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="51" ph="1"/>
+      <c r="S34" s="52"/>
+      <c r="T34" s="51" ph="1"/>
+      <c r="U34" s="52"/>
+      <c r="V34" s="51" ph="1"/>
+      <c r="W34" s="52"/>
+      <c r="X34" s="51" ph="1"/>
+      <c r="Y34" s="52"/>
+      <c r="Z34" s="51" ph="1"/>
+      <c r="AA34" s="52"/>
+      <c r="AB34" s="51" ph="1"/>
+      <c r="AC34" s="52"/>
+      <c r="AD34" s="51" ph="1"/>
+      <c r="AE34" s="52"/>
+      <c r="AF34" s="51" ph="1"/>
+      <c r="AG34" s="52"/>
+      <c r="AH34" s="51" ph="1"/>
+      <c r="AI34" s="52"/>
+      <c r="AJ34" ph="1"/>
+      <c r="AL34" ph="1"/>
+    </row>
+    <row r="35" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="56"/>
+      <c r="B35" s="39">
+        <v>6</v>
+      </c>
+      <c r="C35" s="40">
+        <v>15</v>
+      </c>
+      <c r="D35" s="39">
+        <v>1</v>
+      </c>
+      <c r="E35" s="40"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="40">
+        <v>14</v>
+      </c>
+      <c r="H35" s="39"/>
+      <c r="I35" s="40">
+        <v>9</v>
+      </c>
+      <c r="J35" s="39"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="39"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="39"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="39"/>
+      <c r="Y35" s="40"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="40"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="40"/>
+      <c r="AD35" s="39"/>
+      <c r="AE35" s="40"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="40"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="40"/>
+    </row>
+    <row r="36" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A36" s="56">
+        <v>15</v>
+      </c>
+      <c r="B36" s="51" t="s" ph="1">
+        <v>343</v>
+      </c>
+      <c r="C36" s="52"/>
+      <c r="D36" s="51" t="s" ph="1">
+        <v>344</v>
+      </c>
+      <c r="E36" s="52"/>
+      <c r="F36" s="51" t="s" ph="1">
+        <v>345</v>
+      </c>
+      <c r="G36" s="52"/>
+      <c r="H36" s="51" ph="1"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="51" ph="1"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="51" ph="1"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="51" ph="1"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="51" ph="1"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="51" ph="1"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="51" ph="1"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="51" ph="1"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="51" ph="1"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="51" ph="1"/>
+      <c r="AC36" s="52"/>
+      <c r="AD36" s="51" ph="1"/>
+      <c r="AE36" s="52"/>
+      <c r="AF36" s="51" ph="1"/>
+      <c r="AG36" s="52"/>
+      <c r="AH36" s="51" ph="1"/>
+      <c r="AI36" s="52"/>
+      <c r="AJ36" ph="1"/>
+      <c r="AL36" ph="1"/>
+    </row>
+    <row r="37" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="56"/>
+      <c r="B37" s="39">
+        <v>3</v>
+      </c>
+      <c r="C37" s="40">
+        <v>12</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="E37" s="40">
+        <v>1</v>
+      </c>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40">
+        <v>1</v>
+      </c>
+      <c r="H37" s="39"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="39"/>
+      <c r="S37" s="40"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="40"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="40"/>
+      <c r="X37" s="39"/>
+      <c r="Y37" s="40"/>
+      <c r="Z37" s="39"/>
+      <c r="AA37" s="40"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="40"/>
+      <c r="AD37" s="39"/>
+      <c r="AE37" s="40"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="40"/>
+      <c r="AH37" s="39"/>
+      <c r="AI37" s="40"/>
+    </row>
+    <row r="38" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A38" s="56">
+        <v>16</v>
+      </c>
+      <c r="B38" s="51" t="s" ph="1">
+        <v>338</v>
+      </c>
+      <c r="C38" s="52"/>
+      <c r="D38" s="51" t="s" ph="1">
+        <v>339</v>
+      </c>
+      <c r="E38" s="52"/>
+      <c r="F38" s="51" t="s" ph="1">
+        <v>340</v>
+      </c>
+      <c r="G38" s="52"/>
+      <c r="H38" s="51" t="s" ph="1">
+        <v>341</v>
+      </c>
+      <c r="I38" s="52"/>
+      <c r="J38" s="51" ph="1"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="51" ph="1"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="51" ph="1"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="51" ph="1"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="51" ph="1"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="51" ph="1"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="51" ph="1"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="51" ph="1"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="51" ph="1"/>
+      <c r="AC38" s="52"/>
+      <c r="AD38" s="51" ph="1"/>
+      <c r="AE38" s="52"/>
+      <c r="AF38" s="51" ph="1"/>
+      <c r="AG38" s="52"/>
+      <c r="AH38" s="51" ph="1"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" ph="1"/>
+      <c r="AL38" ph="1"/>
+    </row>
+    <row r="39" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="56"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40">
+        <v>12</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40">
+        <v>2</v>
+      </c>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40">
+        <v>2</v>
+      </c>
+      <c r="H39" s="39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="40"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="39"/>
+      <c r="S39" s="40"/>
+      <c r="T39" s="39"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="39"/>
+      <c r="W39" s="40"/>
+      <c r="X39" s="39"/>
+      <c r="Y39" s="40"/>
+      <c r="Z39" s="39"/>
+      <c r="AA39" s="40"/>
+      <c r="AB39" s="39"/>
+      <c r="AC39" s="40"/>
+      <c r="AD39" s="39"/>
+      <c r="AE39" s="40"/>
+      <c r="AF39" s="39"/>
+      <c r="AG39" s="40"/>
+      <c r="AH39" s="39"/>
+      <c r="AI39" s="40"/>
+    </row>
+    <row r="40" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A40" s="56">
+        <v>17</v>
+      </c>
+      <c r="B40" s="51" t="s" ph="1">
+        <v>337</v>
+      </c>
+      <c r="C40" s="52"/>
+      <c r="D40" s="51" ph="1"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="51" ph="1"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="51" ph="1"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="51" ph="1"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="51" ph="1"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="51" ph="1"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="51" ph="1"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="51" ph="1"/>
+      <c r="U40" s="52"/>
+      <c r="V40" s="51" ph="1"/>
+      <c r="W40" s="52"/>
+      <c r="X40" s="51" ph="1"/>
+      <c r="Y40" s="52"/>
+      <c r="Z40" s="51" ph="1"/>
+      <c r="AA40" s="52"/>
+      <c r="AB40" s="51" ph="1"/>
+      <c r="AC40" s="52"/>
+      <c r="AD40" s="51" ph="1"/>
+      <c r="AE40" s="52"/>
+      <c r="AF40" s="51" ph="1"/>
+      <c r="AG40" s="52"/>
+      <c r="AH40" s="51" ph="1"/>
+      <c r="AI40" s="52"/>
+      <c r="AJ40" ph="1"/>
+      <c r="AL40" ph="1"/>
+    </row>
+    <row r="41" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="56"/>
+      <c r="B41" s="39">
+        <v>2</v>
+      </c>
+      <c r="C41" s="40">
+        <v>6</v>
+      </c>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="40"/>
+      <c r="T41" s="39"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="39"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="39"/>
+      <c r="Y41" s="40"/>
+      <c r="Z41" s="39"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="39"/>
+      <c r="AC41" s="40"/>
+      <c r="AD41" s="39"/>
+      <c r="AE41" s="40"/>
+      <c r="AF41" s="39"/>
+      <c r="AG41" s="40"/>
+      <c r="AH41" s="39"/>
+      <c r="AI41" s="40"/>
+    </row>
+    <row r="42" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A42" s="56">
+        <v>18</v>
+      </c>
+      <c r="B42" s="51" t="s" ph="1">
+        <v>335</v>
+      </c>
+      <c r="C42" s="52"/>
+      <c r="D42" s="51" t="s" ph="1">
+        <v>336</v>
+      </c>
+      <c r="E42" s="52"/>
+      <c r="F42" s="51" ph="1"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="51" ph="1"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="51" ph="1"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="51" ph="1"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="51" ph="1"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="51" ph="1"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="51" ph="1"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="51" ph="1"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="51" ph="1"/>
+      <c r="Y42" s="52"/>
+      <c r="Z42" s="51" ph="1"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="51" ph="1"/>
+      <c r="AC42" s="52"/>
+      <c r="AD42" s="51" ph="1"/>
+      <c r="AE42" s="52"/>
+      <c r="AF42" s="51" ph="1"/>
+      <c r="AG42" s="52"/>
+      <c r="AH42" s="51" ph="1"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" ph="1"/>
+      <c r="AL42" ph="1"/>
+    </row>
+    <row r="43" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="56"/>
+      <c r="B43" s="39">
+        <v>1</v>
+      </c>
+      <c r="C43" s="40">
+        <v>14</v>
+      </c>
+      <c r="D43" s="39"/>
+      <c r="E43" s="40">
+        <v>11</v>
+      </c>
+      <c r="F43" s="39"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="40"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="39"/>
+      <c r="S43" s="40"/>
+      <c r="T43" s="39"/>
+      <c r="U43" s="40"/>
+      <c r="V43" s="39"/>
+      <c r="W43" s="40"/>
+      <c r="X43" s="39"/>
+      <c r="Y43" s="40"/>
+      <c r="Z43" s="39"/>
+      <c r="AA43" s="40"/>
+      <c r="AB43" s="39"/>
+      <c r="AC43" s="40"/>
+      <c r="AD43" s="39"/>
+      <c r="AE43" s="40"/>
+      <c r="AF43" s="39"/>
+      <c r="AG43" s="40"/>
+      <c r="AH43" s="39"/>
+      <c r="AI43" s="40"/>
+    </row>
+    <row r="44" spans="1:38" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="34">
+        <v>1</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="31">
+        <v>2</v>
+      </c>
+      <c r="E44" s="32"/>
+      <c r="F44" s="31">
+        <v>3</v>
+      </c>
+      <c r="G44" s="32"/>
+      <c r="H44" s="31">
+        <v>4</v>
+      </c>
+      <c r="I44" s="30"/>
+      <c r="J44" s="31">
+        <v>5</v>
+      </c>
+      <c r="K44" s="32"/>
+      <c r="L44" s="31">
+        <v>6</v>
+      </c>
+      <c r="M44" s="32"/>
+      <c r="N44" s="31">
+        <v>7</v>
+      </c>
+      <c r="O44" s="30"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="31">
+        <v>9</v>
+      </c>
+      <c r="S44" s="32"/>
+      <c r="T44" s="31">
+        <v>8</v>
+      </c>
+      <c r="U44" s="32"/>
+      <c r="V44" s="31">
+        <v>7</v>
+      </c>
+      <c r="W44" s="32"/>
+      <c r="X44" s="31">
+        <v>6</v>
+      </c>
+      <c r="Y44" s="30"/>
+      <c r="Z44" s="31">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="32"/>
+      <c r="AB44" s="31">
+        <v>4</v>
+      </c>
+      <c r="AC44" s="32"/>
+      <c r="AD44" s="31">
+        <v>3</v>
+      </c>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="31">
+        <v>2</v>
+      </c>
+      <c r="AG44" s="32"/>
+      <c r="AH44" s="31">
+        <v>1</v>
+      </c>
+      <c r="AI44" s="32"/>
+    </row>
+    <row r="45" spans="1:38" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="16"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="60"/>
+      <c r="X45" s="60"/>
+      <c r="Y45" s="60"/>
+      <c r="Z45" s="11"/>
+      <c r="AA45" s="10"/>
+      <c r="AB45" s="11"/>
+      <c r="AC45" s="11"/>
+      <c r="AD45" s="9"/>
+      <c r="AE45" s="9"/>
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="9"/>
+      <c r="AH45" s="9"/>
+      <c r="AI45" s="12"/>
+    </row>
+    <row r="46" spans="1:38" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -6875,19 +8771,19 @@
     <row r="4" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1"/>
       <c r="C4" s="35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -6918,156 +8814,124 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="25">
-        <v>1</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31">
-        <v>2</v>
-      </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="31">
-        <v>3</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="31">
-        <v>4</v>
-      </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31">
-        <v>5</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="31">
-        <v>6</v>
-      </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="31">
-        <v>7</v>
-      </c>
-      <c r="O5" s="30"/>
-      <c r="P5" s="31">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="31">
-        <v>9</v>
-      </c>
-      <c r="S5" s="32"/>
+      <c r="B5" s="64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="66"/>
       <c r="T5" s="34"/>
       <c r="U5" s="32"/>
-      <c r="V5" s="31">
-        <v>9</v>
-      </c>
-      <c r="W5" s="32"/>
-      <c r="X5" s="31">
-        <v>8</v>
-      </c>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="31">
-        <v>7</v>
-      </c>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="31">
-        <v>6</v>
-      </c>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="31">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="31">
-        <v>4</v>
-      </c>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="31">
-        <v>3</v>
-      </c>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="31">
-        <v>2</v>
-      </c>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="31">
-        <v>1</v>
-      </c>
-      <c r="AM5" s="32"/>
+      <c r="V5" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="65"/>
+      <c r="AG5" s="65"/>
+      <c r="AH5" s="65"/>
+      <c r="AI5" s="65"/>
+      <c r="AJ5" s="65"/>
+      <c r="AK5" s="65"/>
+      <c r="AL5" s="65"/>
+      <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="57"/>
+      <c r="AM6" s="59"/>
     </row>
     <row r="7" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -7182,24 +9046,16 @@
       </c>
     </row>
     <row r="8" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="63">
+      <c r="A8" s="56">
         <v>1</v>
       </c>
-      <c r="B8" s="51" t="s" ph="1">
-        <v>0</v>
-      </c>
+      <c r="B8" s="51" ph="1"/>
       <c r="C8" s="52"/>
-      <c r="D8" s="51" t="s" ph="1">
-        <v>320</v>
-      </c>
+      <c r="D8" s="51" ph="1"/>
       <c r="E8" s="52"/>
-      <c r="F8" s="51" t="s" ph="1">
-        <v>321</v>
-      </c>
+      <c r="F8" s="51" ph="1"/>
       <c r="G8" s="52"/>
-      <c r="H8" s="51" t="s" ph="1">
-        <v>322</v>
-      </c>
+      <c r="H8" s="51" ph="1"/>
       <c r="I8" s="52"/>
       <c r="J8" s="51" ph="1"/>
       <c r="K8" s="52"/>
@@ -7229,33 +9085,19 @@
       <c r="AI8" s="52"/>
       <c r="AJ8" s="51" ph="1"/>
       <c r="AK8" s="52"/>
-      <c r="AL8" s="51" t="s" ph="1">
-        <v>313</v>
-      </c>
+      <c r="AL8" s="51" ph="1"/>
       <c r="AM8" s="52"/>
     </row>
     <row r="9" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="63"/>
-      <c r="B9" s="39">
-        <v>10</v>
-      </c>
-      <c r="C9" s="40">
-        <v>18</v>
-      </c>
+      <c r="A9" s="56"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
       <c r="D9" s="39"/>
-      <c r="E9" s="40">
-        <v>1</v>
-      </c>
+      <c r="E9" s="40"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="40">
-        <v>3</v>
-      </c>
-      <c r="H9" s="39">
-        <v>2</v>
-      </c>
-      <c r="I9" s="40">
-        <v>8</v>
-      </c>
+      <c r="G9" s="40"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="40"/>
       <c r="J9" s="39"/>
       <c r="K9" s="40"/>
       <c r="L9" s="39"/>
@@ -7284,24 +9126,16 @@
       <c r="AI9" s="40"/>
       <c r="AJ9" s="39"/>
       <c r="AK9" s="40"/>
-      <c r="AL9" s="39">
+      <c r="AL9" s="39"/>
+      <c r="AM9" s="40"/>
+    </row>
+    <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A10" s="56">
         <v>2</v>
       </c>
-      <c r="AM9" s="40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="63">
-        <v>2</v>
-      </c>
-      <c r="B10" s="51" t="s" ph="1">
-        <v>323</v>
-      </c>
+      <c r="B10" s="51" ph="1"/>
       <c r="C10" s="52"/>
-      <c r="D10" s="51" t="s" ph="1">
-        <v>324</v>
-      </c>
+      <c r="D10" s="51" ph="1"/>
       <c r="E10" s="52"/>
       <c r="F10" s="51" ph="1"/>
       <c r="G10" s="52"/>
@@ -7335,21 +9169,15 @@
       <c r="AI10" s="52"/>
       <c r="AJ10" s="51" ph="1"/>
       <c r="AK10" s="52"/>
-      <c r="AL10" s="51" t="s" ph="1">
-        <v>314</v>
-      </c>
+      <c r="AL10" s="51" ph="1"/>
       <c r="AM10" s="52"/>
     </row>
     <row r="11" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="39"/>
-      <c r="C11" s="40">
-        <v>18</v>
-      </c>
+      <c r="C11" s="40"/>
       <c r="D11" s="39"/>
-      <c r="E11" s="40">
-        <v>11</v>
-      </c>
+      <c r="E11" s="40"/>
       <c r="F11" s="39"/>
       <c r="G11" s="40"/>
       <c r="H11" s="39"/>
@@ -7382,22 +9210,16 @@
       <c r="AI11" s="40"/>
       <c r="AJ11" s="39"/>
       <c r="AK11" s="40"/>
-      <c r="AL11" s="39">
-        <v>18</v>
-      </c>
+      <c r="AL11" s="39"/>
       <c r="AM11" s="40"/>
     </row>
     <row r="12" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="63">
+      <c r="A12" s="56">
         <v>3</v>
       </c>
-      <c r="B12" s="51" t="s" ph="1">
-        <v>325</v>
-      </c>
+      <c r="B12" s="51" ph="1"/>
       <c r="C12" s="52"/>
-      <c r="D12" s="51" t="s" ph="1">
-        <v>326</v>
-      </c>
+      <c r="D12" s="51" ph="1"/>
       <c r="E12" s="52"/>
       <c r="F12" s="51" ph="1"/>
       <c r="G12" s="52"/>
@@ -7431,21 +9253,15 @@
       <c r="AI12" s="52"/>
       <c r="AJ12" s="51" ph="1"/>
       <c r="AK12" s="52"/>
-      <c r="AL12" s="51" t="s" ph="1">
-        <v>314</v>
-      </c>
+      <c r="AL12" s="51" ph="1"/>
       <c r="AM12" s="52"/>
     </row>
     <row r="13" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="39"/>
-      <c r="C13" s="40">
-        <v>8</v>
-      </c>
+      <c r="C13" s="40"/>
       <c r="D13" s="39"/>
-      <c r="E13" s="40">
-        <v>5</v>
-      </c>
+      <c r="E13" s="40"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
       <c r="H13" s="39"/>
@@ -7478,13 +9294,11 @@
       <c r="AI13" s="40"/>
       <c r="AJ13" s="39"/>
       <c r="AK13" s="40"/>
-      <c r="AL13" s="39">
-        <v>20</v>
-      </c>
+      <c r="AL13" s="39"/>
       <c r="AM13" s="40"/>
     </row>
     <row r="14" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="63">
+      <c r="A14" s="56">
         <v>4</v>
       </c>
       <c r="B14" s="51" ph="1"/>
@@ -7523,13 +9337,11 @@
       <c r="AI14" s="52"/>
       <c r="AJ14" s="51" ph="1"/>
       <c r="AK14" s="52"/>
-      <c r="AL14" s="51" t="s" ph="1">
-        <v>315</v>
-      </c>
+      <c r="AL14" s="51" ph="1"/>
       <c r="AM14" s="52"/>
     </row>
     <row r="15" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63"/>
+      <c r="A15" s="56"/>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
       <c r="D15" s="39"/>
@@ -7566,28 +9378,18 @@
       <c r="AI15" s="40"/>
       <c r="AJ15" s="39"/>
       <c r="AK15" s="40"/>
-      <c r="AL15" s="39">
-        <v>6</v>
-      </c>
-      <c r="AM15" s="40">
-        <v>12</v>
-      </c>
+      <c r="AL15" s="39"/>
+      <c r="AM15" s="40"/>
     </row>
     <row r="16" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="63">
+      <c r="A16" s="56">
         <v>5</v>
       </c>
-      <c r="B16" s="51" t="s" ph="1">
-        <v>327</v>
-      </c>
+      <c r="B16" s="51" ph="1"/>
       <c r="C16" s="52"/>
-      <c r="D16" s="51" t="s" ph="1">
-        <v>328</v>
-      </c>
+      <c r="D16" s="51" ph="1"/>
       <c r="E16" s="52"/>
-      <c r="F16" s="51" t="s" ph="1">
-        <v>329</v>
-      </c>
+      <c r="F16" s="51" ph="1"/>
       <c r="G16" s="52"/>
       <c r="H16" s="51" ph="1"/>
       <c r="I16" s="52"/>
@@ -7619,31 +9421,17 @@
       <c r="AI16" s="52"/>
       <c r="AJ16" s="51" ph="1"/>
       <c r="AK16" s="52"/>
-      <c r="AL16" s="51" t="s" ph="1">
-        <v>316</v>
-      </c>
+      <c r="AL16" s="51" ph="1"/>
       <c r="AM16" s="52"/>
     </row>
     <row r="17" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="63"/>
-      <c r="B17" s="39">
-        <v>1</v>
-      </c>
-      <c r="C17" s="40">
-        <v>16</v>
-      </c>
-      <c r="D17" s="39">
-        <v>1</v>
-      </c>
-      <c r="E17" s="40">
-        <v>6</v>
-      </c>
-      <c r="F17" s="39">
-        <v>3</v>
-      </c>
-      <c r="G17" s="40">
-        <v>10</v>
-      </c>
+      <c r="A17" s="56"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
       <c r="J17" s="39"/>
@@ -7674,20 +9462,14 @@
       <c r="AI17" s="40"/>
       <c r="AJ17" s="39"/>
       <c r="AK17" s="40"/>
-      <c r="AL17" s="39">
+      <c r="AL17" s="39"/>
+      <c r="AM17" s="40"/>
+    </row>
+    <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A18" s="56">
         <v>6</v>
       </c>
-      <c r="AM17" s="40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="63">
-        <v>6</v>
-      </c>
-      <c r="B18" s="51" t="s" ph="1">
-        <v>330</v>
-      </c>
+      <c r="B18" s="51" ph="1"/>
       <c r="C18" s="52"/>
       <c r="D18" s="51" ph="1"/>
       <c r="E18" s="52"/>
@@ -7723,19 +9505,13 @@
       <c r="AI18" s="52"/>
       <c r="AJ18" s="51" ph="1"/>
       <c r="AK18" s="52"/>
-      <c r="AL18" s="51" t="s" ph="1">
-        <v>317</v>
-      </c>
+      <c r="AL18" s="51" ph="1"/>
       <c r="AM18" s="52"/>
     </row>
     <row r="19" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
-      <c r="B19" s="39">
-        <v>3</v>
-      </c>
-      <c r="C19" s="40">
-        <v>13</v>
-      </c>
+      <c r="A19" s="56"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="39"/>
       <c r="E19" s="40"/>
       <c r="F19" s="39"/>
@@ -7770,24 +9546,16 @@
       <c r="AI19" s="40"/>
       <c r="AJ19" s="39"/>
       <c r="AK19" s="40"/>
-      <c r="AL19" s="39">
-        <v>5</v>
-      </c>
-      <c r="AM19" s="40">
-        <v>32</v>
-      </c>
+      <c r="AL19" s="39"/>
+      <c r="AM19" s="40"/>
     </row>
     <row r="20" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="63">
+      <c r="A20" s="56">
         <v>7</v>
       </c>
-      <c r="B20" s="51" t="s" ph="1">
-        <v>278</v>
-      </c>
+      <c r="B20" s="51" ph="1"/>
       <c r="C20" s="52"/>
-      <c r="D20" s="51" t="s" ph="1">
-        <v>331</v>
-      </c>
+      <c r="D20" s="51" ph="1"/>
       <c r="E20" s="52"/>
       <c r="F20" s="51" ph="1"/>
       <c r="G20" s="52"/>
@@ -7821,23 +9589,15 @@
       <c r="AI20" s="52"/>
       <c r="AJ20" s="51" ph="1"/>
       <c r="AK20" s="52"/>
-      <c r="AL20" s="51" t="s" ph="1">
-        <v>314</v>
-      </c>
+      <c r="AL20" s="51" ph="1"/>
       <c r="AM20" s="52"/>
     </row>
     <row r="21" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
-      <c r="B21" s="39">
-        <v>3</v>
-      </c>
-      <c r="C21" s="40">
-        <v>9</v>
-      </c>
+      <c r="A21" s="56"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="39"/>
-      <c r="E21" s="40">
-        <v>1</v>
-      </c>
+      <c r="E21" s="40"/>
       <c r="F21" s="39"/>
       <c r="G21" s="40"/>
       <c r="H21" s="39"/>
@@ -7870,20 +9630,14 @@
       <c r="AI21" s="40"/>
       <c r="AJ21" s="39"/>
       <c r="AK21" s="40"/>
-      <c r="AL21" s="39">
+      <c r="AL21" s="39"/>
+      <c r="AM21" s="40"/>
+    </row>
+    <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
+      <c r="A22" s="56">
         <v>8</v>
       </c>
-      <c r="AM21" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="63">
-        <v>8</v>
-      </c>
-      <c r="B22" s="51" t="s" ph="1">
-        <v>332</v>
-      </c>
+      <c r="B22" s="51" ph="1"/>
       <c r="C22" s="52"/>
       <c r="D22" s="51" ph="1"/>
       <c r="E22" s="52"/>
@@ -7919,19 +9673,13 @@
       <c r="AI22" s="52"/>
       <c r="AJ22" s="51" ph="1"/>
       <c r="AK22" s="52"/>
-      <c r="AL22" s="51" t="s" ph="1">
-        <v>318</v>
-      </c>
+      <c r="AL22" s="51" ph="1"/>
       <c r="AM22" s="52"/>
     </row>
     <row r="23" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="63"/>
-      <c r="B23" s="39">
-        <v>2</v>
-      </c>
-      <c r="C23" s="40">
-        <v>10</v>
-      </c>
+      <c r="A23" s="56"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="39"/>
       <c r="E23" s="40"/>
       <c r="F23" s="39"/>
@@ -7966,18 +9714,14 @@
       <c r="AI23" s="40"/>
       <c r="AJ23" s="39"/>
       <c r="AK23" s="40"/>
-      <c r="AL23" s="39">
-        <v>4</v>
-      </c>
+      <c r="AL23" s="39"/>
       <c r="AM23" s="40"/>
     </row>
     <row r="24" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="63">
+      <c r="A24" s="56">
         <v>9</v>
       </c>
-      <c r="B24" s="51" t="s" ph="1">
-        <v>333</v>
-      </c>
+      <c r="B24" s="51" ph="1"/>
       <c r="C24" s="52"/>
       <c r="D24" s="51" ph="1"/>
       <c r="E24" s="52"/>
@@ -8017,10 +9761,8 @@
       <c r="AM24" s="52"/>
     </row>
     <row r="25" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="63"/>
-      <c r="B25" s="39">
-        <v>8</v>
-      </c>
+      <c r="A25" s="56"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="40"/>
       <c r="D25" s="39"/>
       <c r="E25" s="40"/>
@@ -8060,12 +9802,10 @@
       <c r="AM25" s="40"/>
     </row>
     <row r="26" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="63">
+      <c r="A26" s="56">
         <v>10</v>
       </c>
-      <c r="B26" s="51" t="s" ph="1">
-        <v>334</v>
-      </c>
+      <c r="B26" s="51" ph="1"/>
       <c r="C26" s="52"/>
       <c r="D26" s="51" ph="1"/>
       <c r="E26" s="52"/>
@@ -8101,19 +9841,13 @@
       <c r="AI26" s="52"/>
       <c r="AJ26" s="51" ph="1"/>
       <c r="AK26" s="52"/>
-      <c r="AL26" s="51" t="s" ph="1">
-        <v>319</v>
-      </c>
+      <c r="AL26" s="51" ph="1"/>
       <c r="AM26" s="52"/>
     </row>
     <row r="27" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="63"/>
-      <c r="B27" s="39">
-        <v>5</v>
-      </c>
-      <c r="C27" s="40">
-        <v>6</v>
-      </c>
+      <c r="A27" s="56"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="39"/>
       <c r="E27" s="40"/>
       <c r="F27" s="39"/>
@@ -8152,7 +9886,7 @@
       <c r="AM27" s="40"/>
     </row>
     <row r="28" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="63">
+      <c r="A28" s="56">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -8195,7 +9929,7 @@
       <c r="AM28" s="52"/>
     </row>
     <row r="29" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="63"/>
+      <c r="A29" s="56"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -8236,7 +9970,7 @@
       <c r="AM29" s="40"/>
     </row>
     <row r="30" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="63">
+      <c r="A30" s="56">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -8279,7 +10013,7 @@
       <c r="AM30" s="52"/>
     </row>
     <row r="31" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="63"/>
+      <c r="A31" s="56"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -8320,7 +10054,7 @@
       <c r="AM31" s="40"/>
     </row>
     <row r="32" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="63">
+      <c r="A32" s="56">
         <v>13</v>
       </c>
       <c r="B32" s="51" ph="1"/>
@@ -8363,7 +10097,7 @@
       <c r="AM32" s="52"/>
     </row>
     <row r="33" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="63"/>
+      <c r="A33" s="56"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40"/>
       <c r="D33" s="39"/>
@@ -8404,2050 +10138,7 @@
       <c r="AM33" s="40"/>
     </row>
     <row r="34" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="63">
-        <v>14</v>
-      </c>
-      <c r="B34" s="51" t="s" ph="1">
-        <v>346</v>
-      </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="51" t="s" ph="1">
-        <v>347</v>
-      </c>
-      <c r="E34" s="52"/>
-      <c r="F34" s="51" t="s" ph="1">
-        <v>348</v>
-      </c>
-      <c r="G34" s="52"/>
-      <c r="H34" s="51" t="s" ph="1">
-        <v>349</v>
-      </c>
-      <c r="I34" s="52"/>
-      <c r="J34" s="51" ph="1"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="51" ph="1"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="51" ph="1"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="51" ph="1"/>
-      <c r="Q34" s="52"/>
-      <c r="R34" s="51" ph="1"/>
-      <c r="S34" s="52"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="51" ph="1"/>
-      <c r="W34" s="52"/>
-      <c r="X34" s="51" ph="1"/>
-      <c r="Y34" s="52"/>
-      <c r="Z34" s="51" ph="1"/>
-      <c r="AA34" s="52"/>
-      <c r="AB34" s="51" ph="1"/>
-      <c r="AC34" s="52"/>
-      <c r="AD34" s="51" ph="1"/>
-      <c r="AE34" s="52"/>
-      <c r="AF34" s="51" ph="1"/>
-      <c r="AG34" s="52"/>
-      <c r="AH34" s="51" ph="1"/>
-      <c r="AI34" s="52"/>
-      <c r="AJ34" s="51" ph="1"/>
-      <c r="AK34" s="52"/>
-      <c r="AL34" s="51" ph="1"/>
-      <c r="AM34" s="52"/>
-    </row>
-    <row r="35" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="63"/>
-      <c r="B35" s="39">
-        <v>6</v>
-      </c>
-      <c r="C35" s="40">
-        <v>15</v>
-      </c>
-      <c r="D35" s="39">
-        <v>1</v>
-      </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="40">
-        <v>14</v>
-      </c>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40">
-        <v>9</v>
-      </c>
-      <c r="J35" s="39"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="39"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="39"/>
-      <c r="W35" s="40"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="39"/>
-      <c r="AA35" s="40"/>
-      <c r="AB35" s="39"/>
-      <c r="AC35" s="40"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="40"/>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="40"/>
-      <c r="AH35" s="39"/>
-      <c r="AI35" s="40"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="40"/>
-      <c r="AL35" s="39"/>
-      <c r="AM35" s="40"/>
-    </row>
-    <row r="36" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="63">
-        <v>15</v>
-      </c>
-      <c r="B36" s="51" t="s" ph="1">
-        <v>343</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="51" t="s" ph="1">
-        <v>344</v>
-      </c>
-      <c r="E36" s="52"/>
-      <c r="F36" s="51" t="s" ph="1">
-        <v>345</v>
-      </c>
-      <c r="G36" s="52"/>
-      <c r="H36" s="51" ph="1"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="51" ph="1"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="51" ph="1"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="51" ph="1"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="51" ph="1"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="51" ph="1"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="51" ph="1"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="51" ph="1"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="51" ph="1"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="51" ph="1"/>
-      <c r="AC36" s="52"/>
-      <c r="AD36" s="51" ph="1"/>
-      <c r="AE36" s="52"/>
-      <c r="AF36" s="51" ph="1"/>
-      <c r="AG36" s="52"/>
-      <c r="AH36" s="51" ph="1"/>
-      <c r="AI36" s="52"/>
-      <c r="AJ36" s="51" ph="1"/>
-      <c r="AK36" s="52"/>
-      <c r="AL36" s="51" ph="1"/>
-      <c r="AM36" s="52"/>
-    </row>
-    <row r="37" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="63"/>
-      <c r="B37" s="39">
-        <v>3</v>
-      </c>
-      <c r="C37" s="40">
-        <v>12</v>
-      </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40">
-        <v>1</v>
-      </c>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40">
-        <v>1</v>
-      </c>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="39"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="39"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="39"/>
-      <c r="W37" s="40"/>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="39"/>
-      <c r="AA37" s="40"/>
-      <c r="AB37" s="39"/>
-      <c r="AC37" s="40"/>
-      <c r="AD37" s="39"/>
-      <c r="AE37" s="40"/>
-      <c r="AF37" s="39"/>
-      <c r="AG37" s="40"/>
-      <c r="AH37" s="39"/>
-      <c r="AI37" s="40"/>
-      <c r="AJ37" s="39"/>
-      <c r="AK37" s="40"/>
-      <c r="AL37" s="39"/>
-      <c r="AM37" s="40"/>
-    </row>
-    <row r="38" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="63">
-        <v>16</v>
-      </c>
-      <c r="B38" s="51" t="s" ph="1">
-        <v>338</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="51" t="s" ph="1">
-        <v>339</v>
-      </c>
-      <c r="E38" s="52"/>
-      <c r="F38" s="51" t="s" ph="1">
-        <v>340</v>
-      </c>
-      <c r="G38" s="52"/>
-      <c r="H38" s="51" t="s" ph="1">
-        <v>341</v>
-      </c>
-      <c r="I38" s="52"/>
-      <c r="J38" s="51" ph="1"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="51" ph="1"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="51" ph="1"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="51" ph="1"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="51" ph="1"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="51" ph="1"/>
-      <c r="W38" s="52"/>
-      <c r="X38" s="51" ph="1"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="51" ph="1"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="51" ph="1"/>
-      <c r="AC38" s="52"/>
-      <c r="AD38" s="51" ph="1"/>
-      <c r="AE38" s="52"/>
-      <c r="AF38" s="51" ph="1"/>
-      <c r="AG38" s="52"/>
-      <c r="AH38" s="51" ph="1"/>
-      <c r="AI38" s="52"/>
-      <c r="AJ38" s="51" ph="1"/>
-      <c r="AK38" s="52"/>
-      <c r="AL38" s="51" ph="1"/>
-      <c r="AM38" s="52"/>
-    </row>
-    <row r="39" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="63"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="40">
-        <v>12</v>
-      </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40">
-        <v>2</v>
-      </c>
-      <c r="F39" s="39"/>
-      <c r="G39" s="40">
-        <v>2</v>
-      </c>
-      <c r="H39" s="39">
-        <v>1</v>
-      </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="40"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="40"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="40"/>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="40"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="40"/>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="40"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="40"/>
-      <c r="AJ39" s="39"/>
-      <c r="AK39" s="40"/>
-      <c r="AL39" s="39"/>
-      <c r="AM39" s="40"/>
-    </row>
-    <row r="40" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="63">
-        <v>17</v>
-      </c>
-      <c r="B40" s="51" t="s" ph="1">
-        <v>337</v>
-      </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="51" ph="1"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="51" ph="1"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="51" ph="1"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="51" ph="1"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="51" ph="1"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="51" ph="1"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="51" ph="1"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="51" ph="1"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="51" ph="1"/>
-      <c r="W40" s="52"/>
-      <c r="X40" s="51" ph="1"/>
-      <c r="Y40" s="52"/>
-      <c r="Z40" s="51" ph="1"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="51" ph="1"/>
-      <c r="AC40" s="52"/>
-      <c r="AD40" s="51" ph="1"/>
-      <c r="AE40" s="52"/>
-      <c r="AF40" s="51" ph="1"/>
-      <c r="AG40" s="52"/>
-      <c r="AH40" s="51" ph="1"/>
-      <c r="AI40" s="52"/>
-      <c r="AJ40" s="51" ph="1"/>
-      <c r="AK40" s="52"/>
-      <c r="AL40" s="51" ph="1"/>
-      <c r="AM40" s="52"/>
-    </row>
-    <row r="41" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="63"/>
-      <c r="B41" s="39">
-        <v>2</v>
-      </c>
-      <c r="C41" s="40">
-        <v>6</v>
-      </c>
-      <c r="D41" s="39"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="40"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="39"/>
-      <c r="W41" s="40"/>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="40"/>
-      <c r="Z41" s="39"/>
-      <c r="AA41" s="40"/>
-      <c r="AB41" s="39"/>
-      <c r="AC41" s="40"/>
-      <c r="AD41" s="39"/>
-      <c r="AE41" s="40"/>
-      <c r="AF41" s="39"/>
-      <c r="AG41" s="40"/>
-      <c r="AH41" s="39"/>
-      <c r="AI41" s="40"/>
-      <c r="AJ41" s="39"/>
-      <c r="AK41" s="40"/>
-      <c r="AL41" s="39"/>
-      <c r="AM41" s="40"/>
-    </row>
-    <row r="42" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="63">
-        <v>18</v>
-      </c>
-      <c r="B42" s="51" t="s" ph="1">
-        <v>335</v>
-      </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="51" t="s" ph="1">
-        <v>336</v>
-      </c>
-      <c r="E42" s="52"/>
-      <c r="F42" s="51" ph="1"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="51" ph="1"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="51" ph="1"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="51" ph="1"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="51" ph="1"/>
-      <c r="O42" s="52"/>
-      <c r="P42" s="51" ph="1"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51" ph="1"/>
-      <c r="S42" s="52"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="51" ph="1"/>
-      <c r="W42" s="52"/>
-      <c r="X42" s="51" ph="1"/>
-      <c r="Y42" s="52"/>
-      <c r="Z42" s="51" ph="1"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="51" ph="1"/>
-      <c r="AC42" s="52"/>
-      <c r="AD42" s="51" ph="1"/>
-      <c r="AE42" s="52"/>
-      <c r="AF42" s="51" ph="1"/>
-      <c r="AG42" s="52"/>
-      <c r="AH42" s="51" ph="1"/>
-      <c r="AI42" s="52"/>
-      <c r="AJ42" s="51" ph="1"/>
-      <c r="AK42" s="52"/>
-      <c r="AL42" s="51" ph="1"/>
-      <c r="AM42" s="52"/>
-    </row>
-    <row r="43" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="63"/>
-      <c r="B43" s="39">
-        <v>1</v>
-      </c>
-      <c r="C43" s="40">
-        <v>14</v>
-      </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="40">
-        <v>11</v>
-      </c>
-      <c r="F43" s="39"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="39"/>
-      <c r="S43" s="40"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="39"/>
-      <c r="W43" s="40"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="40"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="40"/>
-      <c r="AB43" s="39"/>
-      <c r="AC43" s="40"/>
-      <c r="AD43" s="39"/>
-      <c r="AE43" s="40"/>
-      <c r="AF43" s="39"/>
-      <c r="AG43" s="40"/>
-      <c r="AH43" s="39"/>
-      <c r="AI43" s="40"/>
-      <c r="AJ43" s="39"/>
-      <c r="AK43" s="40"/>
-      <c r="AL43" s="39"/>
-      <c r="AM43" s="40"/>
-    </row>
-    <row r="44" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="34">
-        <v>1</v>
-      </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="31">
-        <v>2</v>
-      </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="31">
-        <v>3</v>
-      </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="31">
-        <v>4</v>
-      </c>
-      <c r="I44" s="30"/>
-      <c r="J44" s="31">
-        <v>5</v>
-      </c>
-      <c r="K44" s="32"/>
-      <c r="L44" s="31">
-        <v>6</v>
-      </c>
-      <c r="M44" s="32"/>
-      <c r="N44" s="31">
-        <v>7</v>
-      </c>
-      <c r="O44" s="30"/>
-      <c r="P44" s="31">
-        <v>8</v>
-      </c>
-      <c r="Q44" s="32"/>
-      <c r="R44" s="31">
-        <v>9</v>
-      </c>
-      <c r="S44" s="32"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="31">
-        <v>9</v>
-      </c>
-      <c r="W44" s="32"/>
-      <c r="X44" s="31">
-        <v>8</v>
-      </c>
-      <c r="Y44" s="32"/>
-      <c r="Z44" s="31">
-        <v>7</v>
-      </c>
-      <c r="AA44" s="32"/>
-      <c r="AB44" s="31">
-        <v>6</v>
-      </c>
-      <c r="AC44" s="30"/>
-      <c r="AD44" s="31">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="32"/>
-      <c r="AF44" s="31">
-        <v>4</v>
-      </c>
-      <c r="AG44" s="32"/>
-      <c r="AH44" s="31">
-        <v>3</v>
-      </c>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="31">
-        <v>2</v>
-      </c>
-      <c r="AK44" s="32"/>
-      <c r="AL44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AM44" s="32"/>
-    </row>
-    <row r="45" spans="1:39" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="16"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
-      <c r="AD45" s="11"/>
-      <c r="AE45" s="10"/>
-      <c r="AF45" s="11"/>
-      <c r="AG45" s="11"/>
-      <c r="AH45" s="9"/>
-      <c r="AI45" s="9"/>
-      <c r="AJ45" s="9"/>
-      <c r="AK45" s="9"/>
-      <c r="AL45" s="9"/>
-      <c r="AM45" s="12"/>
-    </row>
-    <row r="46" spans="1:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor theme="9" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A3:AM46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.125" customWidth="1"/>
-    <col min="2" max="39" width="32.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:39" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-    </row>
-    <row r="4" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="1"/>
-      <c r="C4" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="60">
-        <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3"/>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="4"/>
-    </row>
-    <row r="5" spans="1:39" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="64" t="s">
-        <v>227</v>
-      </c>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="65"/>
-      <c r="AG5" s="65"/>
-      <c r="AH5" s="65"/>
-      <c r="AI5" s="65"/>
-      <c r="AJ5" s="65"/>
-      <c r="AK5" s="65"/>
-      <c r="AL5" s="65"/>
-      <c r="AM5" s="66"/>
-    </row>
-    <row r="6" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM6" s="57"/>
-    </row>
-    <row r="7" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="O7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="R7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="T7" s="28"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="W7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="X7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AD7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AJ7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AL7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM7" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="63">
-        <v>1</v>
-      </c>
-      <c r="B8" s="51" ph="1"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="51" ph="1"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="51" ph="1"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="51" ph="1"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="51" ph="1"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="51" ph="1"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="51" ph="1"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="51" ph="1"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="51" ph="1"/>
-      <c r="S8" s="52"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="51" ph="1"/>
-      <c r="W8" s="52"/>
-      <c r="X8" s="51" ph="1"/>
-      <c r="Y8" s="52"/>
-      <c r="Z8" s="51" ph="1"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="51" ph="1"/>
-      <c r="AC8" s="52"/>
-      <c r="AD8" s="51" ph="1"/>
-      <c r="AE8" s="52"/>
-      <c r="AF8" s="51" ph="1"/>
-      <c r="AG8" s="52"/>
-      <c r="AH8" s="51" ph="1"/>
-      <c r="AI8" s="52"/>
-      <c r="AJ8" s="51" ph="1"/>
-      <c r="AK8" s="52"/>
-      <c r="AL8" s="51" ph="1"/>
-      <c r="AM8" s="52"/>
-    </row>
-    <row r="9" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="63"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="40"/>
-      <c r="AJ9" s="39"/>
-      <c r="AK9" s="40"/>
-      <c r="AL9" s="39"/>
-      <c r="AM9" s="40"/>
-    </row>
-    <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="63">
-        <v>2</v>
-      </c>
-      <c r="B10" s="51" ph="1"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="51" ph="1"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="51" ph="1"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="51" ph="1"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="51" ph="1"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="51" ph="1"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="51" ph="1"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="51" ph="1"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="51" ph="1"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="51" ph="1"/>
-      <c r="W10" s="52"/>
-      <c r="X10" s="51" ph="1"/>
-      <c r="Y10" s="52"/>
-      <c r="Z10" s="51" ph="1"/>
-      <c r="AA10" s="52"/>
-      <c r="AB10" s="51" ph="1"/>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="51" ph="1"/>
-      <c r="AE10" s="52"/>
-      <c r="AF10" s="51" ph="1"/>
-      <c r="AG10" s="52"/>
-      <c r="AH10" s="51" ph="1"/>
-      <c r="AI10" s="52"/>
-      <c r="AJ10" s="51" ph="1"/>
-      <c r="AK10" s="52"/>
-      <c r="AL10" s="51" ph="1"/>
-      <c r="AM10" s="52"/>
-    </row>
-    <row r="11" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="40"/>
-    </row>
-    <row r="12" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="63">
-        <v>3</v>
-      </c>
-      <c r="B12" s="51" ph="1"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="51" ph="1"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="51" ph="1"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="51" ph="1"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="51" ph="1"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="51" ph="1"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="51" ph="1"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="51" ph="1"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="51" ph="1"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="51" ph="1"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="51" ph="1"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="51" ph="1"/>
-      <c r="AA12" s="52"/>
-      <c r="AB12" s="51" ph="1"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="51" ph="1"/>
-      <c r="AE12" s="52"/>
-      <c r="AF12" s="51" ph="1"/>
-      <c r="AG12" s="52"/>
-      <c r="AH12" s="51" ph="1"/>
-      <c r="AI12" s="52"/>
-      <c r="AJ12" s="51" ph="1"/>
-      <c r="AK12" s="52"/>
-      <c r="AL12" s="51" ph="1"/>
-      <c r="AM12" s="52"/>
-    </row>
-    <row r="13" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="39"/>
-      <c r="AI13" s="40"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="40"/>
-      <c r="AL13" s="39"/>
-      <c r="AM13" s="40"/>
-    </row>
-    <row r="14" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="63">
-        <v>4</v>
-      </c>
-      <c r="B14" s="51" ph="1"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="51" ph="1"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="51" ph="1"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="51" ph="1"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="51" ph="1"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="51" ph="1"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="51" ph="1"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="51" ph="1"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="51" ph="1"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="51" ph="1"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="51" ph="1"/>
-      <c r="Y14" s="52"/>
-      <c r="Z14" s="51" ph="1"/>
-      <c r="AA14" s="52"/>
-      <c r="AB14" s="51" ph="1"/>
-      <c r="AC14" s="52"/>
-      <c r="AD14" s="51" ph="1"/>
-      <c r="AE14" s="52"/>
-      <c r="AF14" s="51" ph="1"/>
-      <c r="AG14" s="52"/>
-      <c r="AH14" s="51" ph="1"/>
-      <c r="AI14" s="52"/>
-      <c r="AJ14" s="51" ph="1"/>
-      <c r="AK14" s="52"/>
-      <c r="AL14" s="51" ph="1"/>
-      <c r="AM14" s="52"/>
-    </row>
-    <row r="15" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="40"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="40"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="39"/>
-      <c r="AM15" s="40"/>
-    </row>
-    <row r="16" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="63">
-        <v>5</v>
-      </c>
-      <c r="B16" s="51" ph="1"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="51" ph="1"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="51" ph="1"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="51" ph="1"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="51" ph="1"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="51" ph="1"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="51" ph="1"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="51" ph="1"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="51" ph="1"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="51" ph="1"/>
-      <c r="W16" s="52"/>
-      <c r="X16" s="51" ph="1"/>
-      <c r="Y16" s="52"/>
-      <c r="Z16" s="51" ph="1"/>
-      <c r="AA16" s="52"/>
-      <c r="AB16" s="51" ph="1"/>
-      <c r="AC16" s="52"/>
-      <c r="AD16" s="51" ph="1"/>
-      <c r="AE16" s="52"/>
-      <c r="AF16" s="51" ph="1"/>
-      <c r="AG16" s="52"/>
-      <c r="AH16" s="51" ph="1"/>
-      <c r="AI16" s="52"/>
-      <c r="AJ16" s="51" ph="1"/>
-      <c r="AK16" s="52"/>
-      <c r="AL16" s="51" ph="1"/>
-      <c r="AM16" s="52"/>
-    </row>
-    <row r="17" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="63"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="40"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="39"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="40"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="40"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="40"/>
-      <c r="AH17" s="39"/>
-      <c r="AI17" s="40"/>
-      <c r="AJ17" s="39"/>
-      <c r="AK17" s="40"/>
-      <c r="AL17" s="39"/>
-      <c r="AM17" s="40"/>
-    </row>
-    <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="63">
-        <v>6</v>
-      </c>
-      <c r="B18" s="51" ph="1"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="51" ph="1"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="51" ph="1"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="51" ph="1"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="51" ph="1"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="51" ph="1"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="51" ph="1"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="51" ph="1"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="51" ph="1"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="51" ph="1"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="51" ph="1"/>
-      <c r="Y18" s="52"/>
-      <c r="Z18" s="51" ph="1"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="51" ph="1"/>
-      <c r="AC18" s="52"/>
-      <c r="AD18" s="51" ph="1"/>
-      <c r="AE18" s="52"/>
-      <c r="AF18" s="51" ph="1"/>
-      <c r="AG18" s="52"/>
-      <c r="AH18" s="51" ph="1"/>
-      <c r="AI18" s="52"/>
-      <c r="AJ18" s="51" ph="1"/>
-      <c r="AK18" s="52"/>
-      <c r="AL18" s="51" ph="1"/>
-      <c r="AM18" s="52"/>
-    </row>
-    <row r="19" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="39"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="39"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="39"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="39"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="39"/>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="39"/>
-      <c r="AG19" s="40"/>
-      <c r="AH19" s="39"/>
-      <c r="AI19" s="40"/>
-      <c r="AJ19" s="39"/>
-      <c r="AK19" s="40"/>
-      <c r="AL19" s="39"/>
-      <c r="AM19" s="40"/>
-    </row>
-    <row r="20" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="63">
-        <v>7</v>
-      </c>
-      <c r="B20" s="51" ph="1"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="51" ph="1"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="51" ph="1"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="51" ph="1"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="51" ph="1"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="51" ph="1"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="51" ph="1"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="51" ph="1"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="51" ph="1"/>
-      <c r="S20" s="52"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="51" ph="1"/>
-      <c r="W20" s="52"/>
-      <c r="X20" s="51" ph="1"/>
-      <c r="Y20" s="52"/>
-      <c r="Z20" s="51" ph="1"/>
-      <c r="AA20" s="52"/>
-      <c r="AB20" s="51" ph="1"/>
-      <c r="AC20" s="52"/>
-      <c r="AD20" s="51" ph="1"/>
-      <c r="AE20" s="52"/>
-      <c r="AF20" s="51" ph="1"/>
-      <c r="AG20" s="52"/>
-      <c r="AH20" s="51" ph="1"/>
-      <c r="AI20" s="52"/>
-      <c r="AJ20" s="51" ph="1"/>
-      <c r="AK20" s="52"/>
-      <c r="AL20" s="51" ph="1"/>
-      <c r="AM20" s="52"/>
-    </row>
-    <row r="21" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="63"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="39"/>
-      <c r="W21" s="40"/>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="40"/>
-      <c r="Z21" s="39"/>
-      <c r="AA21" s="40"/>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="39"/>
-      <c r="AE21" s="40"/>
-      <c r="AF21" s="39"/>
-      <c r="AG21" s="40"/>
-      <c r="AH21" s="39"/>
-      <c r="AI21" s="40"/>
-      <c r="AJ21" s="39"/>
-      <c r="AK21" s="40"/>
-      <c r="AL21" s="39"/>
-      <c r="AM21" s="40"/>
-    </row>
-    <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="63">
-        <v>8</v>
-      </c>
-      <c r="B22" s="51" ph="1"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="51" ph="1"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="51" ph="1"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="51" ph="1"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="51" ph="1"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="51" ph="1"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="51" ph="1"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="51" ph="1"/>
-      <c r="Q22" s="52"/>
-      <c r="R22" s="51" ph="1"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="51" ph="1"/>
-      <c r="W22" s="52"/>
-      <c r="X22" s="51" ph="1"/>
-      <c r="Y22" s="52"/>
-      <c r="Z22" s="51" ph="1"/>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="51" ph="1"/>
-      <c r="AC22" s="52"/>
-      <c r="AD22" s="51" ph="1"/>
-      <c r="AE22" s="52"/>
-      <c r="AF22" s="51" ph="1"/>
-      <c r="AG22" s="52"/>
-      <c r="AH22" s="51" ph="1"/>
-      <c r="AI22" s="52"/>
-      <c r="AJ22" s="51" ph="1"/>
-      <c r="AK22" s="52"/>
-      <c r="AL22" s="51" ph="1"/>
-      <c r="AM22" s="52"/>
-    </row>
-    <row r="23" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="63"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="40"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="40"/>
-      <c r="AH23" s="39"/>
-      <c r="AI23" s="40"/>
-      <c r="AJ23" s="39"/>
-      <c r="AK23" s="40"/>
-      <c r="AL23" s="39"/>
-      <c r="AM23" s="40"/>
-    </row>
-    <row r="24" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="63">
-        <v>9</v>
-      </c>
-      <c r="B24" s="51" ph="1"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="51" ph="1"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="51" ph="1"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="51" ph="1"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="51" ph="1"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="51" ph="1"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="51" ph="1"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="51" ph="1"/>
-      <c r="Q24" s="52"/>
-      <c r="R24" s="51" ph="1"/>
-      <c r="S24" s="52"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="51" ph="1"/>
-      <c r="W24" s="52"/>
-      <c r="X24" s="51" ph="1"/>
-      <c r="Y24" s="52"/>
-      <c r="Z24" s="51" ph="1"/>
-      <c r="AA24" s="52"/>
-      <c r="AB24" s="51" ph="1"/>
-      <c r="AC24" s="52"/>
-      <c r="AD24" s="51" ph="1"/>
-      <c r="AE24" s="52"/>
-      <c r="AF24" s="51" ph="1"/>
-      <c r="AG24" s="52"/>
-      <c r="AH24" s="51" ph="1"/>
-      <c r="AI24" s="52"/>
-      <c r="AJ24" s="51" ph="1"/>
-      <c r="AK24" s="52"/>
-      <c r="AL24" s="51" ph="1"/>
-      <c r="AM24" s="52"/>
-    </row>
-    <row r="25" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="63"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="40"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="40"/>
-      <c r="AH25" s="39"/>
-      <c r="AI25" s="40"/>
-      <c r="AJ25" s="39"/>
-      <c r="AK25" s="40"/>
-      <c r="AL25" s="39"/>
-      <c r="AM25" s="40"/>
-    </row>
-    <row r="26" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="63">
-        <v>10</v>
-      </c>
-      <c r="B26" s="51" ph="1"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="51" ph="1"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="51" ph="1"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="51" ph="1"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="51" ph="1"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="51" ph="1"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="51" ph="1"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="51" ph="1"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="51" ph="1"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="51" ph="1"/>
-      <c r="W26" s="52"/>
-      <c r="X26" s="51" ph="1"/>
-      <c r="Y26" s="52"/>
-      <c r="Z26" s="51" ph="1"/>
-      <c r="AA26" s="52"/>
-      <c r="AB26" s="51" ph="1"/>
-      <c r="AC26" s="52"/>
-      <c r="AD26" s="51" ph="1"/>
-      <c r="AE26" s="52"/>
-      <c r="AF26" s="51" ph="1"/>
-      <c r="AG26" s="52"/>
-      <c r="AH26" s="51" ph="1"/>
-      <c r="AI26" s="52"/>
-      <c r="AJ26" s="51" ph="1"/>
-      <c r="AK26" s="52"/>
-      <c r="AL26" s="51" ph="1"/>
-      <c r="AM26" s="52"/>
-    </row>
-    <row r="27" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="63"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="39"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="39"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="39"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="39"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="39"/>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="39"/>
-      <c r="AG27" s="40"/>
-      <c r="AH27" s="39"/>
-      <c r="AI27" s="40"/>
-      <c r="AJ27" s="39"/>
-      <c r="AK27" s="40"/>
-      <c r="AL27" s="39"/>
-      <c r="AM27" s="40"/>
-    </row>
-    <row r="28" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="63">
-        <v>11</v>
-      </c>
-      <c r="B28" s="51" ph="1"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="51" ph="1"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51" ph="1"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="51" ph="1"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="51" ph="1"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="51" ph="1"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="51" ph="1"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="51" ph="1"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="51" ph="1"/>
-      <c r="S28" s="52"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="51" ph="1"/>
-      <c r="W28" s="52"/>
-      <c r="X28" s="51" ph="1"/>
-      <c r="Y28" s="52"/>
-      <c r="Z28" s="51" ph="1"/>
-      <c r="AA28" s="52"/>
-      <c r="AB28" s="51" ph="1"/>
-      <c r="AC28" s="52"/>
-      <c r="AD28" s="51" ph="1"/>
-      <c r="AE28" s="52"/>
-      <c r="AF28" s="51" ph="1"/>
-      <c r="AG28" s="52"/>
-      <c r="AH28" s="51" ph="1"/>
-      <c r="AI28" s="52"/>
-      <c r="AJ28" s="51" ph="1"/>
-      <c r="AK28" s="52"/>
-      <c r="AL28" s="51" ph="1"/>
-      <c r="AM28" s="52"/>
-    </row>
-    <row r="29" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="63"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="39"/>
-      <c r="W29" s="40"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="39"/>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="40"/>
-      <c r="AH29" s="39"/>
-      <c r="AI29" s="40"/>
-      <c r="AJ29" s="39"/>
-      <c r="AK29" s="40"/>
-      <c r="AL29" s="39"/>
-      <c r="AM29" s="40"/>
-    </row>
-    <row r="30" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="63">
-        <v>12</v>
-      </c>
-      <c r="B30" s="51" ph="1"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="51" ph="1"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="51" ph="1"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="51" ph="1"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="51" ph="1"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="51" ph="1"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="51" ph="1"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="51" ph="1"/>
-      <c r="Q30" s="52"/>
-      <c r="R30" s="51" ph="1"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="51" ph="1"/>
-      <c r="W30" s="52"/>
-      <c r="X30" s="51" ph="1"/>
-      <c r="Y30" s="52"/>
-      <c r="Z30" s="51" ph="1"/>
-      <c r="AA30" s="52"/>
-      <c r="AB30" s="51" ph="1"/>
-      <c r="AC30" s="52"/>
-      <c r="AD30" s="51" ph="1"/>
-      <c r="AE30" s="52"/>
-      <c r="AF30" s="51" ph="1"/>
-      <c r="AG30" s="52"/>
-      <c r="AH30" s="51" ph="1"/>
-      <c r="AI30" s="52"/>
-      <c r="AJ30" s="51" ph="1"/>
-      <c r="AK30" s="52"/>
-      <c r="AL30" s="51" ph="1"/>
-      <c r="AM30" s="52"/>
-    </row>
-    <row r="31" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="63"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="40"/>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="40"/>
-      <c r="AB31" s="39"/>
-      <c r="AC31" s="40"/>
-      <c r="AD31" s="39"/>
-      <c r="AE31" s="40"/>
-      <c r="AF31" s="39"/>
-      <c r="AG31" s="40"/>
-      <c r="AH31" s="39"/>
-      <c r="AI31" s="40"/>
-      <c r="AJ31" s="39"/>
-      <c r="AK31" s="40"/>
-      <c r="AL31" s="39"/>
-      <c r="AM31" s="40"/>
-    </row>
-    <row r="32" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="63">
-        <v>13</v>
-      </c>
-      <c r="B32" s="51" ph="1"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="51" ph="1"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="51" ph="1"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="51" ph="1"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="51" ph="1"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="51" ph="1"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="51" ph="1"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="51" ph="1"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="51" ph="1"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="51" ph="1"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="51" ph="1"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="51" ph="1"/>
-      <c r="AA32" s="52"/>
-      <c r="AB32" s="51" ph="1"/>
-      <c r="AC32" s="52"/>
-      <c r="AD32" s="51" ph="1"/>
-      <c r="AE32" s="52"/>
-      <c r="AF32" s="51" ph="1"/>
-      <c r="AG32" s="52"/>
-      <c r="AH32" s="51" ph="1"/>
-      <c r="AI32" s="52"/>
-      <c r="AJ32" s="51" ph="1"/>
-      <c r="AK32" s="52"/>
-      <c r="AL32" s="51" ph="1"/>
-      <c r="AM32" s="52"/>
-    </row>
-    <row r="33" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="63"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="39"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="39"/>
-      <c r="W33" s="40"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="39"/>
-      <c r="AA33" s="40"/>
-      <c r="AB33" s="39"/>
-      <c r="AC33" s="40"/>
-      <c r="AD33" s="39"/>
-      <c r="AE33" s="40"/>
-      <c r="AF33" s="39"/>
-      <c r="AG33" s="40"/>
-      <c r="AH33" s="39"/>
-      <c r="AI33" s="40"/>
-      <c r="AJ33" s="39"/>
-      <c r="AK33" s="40"/>
-      <c r="AL33" s="39"/>
-      <c r="AM33" s="40"/>
-    </row>
-    <row r="34" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="63">
+      <c r="A34" s="56">
         <v>14</v>
       </c>
       <c r="B34" s="51" ph="1"/>
@@ -10490,7 +10181,7 @@
       <c r="AM34" s="52"/>
     </row>
     <row r="35" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="63"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="39"/>
       <c r="C35" s="40"/>
       <c r="D35" s="39"/>
@@ -10531,7 +10222,7 @@
       <c r="AM35" s="40"/>
     </row>
     <row r="36" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="63">
+      <c r="A36" s="56">
         <v>15</v>
       </c>
       <c r="B36" s="51" ph="1"/>
@@ -10574,7 +10265,7 @@
       <c r="AM36" s="52"/>
     </row>
     <row r="37" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="63"/>
+      <c r="A37" s="56"/>
       <c r="B37" s="39"/>
       <c r="C37" s="40"/>
       <c r="D37" s="39"/>
@@ -10615,7 +10306,7 @@
       <c r="AM37" s="40"/>
     </row>
     <row r="38" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="63">
+      <c r="A38" s="56">
         <v>16</v>
       </c>
       <c r="B38" s="51" ph="1"/>
@@ -10658,7 +10349,7 @@
       <c r="AM38" s="52"/>
     </row>
     <row r="39" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="63"/>
+      <c r="A39" s="56"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40"/>
       <c r="D39" s="39"/>
@@ -10699,7 +10390,7 @@
       <c r="AM39" s="40"/>
     </row>
     <row r="40" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="63">
+      <c r="A40" s="56">
         <v>17</v>
       </c>
       <c r="B40" s="51" ph="1"/>
@@ -10742,7 +10433,7 @@
       <c r="AM40" s="52"/>
     </row>
     <row r="41" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="63"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="39"/>
       <c r="C41" s="40"/>
       <c r="D41" s="39"/>
@@ -10783,7 +10474,7 @@
       <c r="AM41" s="40"/>
     </row>
     <row r="42" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="63">
+      <c r="A42" s="56">
         <v>18</v>
       </c>
       <c r="B42" s="51" ph="1"/>
@@ -10826,7 +10517,7 @@
       <c r="AM42" s="52"/>
     </row>
     <row r="43" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="63"/>
+      <c r="A43" s="56"/>
       <c r="B43" s="39"/>
       <c r="C43" s="40"/>
       <c r="D43" s="39"/>
@@ -10968,9 +10659,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
+      <c r="AA45" s="60"/>
+      <c r="AB45" s="60"/>
+      <c r="AC45" s="60"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -10985,24 +10676,13 @@
     <row r="46" spans="1:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="AJ6:AK6"/>
     <mergeCell ref="AL6:AM6"/>
     <mergeCell ref="AA45:AC45"/>
@@ -11019,13 +10699,24 @@
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11034,7 +10725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11066,13 +10757,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -11147,80 +10838,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="57"/>
+      <c r="AM6" s="59"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -12882,9 +12573,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
+      <c r="AA45" s="60"/>
+      <c r="AB45" s="60"/>
+      <c r="AC45" s="60"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -12899,13 +12590,6 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="B5:S5"/>
     <mergeCell ref="V5:AM5"/>
@@ -12922,6 +12606,13 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12930,7 +12621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -12962,13 +12653,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
-      </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+        <v>46206</v>
+      </c>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -13043,80 +12734,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="57"/>
+      <c r="AM6" s="59"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -14772,9 +14463,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
+      <c r="AA45" s="60"/>
+      <c r="AB45" s="60"/>
+      <c r="AC45" s="60"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -14789,13 +14480,6 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="B5:S5"/>
     <mergeCell ref="V5:AM5"/>
@@ -14812,6 +14496,13 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14820,7 +14511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -14855,7 +14546,7 @@
       <c r="I4" s="38"/>
       <c r="J4" s="67">
         <f ca="1">(TODAY())</f>
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="K4" s="67"/>
       <c r="L4" s="2"/>
@@ -14932,80 +14623,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="56" t="s">
+      <c r="G6" s="59"/>
+      <c r="H6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="56" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="56" t="s">
+      <c r="M6" s="59"/>
+      <c r="N6" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="56" t="s">
+      <c r="O6" s="59"/>
+      <c r="P6" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="56" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="59"/>
-      <c r="V6" s="56" t="s">
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="59"/>
+      <c r="X6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="56" t="s">
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="56" t="s">
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="56" t="s">
+      <c r="AC6" s="59"/>
+      <c r="AD6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="57"/>
-      <c r="AF6" s="56" t="s">
+      <c r="AE6" s="59"/>
+      <c r="AF6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="56" t="s">
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="56" t="s">
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="56" t="s">
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="57"/>
+      <c r="AM6" s="59"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -16661,9 +16352,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
-      <c r="AC45" s="58"/>
+      <c r="AA45" s="60"/>
+      <c r="AB45" s="60"/>
+      <c r="AC45" s="60"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -16678,6 +16369,13 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="AA45:AC45"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="AB6:AC6"/>
@@ -16694,13 +16392,6 @@
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16709,7 +16400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:K251"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16736,8 +16427,8 @@
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="24">
-        <f ca="1">+'B1'!H4</f>
-        <v>46202</v>
+        <f ca="1">+셀!H4</f>
+        <v>46206</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>69</v>
@@ -19369,12 +19060,12 @@
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="14">
-        <f t="shared" ref="I68:I131" si="6">+G97+H97</f>
+        <f t="shared" ref="I97:I131" si="6">+G97+H97</f>
         <v>0</v>
       </c>
       <c r="J97" s="14"/>
       <c r="K97" s="14">
-        <f t="shared" ref="K68:K131" si="7">+I97-J97</f>
+        <f t="shared" ref="K97:K131" si="7">+I97-J97</f>
         <v>0</v>
       </c>
     </row>

--- a/재고조사표.xlsx
+++ b/재고조사표.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'W3'!$A$3:$AM$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">루!$A$3:$AM$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">리!$A$3:$AI$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">셀!$A$3:$AE$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">셀!$A$3:$Y$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'액젓,비트,완제품'!$A$3:$AM$45</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="358">
   <si>
     <t>M300</t>
   </si>
@@ -1952,12 +1952,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1968,6 +1962,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2708,7 +2708,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.125" customWidth="1"/>
-    <col min="2" max="31" width="36.125" customWidth="1"/>
+    <col min="2" max="25" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:34" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2732,13 +2732,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -2752,13 +2752,7 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="4"/>
+      <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:34" ht="115.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="25">
@@ -2792,93 +2786,69 @@
       <c r="P5" s="34"/>
       <c r="Q5" s="32"/>
       <c r="R5" s="31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S5" s="32"/>
       <c r="T5" s="31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U5" s="30"/>
       <c r="V5" s="31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W5" s="32"/>
       <c r="X5" s="31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="32"/>
-      <c r="Z5" s="31">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="31">
-        <v>2</v>
-      </c>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="31">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="32"/>
     </row>
     <row r="6" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="U6" s="59"/>
-      <c r="V6" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="U6" s="57"/>
+      <c r="V6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AE6" s="59"/>
+      <c r="Y6" s="57"/>
     </row>
     <row r="7" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="41" t="s">
@@ -2949,27 +2919,9 @@
       <c r="Y7" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="Z7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC7" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AD7" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE7" s="27" t="s">
-        <v>154</v>
-      </c>
     </row>
     <row r="8" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="56">
+      <c r="A8" s="61">
         <v>1</v>
       </c>
       <c r="B8" s="53" t="s" ph="1">
@@ -2996,21 +2948,18 @@
       <c r="U8" s="52"/>
       <c r="V8" s="51" ph="1"/>
       <c r="W8" s="52"/>
-      <c r="X8" s="51" ph="1"/>
+      <c r="X8" s="51" t="s" ph="1">
+        <v>278</v>
+      </c>
       <c r="Y8" s="52"/>
-      <c r="Z8" s="51" ph="1"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="51" ph="1"/>
-      <c r="AC8" s="52"/>
-      <c r="AD8" s="51" t="s" ph="1">
-        <v>278</v>
-      </c>
-      <c r="AE8" s="52"/>
+      <c r="Z8" ph="1"/>
+      <c r="AB8" ph="1"/>
+      <c r="AD8" ph="1"/>
       <c r="AF8" ph="1"/>
       <c r="AH8" ph="1"/>
     </row>
     <row r="9" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="47">
         <v>10</v>
       </c>
@@ -3038,18 +2987,12 @@
       <c r="V9" s="39"/>
       <c r="W9" s="40"/>
       <c r="X9" s="39"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="40">
+      <c r="Y9" s="40">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="56">
+      <c r="A10" s="61">
         <v>2</v>
       </c>
       <c r="B10" s="49" ph="1"/>
@@ -3072,25 +3015,22 @@
       <c r="S10" s="52"/>
       <c r="T10" s="51" ph="1"/>
       <c r="U10" s="52"/>
-      <c r="V10" s="51" ph="1"/>
+      <c r="V10" s="51" t="s" ph="1">
+        <v>280</v>
+      </c>
       <c r="W10" s="52"/>
-      <c r="X10" s="51" ph="1"/>
+      <c r="X10" s="51" t="s" ph="1">
+        <v>279</v>
+      </c>
       <c r="Y10" s="52"/>
-      <c r="Z10" s="51" ph="1"/>
-      <c r="AA10" s="52"/>
-      <c r="AB10" s="51" t="s" ph="1">
-        <v>280</v>
-      </c>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="51" t="s" ph="1">
-        <v>279</v>
-      </c>
-      <c r="AE10" s="52"/>
+      <c r="Z10" ph="1"/>
+      <c r="AB10" ph="1"/>
+      <c r="AD10" ph="1"/>
       <c r="AF10" ph="1"/>
       <c r="AH10" ph="1"/>
     </row>
     <row r="11" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="47"/>
       <c r="C11" s="48"/>
       <c r="D11" s="47"/>
@@ -3112,24 +3052,18 @@
       <c r="T11" s="39"/>
       <c r="U11" s="40"/>
       <c r="V11" s="39"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="40">
+      <c r="W11" s="40">
         <v>6</v>
       </c>
-      <c r="AD11" s="39">
+      <c r="X11" s="39">
         <v>5</v>
       </c>
-      <c r="AE11" s="40">
+      <c r="Y11" s="40">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="56">
+      <c r="A12" s="61">
         <v>3</v>
       </c>
       <c r="B12" s="49" ph="1"/>
@@ -3154,21 +3088,18 @@
       <c r="U12" s="52"/>
       <c r="V12" s="51" ph="1"/>
       <c r="W12" s="52"/>
-      <c r="X12" s="51" ph="1"/>
+      <c r="X12" s="51" t="s" ph="1">
+        <v>281</v>
+      </c>
       <c r="Y12" s="52"/>
-      <c r="Z12" s="51" ph="1"/>
-      <c r="AA12" s="52"/>
-      <c r="AB12" s="51" ph="1"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="51" t="s" ph="1">
-        <v>281</v>
-      </c>
-      <c r="AE12" s="52"/>
+      <c r="Z12" ph="1"/>
+      <c r="AB12" ph="1"/>
+      <c r="AD12" ph="1"/>
       <c r="AF12" ph="1"/>
       <c r="AH12" ph="1"/>
     </row>
     <row r="13" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="56"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="47"/>
       <c r="C13" s="48"/>
       <c r="D13" s="47"/>
@@ -3191,21 +3122,15 @@
       <c r="U13" s="40"/>
       <c r="V13" s="39"/>
       <c r="W13" s="40"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="39">
+      <c r="X13" s="39">
         <v>10</v>
       </c>
-      <c r="AE13" s="40">
+      <c r="Y13" s="40">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="56">
+      <c r="A14" s="61">
         <v>4</v>
       </c>
       <c r="B14" s="49" ph="1"/>
@@ -3230,21 +3155,18 @@
       <c r="U14" s="52"/>
       <c r="V14" s="51" ph="1"/>
       <c r="W14" s="52"/>
-      <c r="X14" s="51" ph="1"/>
+      <c r="X14" s="51" t="s" ph="1">
+        <v>282</v>
+      </c>
       <c r="Y14" s="52"/>
-      <c r="Z14" s="51" ph="1"/>
-      <c r="AA14" s="52"/>
-      <c r="AB14" s="51" ph="1"/>
-      <c r="AC14" s="52"/>
-      <c r="AD14" s="51" t="s" ph="1">
-        <v>282</v>
-      </c>
-      <c r="AE14" s="52"/>
+      <c r="Z14" ph="1"/>
+      <c r="AB14" ph="1"/>
+      <c r="AD14" ph="1"/>
       <c r="AF14" ph="1"/>
       <c r="AH14" ph="1"/>
     </row>
     <row r="15" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="56"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="47"/>
       <c r="C15" s="48"/>
       <c r="D15" s="47"/>
@@ -3267,21 +3189,15 @@
       <c r="U15" s="40"/>
       <c r="V15" s="39"/>
       <c r="W15" s="40"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="40"/>
-      <c r="AD15" s="39">
+      <c r="X15" s="39">
         <v>2</v>
       </c>
-      <c r="AE15" s="40">
+      <c r="Y15" s="40">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="56">
+      <c r="A16" s="61">
         <v>5</v>
       </c>
       <c r="B16" s="51" ph="1"/>
@@ -3306,21 +3222,18 @@
       <c r="U16" s="52"/>
       <c r="V16" s="51" ph="1"/>
       <c r="W16" s="52"/>
-      <c r="X16" s="51" ph="1"/>
+      <c r="X16" s="51" t="s" ph="1">
+        <v>283</v>
+      </c>
       <c r="Y16" s="52"/>
-      <c r="Z16" s="51" ph="1"/>
-      <c r="AA16" s="52"/>
-      <c r="AB16" s="51" ph="1"/>
-      <c r="AC16" s="52"/>
-      <c r="AD16" s="51" t="s" ph="1">
-        <v>283</v>
-      </c>
-      <c r="AE16" s="52"/>
+      <c r="Z16" ph="1"/>
+      <c r="AB16" ph="1"/>
+      <c r="AD16" ph="1"/>
       <c r="AF16" ph="1"/>
       <c r="AH16" ph="1"/>
     </row>
     <row r="17" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="39"/>
@@ -3343,21 +3256,15 @@
       <c r="U17" s="40"/>
       <c r="V17" s="39"/>
       <c r="W17" s="40"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="39"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="40"/>
-      <c r="AD17" s="39">
+      <c r="X17" s="39">
         <v>1</v>
       </c>
-      <c r="AE17" s="40">
+      <c r="Y17" s="40">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="56">
+      <c r="A18" s="61">
         <v>6</v>
       </c>
       <c r="B18" s="51" t="s" ph="1">
@@ -3382,25 +3289,22 @@
       <c r="S18" s="52"/>
       <c r="T18" s="51" ph="1"/>
       <c r="U18" s="52"/>
-      <c r="V18" s="51" ph="1"/>
+      <c r="V18" s="51" t="s" ph="1">
+        <v>286</v>
+      </c>
       <c r="W18" s="52"/>
-      <c r="X18" s="51" ph="1"/>
+      <c r="X18" s="51" t="s" ph="1">
+        <v>285</v>
+      </c>
       <c r="Y18" s="52"/>
-      <c r="Z18" s="51" ph="1"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="51" t="s" ph="1">
-        <v>286</v>
-      </c>
-      <c r="AC18" s="52"/>
-      <c r="AD18" s="51" t="s" ph="1">
-        <v>285</v>
-      </c>
-      <c r="AE18" s="52"/>
+      <c r="Z18" ph="1"/>
+      <c r="AB18" ph="1"/>
+      <c r="AD18" ph="1"/>
       <c r="AF18" ph="1"/>
       <c r="AH18" ph="1"/>
     </row>
     <row r="19" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="56"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="39">
         <v>10</v>
       </c>
@@ -3425,25 +3329,19 @@
       <c r="S19" s="40"/>
       <c r="T19" s="39"/>
       <c r="U19" s="40"/>
-      <c r="V19" s="39"/>
+      <c r="V19" s="39">
+        <v>4</v>
+      </c>
       <c r="W19" s="40"/>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="39"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="39">
-        <v>4</v>
-      </c>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="39">
+      <c r="X19" s="39">
         <v>6</v>
       </c>
-      <c r="AE19" s="40">
+      <c r="Y19" s="40">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="56">
+      <c r="A20" s="61">
         <v>7</v>
       </c>
       <c r="B20" s="51" t="s" ph="1">
@@ -3468,25 +3366,22 @@
       <c r="S20" s="52"/>
       <c r="T20" s="51" ph="1"/>
       <c r="U20" s="52"/>
-      <c r="V20" s="51" ph="1"/>
+      <c r="V20" s="51" t="s" ph="1">
+        <v>286</v>
+      </c>
       <c r="W20" s="52"/>
-      <c r="X20" s="51" ph="1"/>
+      <c r="X20" s="51" t="s" ph="1">
+        <v>287</v>
+      </c>
       <c r="Y20" s="52"/>
-      <c r="Z20" s="51" ph="1"/>
-      <c r="AA20" s="52"/>
-      <c r="AB20" s="51" t="s" ph="1">
-        <v>286</v>
-      </c>
-      <c r="AC20" s="52"/>
-      <c r="AD20" s="51" t="s" ph="1">
-        <v>287</v>
-      </c>
-      <c r="AE20" s="52"/>
+      <c r="Z20" ph="1"/>
+      <c r="AB20" ph="1"/>
+      <c r="AD20" ph="1"/>
       <c r="AF20" ph="1"/>
       <c r="AH20" ph="1"/>
     </row>
     <row r="21" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="56"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="39">
         <v>6</v>
       </c>
@@ -3511,27 +3406,21 @@
       <c r="S21" s="40"/>
       <c r="T21" s="39"/>
       <c r="U21" s="40"/>
-      <c r="V21" s="39"/>
-      <c r="W21" s="40"/>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="40"/>
-      <c r="Z21" s="39"/>
-      <c r="AA21" s="40"/>
-      <c r="AB21" s="39">
+      <c r="V21" s="39">
         <v>3</v>
       </c>
-      <c r="AC21" s="40">
+      <c r="W21" s="40">
         <v>15</v>
       </c>
-      <c r="AD21" s="39">
+      <c r="X21" s="39">
         <v>10</v>
       </c>
-      <c r="AE21" s="40">
+      <c r="Y21" s="40">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="56">
+      <c r="A22" s="61">
         <v>8</v>
       </c>
       <c r="B22" s="51" t="s" ph="1">
@@ -3558,21 +3447,18 @@
       <c r="U22" s="52"/>
       <c r="V22" s="51" ph="1"/>
       <c r="W22" s="52"/>
-      <c r="X22" s="51" ph="1"/>
+      <c r="X22" s="51" t="s" ph="1">
+        <v>277</v>
+      </c>
       <c r="Y22" s="52"/>
-      <c r="Z22" s="51" ph="1"/>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="51" ph="1"/>
-      <c r="AC22" s="52"/>
-      <c r="AD22" s="51" t="s" ph="1">
-        <v>277</v>
-      </c>
-      <c r="AE22" s="52"/>
+      <c r="Z22" ph="1"/>
+      <c r="AB22" ph="1"/>
+      <c r="AD22" ph="1"/>
       <c r="AF22" ph="1"/>
       <c r="AH22" ph="1"/>
     </row>
     <row r="23" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="39">
         <v>16</v>
       </c>
@@ -3599,19 +3485,13 @@
       <c r="U23" s="40"/>
       <c r="V23" s="39"/>
       <c r="W23" s="40"/>
-      <c r="X23" s="39"/>
+      <c r="X23" s="39">
+        <v>13</v>
+      </c>
       <c r="Y23" s="40"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="39">
-        <v>13</v>
-      </c>
-      <c r="AE23" s="40"/>
     </row>
     <row r="24" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="56">
+      <c r="A24" s="61">
         <v>9</v>
       </c>
       <c r="B24" s="51" t="s" ph="1">
@@ -3640,21 +3520,18 @@
       <c r="U24" s="52"/>
       <c r="V24" s="51" ph="1"/>
       <c r="W24" s="52"/>
-      <c r="X24" s="51" ph="1"/>
+      <c r="X24" s="51" t="s" ph="1">
+        <v>272</v>
+      </c>
       <c r="Y24" s="52"/>
-      <c r="Z24" s="51" ph="1"/>
-      <c r="AA24" s="52"/>
-      <c r="AB24" s="51" ph="1"/>
-      <c r="AC24" s="52"/>
-      <c r="AD24" s="51" t="s" ph="1">
-        <v>272</v>
-      </c>
-      <c r="AE24" s="52"/>
+      <c r="Z24" ph="1"/>
+      <c r="AB24" ph="1"/>
+      <c r="AD24" ph="1"/>
       <c r="AF24" ph="1"/>
       <c r="AH24" ph="1"/>
     </row>
     <row r="25" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="56"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="39">
         <v>2</v>
       </c>
@@ -3683,21 +3560,15 @@
       <c r="U25" s="40"/>
       <c r="V25" s="39"/>
       <c r="W25" s="40"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="39">
+      <c r="X25" s="39">
         <v>5</v>
       </c>
-      <c r="AE25" s="40">
+      <c r="Y25" s="40">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="56">
+      <c r="A26" s="61">
         <v>10</v>
       </c>
       <c r="B26" s="51" ph="1"/>
@@ -3724,17 +3595,14 @@
       <c r="W26" s="52"/>
       <c r="X26" s="51" ph="1"/>
       <c r="Y26" s="52"/>
-      <c r="Z26" s="51" ph="1"/>
-      <c r="AA26" s="52"/>
-      <c r="AB26" s="51" ph="1"/>
-      <c r="AC26" s="52"/>
-      <c r="AD26" s="51" ph="1"/>
-      <c r="AE26" s="52"/>
+      <c r="Z26" ph="1"/>
+      <c r="AB26" ph="1"/>
+      <c r="AD26" ph="1"/>
       <c r="AF26" ph="1"/>
       <c r="AH26" ph="1"/>
     </row>
     <row r="27" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="56"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="39"/>
@@ -3759,15 +3627,9 @@
       <c r="W27" s="40"/>
       <c r="X27" s="39"/>
       <c r="Y27" s="40"/>
-      <c r="Z27" s="39"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="39"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="39"/>
-      <c r="AE27" s="40"/>
     </row>
     <row r="28" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="56">
+      <c r="A28" s="61">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -3794,17 +3656,14 @@
       <c r="W28" s="52"/>
       <c r="X28" s="51" ph="1"/>
       <c r="Y28" s="52"/>
-      <c r="Z28" s="51" ph="1"/>
-      <c r="AA28" s="52"/>
-      <c r="AB28" s="51" ph="1"/>
-      <c r="AC28" s="52"/>
-      <c r="AD28" s="51" ph="1"/>
-      <c r="AE28" s="52"/>
+      <c r="Z28" ph="1"/>
+      <c r="AB28" ph="1"/>
+      <c r="AD28" ph="1"/>
       <c r="AF28" ph="1"/>
       <c r="AH28" ph="1"/>
     </row>
     <row r="29" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -3829,15 +3688,9 @@
       <c r="W29" s="40"/>
       <c r="X29" s="39"/>
       <c r="Y29" s="40"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="39"/>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="40"/>
     </row>
     <row r="30" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="56">
+      <c r="A30" s="61">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -3860,25 +3713,22 @@
       <c r="S30" s="52"/>
       <c r="T30" s="51" ph="1"/>
       <c r="U30" s="52"/>
-      <c r="V30" s="51" ph="1"/>
+      <c r="V30" s="51" t="s" ph="1">
+        <v>276</v>
+      </c>
       <c r="W30" s="52"/>
-      <c r="X30" s="51" ph="1"/>
+      <c r="X30" s="51" t="s" ph="1">
+        <v>275</v>
+      </c>
       <c r="Y30" s="52"/>
-      <c r="Z30" s="51" ph="1"/>
-      <c r="AA30" s="52"/>
-      <c r="AB30" s="51" t="s" ph="1">
-        <v>276</v>
-      </c>
-      <c r="AC30" s="52"/>
-      <c r="AD30" s="51" t="s" ph="1">
-        <v>275</v>
-      </c>
-      <c r="AE30" s="52"/>
+      <c r="Z30" ph="1"/>
+      <c r="AB30" ph="1"/>
+      <c r="AD30" ph="1"/>
       <c r="AF30" ph="1"/>
       <c r="AH30" ph="1"/>
     </row>
     <row r="31" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -3899,25 +3749,19 @@
       <c r="S31" s="40"/>
       <c r="T31" s="39"/>
       <c r="U31" s="40"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="40"/>
+      <c r="V31" s="39">
+        <v>2</v>
+      </c>
+      <c r="W31" s="40">
+        <v>14</v>
+      </c>
       <c r="X31" s="39"/>
-      <c r="Y31" s="40"/>
-      <c r="Z31" s="39"/>
-      <c r="AA31" s="40"/>
-      <c r="AB31" s="39">
-        <v>2</v>
-      </c>
-      <c r="AC31" s="40">
-        <v>14</v>
-      </c>
-      <c r="AD31" s="39"/>
-      <c r="AE31" s="40">
+      <c r="Y31" s="40">
         <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="56">
+      <c r="A32" s="61">
         <v>13</v>
       </c>
       <c r="B32" s="51" ph="1"/>
@@ -3940,25 +3784,22 @@
       <c r="S32" s="52"/>
       <c r="T32" s="51" ph="1"/>
       <c r="U32" s="52"/>
-      <c r="V32" s="51" ph="1"/>
+      <c r="V32" s="51" t="s" ph="1">
+        <v>274</v>
+      </c>
       <c r="W32" s="52"/>
-      <c r="X32" s="51" ph="1"/>
+      <c r="X32" s="51" t="s" ph="1">
+        <v>273</v>
+      </c>
       <c r="Y32" s="52"/>
-      <c r="Z32" s="51" ph="1"/>
-      <c r="AA32" s="52"/>
-      <c r="AB32" s="51" t="s" ph="1">
-        <v>274</v>
-      </c>
-      <c r="AC32" s="52"/>
-      <c r="AD32" s="51" t="s" ph="1">
-        <v>273</v>
-      </c>
-      <c r="AE32" s="52"/>
+      <c r="Z32" ph="1"/>
+      <c r="AB32" ph="1"/>
+      <c r="AD32" ph="1"/>
       <c r="AF32" ph="1"/>
       <c r="AH32" ph="1"/>
     </row>
     <row r="33" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="56"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40"/>
       <c r="D33" s="39"/>
@@ -3979,27 +3820,21 @@
       <c r="S33" s="40"/>
       <c r="T33" s="39"/>
       <c r="U33" s="40"/>
-      <c r="V33" s="39"/>
-      <c r="W33" s="40"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="39"/>
-      <c r="AA33" s="40"/>
-      <c r="AB33" s="39">
+      <c r="V33" s="39">
         <v>1</v>
       </c>
-      <c r="AC33" s="40">
+      <c r="W33" s="40">
         <v>3</v>
       </c>
-      <c r="AD33" s="39">
+      <c r="X33" s="39">
         <v>1</v>
       </c>
-      <c r="AE33" s="40">
+      <c r="Y33" s="40">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="56">
+      <c r="A34" s="61">
         <v>14</v>
       </c>
       <c r="B34" s="51" ph="1"/>
@@ -4024,21 +3859,18 @@
       <c r="U34" s="52"/>
       <c r="V34" s="51" ph="1"/>
       <c r="W34" s="52"/>
-      <c r="X34" s="51" ph="1"/>
+      <c r="X34" s="51" t="s" ph="1">
+        <v>272</v>
+      </c>
       <c r="Y34" s="52"/>
-      <c r="Z34" s="51" ph="1"/>
-      <c r="AA34" s="52"/>
-      <c r="AB34" s="51" ph="1"/>
-      <c r="AC34" s="52"/>
-      <c r="AD34" s="51" t="s" ph="1">
-        <v>272</v>
-      </c>
-      <c r="AE34" s="52"/>
+      <c r="Z34" ph="1"/>
+      <c r="AB34" ph="1"/>
+      <c r="AD34" ph="1"/>
       <c r="AF34" ph="1"/>
       <c r="AH34" ph="1"/>
     </row>
     <row r="35" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="56"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="39"/>
       <c r="C35" s="40"/>
       <c r="D35" s="39"/>
@@ -4061,21 +3893,15 @@
       <c r="U35" s="40"/>
       <c r="V35" s="39"/>
       <c r="W35" s="40"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="39"/>
-      <c r="AA35" s="40"/>
-      <c r="AB35" s="39"/>
-      <c r="AC35" s="40"/>
-      <c r="AD35" s="39">
+      <c r="X35" s="39">
         <v>2</v>
       </c>
-      <c r="AE35" s="40">
+      <c r="Y35" s="40">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="56">
+      <c r="A36" s="61">
         <v>15</v>
       </c>
       <c r="B36" s="51" ph="1"/>
@@ -4100,21 +3926,18 @@
       <c r="U36" s="52"/>
       <c r="V36" s="51" ph="1"/>
       <c r="W36" s="52"/>
-      <c r="X36" s="51" ph="1"/>
+      <c r="X36" s="51" t="s" ph="1">
+        <v>271</v>
+      </c>
       <c r="Y36" s="52"/>
-      <c r="Z36" s="51" ph="1"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="51" ph="1"/>
-      <c r="AC36" s="52"/>
-      <c r="AD36" s="51" t="s" ph="1">
-        <v>271</v>
-      </c>
-      <c r="AE36" s="52"/>
+      <c r="Z36" ph="1"/>
+      <c r="AB36" ph="1"/>
+      <c r="AD36" ph="1"/>
       <c r="AF36" ph="1"/>
       <c r="AH36" ph="1"/>
     </row>
     <row r="37" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
+      <c r="A37" s="61"/>
       <c r="B37" s="39"/>
       <c r="C37" s="40"/>
       <c r="D37" s="39"/>
@@ -4137,21 +3960,15 @@
       <c r="U37" s="40"/>
       <c r="V37" s="39"/>
       <c r="W37" s="40"/>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="40"/>
-      <c r="Z37" s="39"/>
-      <c r="AA37" s="40"/>
-      <c r="AB37" s="39"/>
-      <c r="AC37" s="40"/>
-      <c r="AD37" s="39">
+      <c r="X37" s="39">
         <v>16</v>
       </c>
-      <c r="AE37" s="40">
+      <c r="Y37" s="40">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="56">
+      <c r="A38" s="61">
         <v>16</v>
       </c>
       <c r="B38" s="51" ph="1"/>
@@ -4176,21 +3993,18 @@
       <c r="U38" s="52"/>
       <c r="V38" s="51" ph="1"/>
       <c r="W38" s="52"/>
-      <c r="X38" s="51" ph="1"/>
+      <c r="X38" s="51" t="s" ph="1">
+        <v>270</v>
+      </c>
       <c r="Y38" s="52"/>
-      <c r="Z38" s="51" ph="1"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="51" ph="1"/>
-      <c r="AC38" s="52"/>
-      <c r="AD38" s="51" t="s" ph="1">
-        <v>270</v>
-      </c>
-      <c r="AE38" s="52"/>
+      <c r="Z38" ph="1"/>
+      <c r="AB38" ph="1"/>
+      <c r="AD38" ph="1"/>
       <c r="AF38" ph="1"/>
       <c r="AH38" ph="1"/>
     </row>
     <row r="39" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="56"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40"/>
       <c r="D39" s="39"/>
@@ -4213,21 +4027,15 @@
       <c r="U39" s="40"/>
       <c r="V39" s="39"/>
       <c r="W39" s="40"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="40"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="40"/>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="40"/>
-      <c r="AD39" s="39">
+      <c r="X39" s="39">
         <v>3</v>
       </c>
-      <c r="AE39" s="40">
+      <c r="Y39" s="40">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="56">
+      <c r="A40" s="61">
         <v>17</v>
       </c>
       <c r="B40" s="51" ph="1"/>
@@ -4250,25 +4058,22 @@
       <c r="S40" s="52"/>
       <c r="T40" s="51" ph="1"/>
       <c r="U40" s="52"/>
-      <c r="V40" s="51" ph="1"/>
+      <c r="V40" s="51" t="s" ph="1">
+        <v>269</v>
+      </c>
       <c r="W40" s="52"/>
-      <c r="X40" s="51" ph="1"/>
+      <c r="X40" s="51" t="s" ph="1">
+        <v>268</v>
+      </c>
       <c r="Y40" s="52"/>
-      <c r="Z40" s="51" ph="1"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="51" t="s" ph="1">
-        <v>269</v>
-      </c>
-      <c r="AC40" s="52"/>
-      <c r="AD40" s="51" t="s" ph="1">
-        <v>268</v>
-      </c>
-      <c r="AE40" s="52"/>
+      <c r="Z40" ph="1"/>
+      <c r="AB40" ph="1"/>
+      <c r="AD40" ph="1"/>
       <c r="AF40" ph="1"/>
       <c r="AH40" ph="1"/>
     </row>
     <row r="41" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="56"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="39"/>
       <c r="C41" s="40"/>
       <c r="D41" s="39"/>
@@ -4290,24 +4095,18 @@
       <c r="T41" s="39"/>
       <c r="U41" s="40"/>
       <c r="V41" s="39"/>
-      <c r="W41" s="40"/>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="40"/>
-      <c r="Z41" s="39"/>
-      <c r="AA41" s="40"/>
-      <c r="AB41" s="39"/>
-      <c r="AC41" s="40">
+      <c r="W41" s="40">
         <v>21</v>
       </c>
-      <c r="AD41" s="39">
+      <c r="X41" s="39">
         <v>2</v>
       </c>
-      <c r="AE41" s="40">
+      <c r="Y41" s="40">
         <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:34" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="56">
+      <c r="A42" s="61">
         <v>18</v>
       </c>
       <c r="B42" s="51" ph="1"/>
@@ -4330,25 +4129,22 @@
       <c r="S42" s="52"/>
       <c r="T42" s="51" ph="1"/>
       <c r="U42" s="52"/>
-      <c r="V42" s="51" ph="1"/>
+      <c r="V42" s="51" t="s" ph="1">
+        <v>267</v>
+      </c>
       <c r="W42" s="52"/>
-      <c r="X42" s="51" ph="1"/>
+      <c r="X42" s="51" t="s" ph="1">
+        <v>266</v>
+      </c>
       <c r="Y42" s="52"/>
-      <c r="Z42" s="51" ph="1"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="51" t="s" ph="1">
-        <v>267</v>
-      </c>
-      <c r="AC42" s="52"/>
-      <c r="AD42" s="51" t="s" ph="1">
-        <v>266</v>
-      </c>
-      <c r="AE42" s="52"/>
+      <c r="Z42" ph="1"/>
+      <c r="AB42" ph="1"/>
+      <c r="AD42" ph="1"/>
       <c r="AF42" ph="1"/>
       <c r="AH42" ph="1"/>
     </row>
     <row r="43" spans="1:34" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="39"/>
       <c r="C43" s="40"/>
       <c r="D43" s="39"/>
@@ -4370,19 +4166,13 @@
       <c r="T43" s="39"/>
       <c r="U43" s="40"/>
       <c r="V43" s="39"/>
-      <c r="W43" s="40"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="40"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="40"/>
-      <c r="AB43" s="39"/>
-      <c r="AC43" s="40">
+      <c r="W43" s="40">
         <v>22</v>
       </c>
-      <c r="AD43" s="39">
+      <c r="X43" s="39">
         <v>12</v>
       </c>
-      <c r="AE43" s="40">
+      <c r="Y43" s="40">
         <v>12</v>
       </c>
     </row>
@@ -4418,33 +4208,21 @@
       <c r="P44" s="37"/>
       <c r="Q44" s="33"/>
       <c r="R44" s="31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S44" s="32"/>
       <c r="T44" s="31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U44" s="30"/>
       <c r="V44" s="31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W44" s="32"/>
       <c r="X44" s="31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y44" s="32"/>
-      <c r="Z44" s="31">
-        <v>3</v>
-      </c>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="31">
-        <v>2</v>
-      </c>
-      <c r="AC44" s="32"/>
-      <c r="AD44" s="31">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="32"/>
     </row>
     <row r="45" spans="1:34" ht="33" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16"/>
@@ -4463,51 +4241,18 @@
       <c r="O45" s="9"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="60"/>
-      <c r="T45" s="60"/>
-      <c r="U45" s="60"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
-      <c r="AB45" s="9"/>
-      <c r="AC45" s="9"/>
-      <c r="AD45" s="9"/>
-      <c r="AE45" s="12"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="12"/>
     </row>
     <row r="46" spans="1:34" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="S45:U45"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
+  <mergeCells count="31">
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A42:A43"/>
@@ -4516,6 +4261,29 @@
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4557,13 +4325,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -4670,80 +4438,80 @@
       <c r="AM5" s="63"/>
     </row>
     <row r="6" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="58" t="s">
+      <c r="Q6" s="57"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="58" t="s">
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="58" t="s">
+      <c r="AK6" s="57"/>
+      <c r="AL6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="59"/>
+      <c r="AM6" s="57"/>
     </row>
     <row r="7" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -4858,7 +4626,7 @@
       </c>
     </row>
     <row r="8" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="56">
+      <c r="A8" s="61">
         <v>1</v>
       </c>
       <c r="B8" s="51" t="s" ph="1">
@@ -4907,7 +4675,7 @@
       <c r="AM8" s="52"/>
     </row>
     <row r="9" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="39">
         <v>10</v>
       </c>
@@ -4958,7 +4726,7 @@
       <c r="AM9" s="40"/>
     </row>
     <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="56">
+      <c r="A10" s="61">
         <v>2</v>
       </c>
       <c r="B10" s="51" t="s" ph="1">
@@ -5005,7 +4773,7 @@
       <c r="AM10" s="52"/>
     </row>
     <row r="11" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="39">
         <v>4</v>
       </c>
@@ -5052,7 +4820,7 @@
       <c r="AM11" s="40"/>
     </row>
     <row r="12" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="56">
+      <c r="A12" s="61">
         <v>3</v>
       </c>
       <c r="B12" s="51" t="s" ph="1">
@@ -5101,7 +4869,7 @@
       <c r="AM12" s="52"/>
     </row>
     <row r="13" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="56"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="39">
         <v>10</v>
       </c>
@@ -5150,7 +4918,7 @@
       <c r="AM13" s="40"/>
     </row>
     <row r="14" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="56">
+      <c r="A14" s="61">
         <v>4</v>
       </c>
       <c r="B14" s="51" t="s" ph="1">
@@ -5199,7 +4967,7 @@
       <c r="AM14" s="52"/>
     </row>
     <row r="15" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="56"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="39">
         <v>2</v>
       </c>
@@ -5250,7 +5018,7 @@
       </c>
     </row>
     <row r="16" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="56">
+      <c r="A16" s="61">
         <v>5</v>
       </c>
       <c r="B16" s="51" t="s" ph="1">
@@ -5297,7 +5065,7 @@
       <c r="AM16" s="52"/>
     </row>
     <row r="17" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="39">
         <v>8</v>
       </c>
@@ -5344,7 +5112,7 @@
       </c>
     </row>
     <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="56">
+      <c r="A18" s="61">
         <v>6</v>
       </c>
       <c r="B18" s="51" t="s" ph="1">
@@ -5391,7 +5159,7 @@
       <c r="AM18" s="52"/>
     </row>
     <row r="19" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="56"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="39">
         <v>6</v>
       </c>
@@ -5438,7 +5206,7 @@
       </c>
     </row>
     <row r="20" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="56">
+      <c r="A20" s="61">
         <v>7</v>
       </c>
       <c r="B20" s="51" ph="1"/>
@@ -5483,7 +5251,7 @@
       <c r="AM20" s="52"/>
     </row>
     <row r="21" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="56"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="39"/>
@@ -5526,7 +5294,7 @@
       <c r="AM21" s="40"/>
     </row>
     <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="56">
+      <c r="A22" s="61">
         <v>8</v>
       </c>
       <c r="B22" s="51" ph="1"/>
@@ -5569,7 +5337,7 @@
       <c r="AM22" s="52"/>
     </row>
     <row r="23" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
       <c r="D23" s="39"/>
@@ -5610,7 +5378,7 @@
       <c r="AM23" s="40"/>
     </row>
     <row r="24" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="56">
+      <c r="A24" s="61">
         <v>9</v>
       </c>
       <c r="B24" s="51" ph="1"/>
@@ -5653,7 +5421,7 @@
       <c r="AM24" s="52"/>
     </row>
     <row r="25" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="56"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
       <c r="D25" s="39"/>
@@ -5694,7 +5462,7 @@
       <c r="AM25" s="40"/>
     </row>
     <row r="26" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="56">
+      <c r="A26" s="61">
         <v>10</v>
       </c>
       <c r="B26" s="51" ph="1"/>
@@ -5737,7 +5505,7 @@
       <c r="AM26" s="52"/>
     </row>
     <row r="27" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="56"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="39"/>
@@ -5778,7 +5546,7 @@
       <c r="AM27" s="40"/>
     </row>
     <row r="28" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="56">
+      <c r="A28" s="61">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -5821,7 +5589,7 @@
       <c r="AM28" s="52"/>
     </row>
     <row r="29" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -5862,7 +5630,7 @@
       <c r="AM29" s="40"/>
     </row>
     <row r="30" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="56">
+      <c r="A30" s="61">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -5905,7 +5673,7 @@
       <c r="AM30" s="52"/>
     </row>
     <row r="31" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -5946,7 +5714,7 @@
       <c r="AM31" s="40"/>
     </row>
     <row r="32" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="56">
+      <c r="A32" s="61">
         <v>13</v>
       </c>
       <c r="B32" s="51" t="s" ph="1">
@@ -5993,7 +5761,7 @@
       <c r="AM32" s="52"/>
     </row>
     <row r="33" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="56"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="39">
         <v>5</v>
       </c>
@@ -6040,7 +5808,7 @@
       <c r="AM33" s="40"/>
     </row>
     <row r="34" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="56">
+      <c r="A34" s="61">
         <v>14</v>
       </c>
       <c r="B34" s="51" t="s" ph="1">
@@ -6087,7 +5855,7 @@
       <c r="AM34" s="52"/>
     </row>
     <row r="35" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="56"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="39">
         <v>15</v>
       </c>
@@ -6136,7 +5904,7 @@
       </c>
     </row>
     <row r="36" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="56">
+      <c r="A36" s="61">
         <v>15</v>
       </c>
       <c r="B36" s="51" t="s" ph="1">
@@ -6185,7 +5953,7 @@
       <c r="AM36" s="52"/>
     </row>
     <row r="37" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
+      <c r="A37" s="61"/>
       <c r="B37" s="39">
         <v>6</v>
       </c>
@@ -6236,7 +6004,7 @@
       </c>
     </row>
     <row r="38" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="56">
+      <c r="A38" s="61">
         <v>16</v>
       </c>
       <c r="B38" s="51" t="s" ph="1">
@@ -6283,7 +6051,7 @@
       <c r="AM38" s="52"/>
     </row>
     <row r="39" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="56"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="39">
         <v>20</v>
       </c>
@@ -6328,7 +6096,7 @@
       <c r="AM39" s="40"/>
     </row>
     <row r="40" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="56">
+      <c r="A40" s="61">
         <v>17</v>
       </c>
       <c r="B40" s="51" t="s" ph="1">
@@ -6373,7 +6141,7 @@
       <c r="AM40" s="52"/>
     </row>
     <row r="41" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="56"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="39">
         <v>17</v>
       </c>
@@ -6416,7 +6184,7 @@
       <c r="AM41" s="40"/>
     </row>
     <row r="42" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="56">
+      <c r="A42" s="61">
         <v>18</v>
       </c>
       <c r="B42" s="51" t="s" ph="1">
@@ -6463,7 +6231,7 @@
       <c r="AM42" s="52"/>
     </row>
     <row r="43" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="39">
         <v>3</v>
       </c>
@@ -6611,9 +6379,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="58"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -6628,19 +6396,34 @@
     <row r="46" spans="1:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="AH5:AI5"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="AL5:AM5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF5:AG5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="A42:A43"/>
@@ -6657,34 +6440,19 @@
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AJ6:AK6"/>
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="AH5:AI5"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="AL5:AM5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AF5:AG5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6726,13 +6494,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -6827,72 +6595,72 @@
       <c r="AI5" s="32"/>
     </row>
     <row r="6" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="U6" s="59"/>
-      <c r="V6" s="58" t="s">
+      <c r="U6" s="57"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AI6" s="59"/>
+      <c r="AI6" s="57"/>
     </row>
     <row r="7" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -6995,7 +6763,7 @@
       </c>
     </row>
     <row r="8" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="56">
+      <c r="A8" s="61">
         <v>1</v>
       </c>
       <c r="B8" s="51" t="s" ph="1">
@@ -7046,7 +6814,7 @@
       <c r="AL8" ph="1"/>
     </row>
     <row r="9" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="39">
         <v>10</v>
       </c>
@@ -7099,7 +6867,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="56">
+      <c r="A10" s="61">
         <v>2</v>
       </c>
       <c r="B10" s="51" t="s" ph="1">
@@ -7146,7 +6914,7 @@
       <c r="AL10" ph="1"/>
     </row>
     <row r="11" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="39"/>
       <c r="C11" s="40">
         <v>18</v>
@@ -7189,7 +6957,7 @@
       <c r="AI11" s="40"/>
     </row>
     <row r="12" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="56">
+      <c r="A12" s="61">
         <v>3</v>
       </c>
       <c r="B12" s="51" t="s" ph="1">
@@ -7236,7 +7004,7 @@
       <c r="AL12" ph="1"/>
     </row>
     <row r="13" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="56"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="39"/>
       <c r="C13" s="40">
         <v>8</v>
@@ -7279,7 +7047,7 @@
       <c r="AI13" s="40"/>
     </row>
     <row r="14" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="56">
+      <c r="A14" s="61">
         <v>4</v>
       </c>
       <c r="B14" s="51" ph="1"/>
@@ -7322,7 +7090,7 @@
       <c r="AL14" ph="1"/>
     </row>
     <row r="15" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="56"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
       <c r="D15" s="39"/>
@@ -7363,7 +7131,7 @@
       </c>
     </row>
     <row r="16" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="56">
+      <c r="A16" s="61">
         <v>5</v>
       </c>
       <c r="B16" s="51" t="s" ph="1">
@@ -7412,7 +7180,7 @@
       <c r="AL16" ph="1"/>
     </row>
     <row r="17" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="39">
         <v>1</v>
       </c>
@@ -7465,7 +7233,7 @@
       </c>
     </row>
     <row r="18" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="56">
+      <c r="A18" s="61">
         <v>6</v>
       </c>
       <c r="B18" s="51" t="s" ph="1">
@@ -7510,7 +7278,7 @@
       <c r="AL18" ph="1"/>
     </row>
     <row r="19" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="56"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="39">
         <v>3</v>
       </c>
@@ -7555,7 +7323,7 @@
       </c>
     </row>
     <row r="20" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="56">
+      <c r="A20" s="61">
         <v>7</v>
       </c>
       <c r="B20" s="51" t="s" ph="1">
@@ -7602,7 +7370,7 @@
       <c r="AL20" ph="1"/>
     </row>
     <row r="21" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="56"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="39">
         <v>3</v>
       </c>
@@ -7649,7 +7417,7 @@
       </c>
     </row>
     <row r="22" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="56">
+      <c r="A22" s="61">
         <v>8</v>
       </c>
       <c r="B22" s="51" t="s" ph="1">
@@ -7694,7 +7462,7 @@
       <c r="AL22" ph="1"/>
     </row>
     <row r="23" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="39">
         <v>2</v>
       </c>
@@ -7737,7 +7505,7 @@
       <c r="AI23" s="40"/>
     </row>
     <row r="24" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="56">
+      <c r="A24" s="61">
         <v>9</v>
       </c>
       <c r="B24" s="51" t="s" ph="1">
@@ -7780,7 +7548,7 @@
       <c r="AL24" ph="1"/>
     </row>
     <row r="25" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="56"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="39">
         <v>8</v>
       </c>
@@ -7819,7 +7587,7 @@
       <c r="AI25" s="40"/>
     </row>
     <row r="26" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="56">
+      <c r="A26" s="61">
         <v>10</v>
       </c>
       <c r="B26" s="51" t="s" ph="1">
@@ -7864,7 +7632,7 @@
       <c r="AL26" ph="1"/>
     </row>
     <row r="27" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="56"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="39">
         <v>5</v>
       </c>
@@ -7905,7 +7673,7 @@
       <c r="AI27" s="40"/>
     </row>
     <row r="28" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="56">
+      <c r="A28" s="61">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -7946,7 +7714,7 @@
       <c r="AL28" ph="1"/>
     </row>
     <row r="29" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -7983,7 +7751,7 @@
       <c r="AI29" s="40"/>
     </row>
     <row r="30" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="56">
+      <c r="A30" s="61">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -8024,7 +7792,7 @@
       <c r="AL30" ph="1"/>
     </row>
     <row r="31" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -8061,7 +7829,7 @@
       <c r="AI31" s="40"/>
     </row>
     <row r="32" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="56">
+      <c r="A32" s="61">
         <v>13</v>
       </c>
       <c r="B32" s="51" ph="1"/>
@@ -8102,7 +7870,7 @@
       <c r="AL32" ph="1"/>
     </row>
     <row r="33" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="56"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40"/>
       <c r="D33" s="39"/>
@@ -8139,7 +7907,7 @@
       <c r="AI33" s="40"/>
     </row>
     <row r="34" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="56">
+      <c r="A34" s="61">
         <v>14</v>
       </c>
       <c r="B34" s="51" t="s" ph="1">
@@ -8188,7 +7956,7 @@
       <c r="AL34" ph="1"/>
     </row>
     <row r="35" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="56"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="39">
         <v>6</v>
       </c>
@@ -8235,7 +8003,7 @@
       <c r="AI35" s="40"/>
     </row>
     <row r="36" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="56">
+      <c r="A36" s="61">
         <v>15</v>
       </c>
       <c r="B36" s="51" t="s" ph="1">
@@ -8282,7 +8050,7 @@
       <c r="AL36" ph="1"/>
     </row>
     <row r="37" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
+      <c r="A37" s="61"/>
       <c r="B37" s="39">
         <v>3</v>
       </c>
@@ -8327,7 +8095,7 @@
       <c r="AI37" s="40"/>
     </row>
     <row r="38" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="56">
+      <c r="A38" s="61">
         <v>16</v>
       </c>
       <c r="B38" s="51" t="s" ph="1">
@@ -8376,7 +8144,7 @@
       <c r="AL38" ph="1"/>
     </row>
     <row r="39" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="56"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40">
         <v>12</v>
@@ -8421,7 +8189,7 @@
       <c r="AI39" s="40"/>
     </row>
     <row r="40" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="56">
+      <c r="A40" s="61">
         <v>17</v>
       </c>
       <c r="B40" s="51" t="s" ph="1">
@@ -8464,7 +8232,7 @@
       <c r="AL40" ph="1"/>
     </row>
     <row r="41" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="56"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="39">
         <v>2</v>
       </c>
@@ -8505,7 +8273,7 @@
       <c r="AI41" s="40"/>
     </row>
     <row r="42" spans="1:38" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="56">
+      <c r="A42" s="61">
         <v>18</v>
       </c>
       <c r="B42" s="51" t="s" ph="1">
@@ -8550,7 +8318,7 @@
       <c r="AL42" ph="1"/>
     </row>
     <row r="43" spans="1:38" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="39">
         <v>1</v>
       </c>
@@ -8682,9 +8450,9 @@
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
       <c r="V45" s="10"/>
-      <c r="W45" s="60"/>
-      <c r="X45" s="60"/>
-      <c r="Y45" s="60"/>
+      <c r="W45" s="58"/>
+      <c r="X45" s="58"/>
+      <c r="Y45" s="58"/>
       <c r="Z45" s="11"/>
       <c r="AA45" s="10"/>
       <c r="AB45" s="11"/>
@@ -8699,6 +8467,33 @@
     <row r="46" spans="1:38" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="B6:C6"/>
@@ -8709,33 +8504,6 @@
     <mergeCell ref="L6:M6"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="W45:Y45"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8777,13 +8545,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -8858,80 +8626,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="58" t="s">
+      <c r="Q6" s="57"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="58" t="s">
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="58" t="s">
+      <c r="AK6" s="57"/>
+      <c r="AL6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="59"/>
+      <c r="AM6" s="57"/>
     </row>
     <row r="7" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -9046,7 +8814,7 @@
       </c>
     </row>
     <row r="8" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A8" s="56">
+      <c r="A8" s="61">
         <v>1</v>
       </c>
       <c r="B8" s="51" ph="1"/>
@@ -9089,7 +8857,7 @@
       <c r="AM8" s="52"/>
     </row>
     <row r="9" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="39"/>
       <c r="C9" s="40"/>
       <c r="D9" s="39"/>
@@ -9130,7 +8898,7 @@
       <c r="AM9" s="40"/>
     </row>
     <row r="10" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A10" s="56">
+      <c r="A10" s="61">
         <v>2</v>
       </c>
       <c r="B10" s="51" ph="1"/>
@@ -9173,7 +8941,7 @@
       <c r="AM10" s="52"/>
     </row>
     <row r="11" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="39"/>
       <c r="C11" s="40"/>
       <c r="D11" s="39"/>
@@ -9214,7 +8982,7 @@
       <c r="AM11" s="40"/>
     </row>
     <row r="12" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A12" s="56">
+      <c r="A12" s="61">
         <v>3</v>
       </c>
       <c r="B12" s="51" ph="1"/>
@@ -9257,7 +9025,7 @@
       <c r="AM12" s="52"/>
     </row>
     <row r="13" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="56"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="39"/>
       <c r="C13" s="40"/>
       <c r="D13" s="39"/>
@@ -9298,7 +9066,7 @@
       <c r="AM13" s="40"/>
     </row>
     <row r="14" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A14" s="56">
+      <c r="A14" s="61">
         <v>4</v>
       </c>
       <c r="B14" s="51" ph="1"/>
@@ -9341,7 +9109,7 @@
       <c r="AM14" s="52"/>
     </row>
     <row r="15" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="56"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
       <c r="D15" s="39"/>
@@ -9382,7 +9150,7 @@
       <c r="AM15" s="40"/>
     </row>
     <row r="16" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A16" s="56">
+      <c r="A16" s="61">
         <v>5</v>
       </c>
       <c r="B16" s="51" ph="1"/>
@@ -9425,7 +9193,7 @@
       <c r="AM16" s="52"/>
     </row>
     <row r="17" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="39"/>
       <c r="C17" s="40"/>
       <c r="D17" s="39"/>
@@ -9466,7 +9234,7 @@
       <c r="AM17" s="40"/>
     </row>
     <row r="18" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A18" s="56">
+      <c r="A18" s="61">
         <v>6</v>
       </c>
       <c r="B18" s="51" ph="1"/>
@@ -9509,7 +9277,7 @@
       <c r="AM18" s="52"/>
     </row>
     <row r="19" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="56"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="39"/>
@@ -9550,7 +9318,7 @@
       <c r="AM19" s="40"/>
     </row>
     <row r="20" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A20" s="56">
+      <c r="A20" s="61">
         <v>7</v>
       </c>
       <c r="B20" s="51" ph="1"/>
@@ -9593,7 +9361,7 @@
       <c r="AM20" s="52"/>
     </row>
     <row r="21" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="56"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="39"/>
@@ -9634,7 +9402,7 @@
       <c r="AM21" s="40"/>
     </row>
     <row r="22" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A22" s="56">
+      <c r="A22" s="61">
         <v>8</v>
       </c>
       <c r="B22" s="51" ph="1"/>
@@ -9677,7 +9445,7 @@
       <c r="AM22" s="52"/>
     </row>
     <row r="23" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="39"/>
       <c r="C23" s="40"/>
       <c r="D23" s="39"/>
@@ -9718,7 +9486,7 @@
       <c r="AM23" s="40"/>
     </row>
     <row r="24" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A24" s="56">
+      <c r="A24" s="61">
         <v>9</v>
       </c>
       <c r="B24" s="51" ph="1"/>
@@ -9761,7 +9529,7 @@
       <c r="AM24" s="52"/>
     </row>
     <row r="25" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="56"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
       <c r="D25" s="39"/>
@@ -9802,7 +9570,7 @@
       <c r="AM25" s="40"/>
     </row>
     <row r="26" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A26" s="56">
+      <c r="A26" s="61">
         <v>10</v>
       </c>
       <c r="B26" s="51" ph="1"/>
@@ -9845,7 +9613,7 @@
       <c r="AM26" s="52"/>
     </row>
     <row r="27" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="56"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="39"/>
       <c r="C27" s="40"/>
       <c r="D27" s="39"/>
@@ -9886,7 +9654,7 @@
       <c r="AM27" s="40"/>
     </row>
     <row r="28" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A28" s="56">
+      <c r="A28" s="61">
         <v>11</v>
       </c>
       <c r="B28" s="51" ph="1"/>
@@ -9929,7 +9697,7 @@
       <c r="AM28" s="52"/>
     </row>
     <row r="29" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="56"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="39"/>
       <c r="C29" s="40"/>
       <c r="D29" s="39"/>
@@ -9970,7 +9738,7 @@
       <c r="AM29" s="40"/>
     </row>
     <row r="30" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A30" s="56">
+      <c r="A30" s="61">
         <v>12</v>
       </c>
       <c r="B30" s="51" ph="1"/>
@@ -10013,7 +9781,7 @@
       <c r="AM30" s="52"/>
     </row>
     <row r="31" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="39"/>
       <c r="C31" s="40"/>
       <c r="D31" s="39"/>
@@ -10054,7 +9822,7 @@
       <c r="AM31" s="40"/>
     </row>
     <row r="32" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A32" s="56">
+      <c r="A32" s="61">
         <v>13</v>
       </c>
       <c r="B32" s="51" ph="1"/>
@@ -10097,7 +9865,7 @@
       <c r="AM32" s="52"/>
     </row>
     <row r="33" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="56"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40"/>
       <c r="D33" s="39"/>
@@ -10138,7 +9906,7 @@
       <c r="AM33" s="40"/>
     </row>
     <row r="34" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A34" s="56">
+      <c r="A34" s="61">
         <v>14</v>
       </c>
       <c r="B34" s="51" ph="1"/>
@@ -10181,7 +9949,7 @@
       <c r="AM34" s="52"/>
     </row>
     <row r="35" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="56"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="39"/>
       <c r="C35" s="40"/>
       <c r="D35" s="39"/>
@@ -10222,7 +9990,7 @@
       <c r="AM35" s="40"/>
     </row>
     <row r="36" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A36" s="56">
+      <c r="A36" s="61">
         <v>15</v>
       </c>
       <c r="B36" s="51" ph="1"/>
@@ -10265,7 +10033,7 @@
       <c r="AM36" s="52"/>
     </row>
     <row r="37" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="56"/>
+      <c r="A37" s="61"/>
       <c r="B37" s="39"/>
       <c r="C37" s="40"/>
       <c r="D37" s="39"/>
@@ -10306,7 +10074,7 @@
       <c r="AM37" s="40"/>
     </row>
     <row r="38" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A38" s="56">
+      <c r="A38" s="61">
         <v>16</v>
       </c>
       <c r="B38" s="51" ph="1"/>
@@ -10349,7 +10117,7 @@
       <c r="AM38" s="52"/>
     </row>
     <row r="39" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="56"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="39"/>
       <c r="C39" s="40"/>
       <c r="D39" s="39"/>
@@ -10390,7 +10158,7 @@
       <c r="AM39" s="40"/>
     </row>
     <row r="40" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A40" s="56">
+      <c r="A40" s="61">
         <v>17</v>
       </c>
       <c r="B40" s="51" ph="1"/>
@@ -10433,7 +10201,7 @@
       <c r="AM40" s="52"/>
     </row>
     <row r="41" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="56"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="39"/>
       <c r="C41" s="40"/>
       <c r="D41" s="39"/>
@@ -10474,7 +10242,7 @@
       <c r="AM41" s="40"/>
     </row>
     <row r="42" spans="1:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="1.1499999999999999">
-      <c r="A42" s="56">
+      <c r="A42" s="61">
         <v>18</v>
       </c>
       <c r="B42" s="51" ph="1"/>
@@ -10517,7 +10285,7 @@
       <c r="AM42" s="52"/>
     </row>
     <row r="43" spans="1:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="39"/>
       <c r="C43" s="40"/>
       <c r="D43" s="39"/>
@@ -10659,9 +10427,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="58"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -10676,13 +10444,24 @@
     <row r="46" spans="1:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="AJ6:AK6"/>
     <mergeCell ref="AL6:AM6"/>
     <mergeCell ref="AA45:AC45"/>
@@ -10699,24 +10478,13 @@
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10757,13 +10525,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -10838,80 +10606,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="58" t="s">
+      <c r="Q6" s="57"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="58" t="s">
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="58" t="s">
+      <c r="AK6" s="57"/>
+      <c r="AL6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="59"/>
+      <c r="AM6" s="57"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -12573,9 +12341,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="58"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -12590,6 +12358,13 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="B5:S5"/>
     <mergeCell ref="V5:AM5"/>
@@ -12606,13 +12381,6 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12653,13 +12421,13 @@
       <c r="E4" s="36"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="57">
+      <c r="H4" s="60">
         <f ca="1">(TODAY())</f>
         <v>46206</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -12734,80 +12502,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="58" t="s">
+      <c r="Q6" s="57"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="58" t="s">
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="58" t="s">
+      <c r="AK6" s="57"/>
+      <c r="AL6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="59"/>
+      <c r="AM6" s="57"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -14463,9 +14231,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="58"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -14480,6 +14248,13 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="B5:S5"/>
     <mergeCell ref="V5:AM5"/>
@@ -14496,13 +14271,6 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AD6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14623,80 +14391,80 @@
       <c r="AM5" s="66"/>
     </row>
     <row r="6" spans="2:39" ht="115.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="58" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="58" t="s">
+      <c r="I6" s="57"/>
+      <c r="J6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="59"/>
-      <c r="L6" s="58" t="s">
+      <c r="K6" s="57"/>
+      <c r="L6" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="N6" s="58" t="s">
+      <c r="M6" s="57"/>
+      <c r="N6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="O6" s="59"/>
-      <c r="P6" s="58" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="58" t="s">
+      <c r="Q6" s="57"/>
+      <c r="R6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="58" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="W6" s="59"/>
-      <c r="X6" s="58" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="58" t="s">
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="58" t="s">
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="58" t="s">
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="58" t="s">
+      <c r="AE6" s="57"/>
+      <c r="AF6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AG6" s="57"/>
+      <c r="AH6" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="58" t="s">
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="58" t="s">
+      <c r="AK6" s="57"/>
+      <c r="AL6" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="AM6" s="59"/>
+      <c r="AM6" s="57"/>
     </row>
     <row r="7" spans="2:39" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26" t="s">
@@ -16352,9 +16120,9 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
       <c r="Z45" s="10"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+      <c r="AC45" s="58"/>
       <c r="AD45" s="11"/>
       <c r="AE45" s="10"/>
       <c r="AF45" s="11"/>
@@ -16369,13 +16137,6 @@
     <row r="46" spans="2:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AL6:AM6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="AA45:AC45"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="AB6:AC6"/>
@@ -16392,6 +16153,13 @@
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AJ6:AK6"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
